--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,96 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R214"/>
+  <dimension ref="A1:R222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>F. De Reclamo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tipo de tarea</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tipo de Elemento</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Coordenada_X</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Coordenada_Y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Operacion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
@@ -8416,7 +8404,11 @@
           <t>ESTADOS UNIDOS 4030</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -8434,8 +8426,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>base corroida
-Colocar PRFV 400</t>
+          <t>base corroida Colocar PRFV 400</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8486,7 +8477,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> S01123014</t>
+          <t>S01123014</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9174,7 +9165,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7981 </t>
+          <t>7981</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9209,7 +9200,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro </t>
+          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9260,7 +9251,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7874 </t>
+          <t>7874</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9948,7 +9939,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7919 </t>
+          <t>7919</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10120,7 +10111,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7891 </t>
+          <t>7891</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10206,7 +10197,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7961</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10550,7 +10541,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7939 </t>
+          <t>7939</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10722,7 +10713,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">900008939210 </t>
+          <t>900008939210</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10894,7 +10885,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7929 </t>
+          <t>7929</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10980,7 +10971,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7933 </t>
+          <t>7933</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11754,7 +11745,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> S01199412</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12012,7 +12003,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7965 </t>
+          <t>7965</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12098,7 +12089,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7971 </t>
+          <t>7971</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12270,7 +12261,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7976 </t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12356,7 +12347,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7980 </t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12442,7 +12433,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6343 </t>
+          <t>6343</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12786,7 +12777,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7995 </t>
+          <t>7995</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -14162,7 +14153,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8170 </t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14248,7 +14239,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8123 </t>
+          <t>8123</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14592,7 +14583,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8150 </t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -16308,7 +16299,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">8349 </t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -17684,7 +17675,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>-756</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -18372,7 +18363,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">8405 </t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18794,6 +18785,694 @@
         </is>
       </c>
       <c r="R214" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>S00165389</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>3/5/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>HONDURAS AV. 3708</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-58.414717</v>
+      </c>
+      <c r="N215" t="n">
+        <v>-34.594123</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>VCR-B</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>8509</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>GANDHI, MAHATMA 218</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Desmonte</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-58.440278</v>
+      </c>
+      <c r="N216" t="n">
+        <v>-34.603336</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>ALM-N</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>8514</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMARGO 481 </t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-58.439755</v>
+      </c>
+      <c r="N217" t="n">
+        <v>-34.60075</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>VCR-J</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>900009601610</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>THAMES 1109</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>-58.436188</v>
+      </c>
+      <c r="N218" t="n">
+        <v>-34.59138</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>VCR-I</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>S00194756</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CALIFORNIA 2861</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>columna inclinada</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-58.38692</v>
+      </c>
+      <c r="N219" t="n">
+        <v>-34.649509</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>CON-I</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>3/5/2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINOSA 98 </t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>base quebrada</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>-58.446457</v>
+      </c>
+      <c r="N220" t="n">
+        <v>-34.621398</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>PCH-G</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>8483</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>3/5/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ PEÑA 1650</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="n">
+        <v>-58.389533</v>
+      </c>
+      <c r="N221" t="n">
+        <v>-34.591306</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>RET-L</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>8556</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>OLAVARRIA 861</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>-58.365014</v>
+      </c>
+      <c r="N222" t="n">
+        <v>-34.638541</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>CON-E</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -7135,7 +7135,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ugarteche 3075</t>
+          <t>UGARTECHE 3079</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Castillo 4</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8042,10 +8042,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.430346</v>
+        <v>-58.430396</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.599721</v>
+        <v>-34.599668</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Catamarca 236</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R180"/>
+  <dimension ref="A1:R181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15894,6 +15894,84 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>3/18/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>GALLARDO, ANGEL AV. 1072</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-58.444908</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-34.607205</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R180"/>
+  <dimension ref="A1:R177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8243,22 +8243,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>900008939210</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LOPEZ, VICENTE 2099</t>
+          <t>Riglos 957</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811131662</t>
+          <t>811198753</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8300,14 +8300,14 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.394159</v>
+        <v>-58.435265</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.588587</v>
+        <v>-34.630164</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>RET-A</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8329,7 +8329,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Riglos 957</t>
+          <t>ABDALA, GERMAN 115</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811198753</t>
+          <t>811198752</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8379,21 +8379,21 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.435265</v>
+        <v>-58.36748</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.630164</v>
+        <v>-34.629504</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CON-D</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8415,7 +8415,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ABDALA, GERMAN 115</t>
+          <t xml:space="preserve"> GARCIA, MARTIN AV. 464 </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811198752</t>
+          <t>811198750</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8465,17 +8465,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.36748</v>
+        <v>-58.3713</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.629504</v>
+        <v>-34.630267</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8489,19 +8489,19 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CON-D</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GARCIA, MARTIN AV. 464 </t>
+          <t>French 2377</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811198750</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8558,14 +8558,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.3713</v>
+        <v>-58.398947</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.630267</v>
+        <v>-34.590946</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8575,19 +8575,19 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>French 2377</t>
+          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8644,14 +8644,14 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.398947</v>
+        <v>-58.409318</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.590946</v>
+        <v>-34.619842</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8661,19 +8661,19 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>poste inclinado base quebrada</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8723,21 +8723,21 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.409318</v>
+        <v>-58.403895</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.619842</v>
+        <v>-34.575559</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8759,7 +8759,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
+          <t>GURRUCHAGA 2473</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>poste inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8809,21 +8809,21 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.403895</v>
+        <v>-58.420304</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.575559</v>
+        <v>-34.582607</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>VCR-L</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8845,7 +8845,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GURRUCHAGA 2473</t>
+          <t xml:space="preserve">HUMAHUACA 4298 </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t>811198696</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8902,14 +8902,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.420304</v>
+        <v>-58.425302</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.582607</v>
+        <v>-34.601502</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>VCR-L</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8931,22 +8931,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>S01217715</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAHUACA 4298 </t>
+          <t xml:space="preserve">NECOCHEA 535 </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>811198691</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8988,14 +8988,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.425302</v>
+        <v>-58.362989</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.601502</v>
+        <v>-34.629167</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S01217715</t>
+          <t>S01159828</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">NECOCHEA 535 </t>
+          <t xml:space="preserve"> THAMES 2041</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811198691</t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9074,14 +9074,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.362989</v>
+        <v>-58.426667</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.629167</v>
+        <v>-34.585153</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9103,7 +9103,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S01159828</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9113,12 +9113,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> THAMES 2041</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9160,14 +9160,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.426667</v>
+        <v>-58.422033</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.585153</v>
+        <v>-34.598976</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9189,7 +9189,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>S01204493</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t>VILLAFAÑE, WENCESLAO 1697</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>811198665</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto inclinada corroida</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9239,21 +9239,21 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L103" t="n">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.422033</v>
+        <v>-58.374994</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.598976</v>
+        <v>-34.635173</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9263,34 +9263,34 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S01204493</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VILLAFAÑE, WENCESLAO 1697</t>
+          <t>GANDHI, MAHATMA 218</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811198665</t>
+          <t>811238734</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>tensor roto inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9325,43 +9325,43 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.374994</v>
+        <v>-58.440278</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.635173</v>
+        <v>-34.603336</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 218</t>
+          <t xml:space="preserve">GAONA AV. 1360 </t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811238734</t>
+          <t>811238719</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9418,24 +9418,24 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.440278</v>
+        <v>-58.448401</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.603336</v>
+        <v>-34.608681</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>NRA-B</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAONA AV. 1360 </t>
+          <t xml:space="preserve">FERRARI 490 </t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811238719</t>
+          <t>811238711</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9497,31 +9497,31 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.448401</v>
+        <v>-58.441842</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.608681</v>
+        <v>-34.605759</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>NRA-B</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9533,7 +9533,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERRARI 490 </t>
+          <t>SOLER 4509</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811238711</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9578,36 +9578,36 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.441842</v>
+        <v>-58.42336</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.605759</v>
+        <v>-34.588111</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9619,7 +9619,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SOLER 4509</t>
+          <t>DIAZ, CNEL. AV. 2512</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9664,26 +9664,26 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L108" t="n">
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.42336</v>
+        <v>-58.406111</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.588111</v>
+        <v>-34.58316</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9705,7 +9705,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2512</t>
+          <t>ESPINOSA 1099</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t>811238674</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9762,14 +9762,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.406111</v>
+        <v>-58.452139</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.58316</v>
+        <v>-34.610772</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>NRA-H</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9791,22 +9791,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ESPINOSA 1099</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811238674</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9841,21 +9841,21 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.452139</v>
+        <v>-58.416901</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.610772</v>
+        <v>-34.604236</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>NRA-H</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9877,22 +9877,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>ARANGUREN, JUAN F., DR. 462</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>811299459</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9934,10 +9934,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.416901</v>
+        <v>-58.437431</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.604236</v>
+        <v>-34.612405</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>ALM-I</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9963,22 +9963,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ARANGUREN, JUAN F., DR. 462</t>
+          <t>REPETTO, NICOLAS, DR. 1608</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811299459</t>
+          <t>811453857</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10020,24 +10020,24 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.437431</v>
+        <v>-58.452794</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.612405</v>
+        <v>-34.604603</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>ALM-I</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10049,7 +10049,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>REPETTO, NICOLAS, DR. 1608</t>
+          <t>LAVALLEJA 152</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10079,12 +10079,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811453857</t>
+          <t>811453799</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10106,10 +10106,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.452794</v>
+        <v>-58.437275</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.604603</v>
+        <v>-34.602678</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>NRA-G</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10135,22 +10135,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LAVALLEJA 152</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>811453799</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10192,24 +10192,24 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.437275</v>
+        <v>-58.412204</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.602678</v>
+        <v>-34.628609</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10221,22 +10221,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>S01248250</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>ALVAREZ, JULIAN 564</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t>811454078</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10278,14 +10278,14 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.412204</v>
+        <v>-58.434547</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.628609</v>
+        <v>-34.599587</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10307,22 +10307,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S01018482</t>
+          <t>S01248679</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AGUERO 2364</t>
+          <t>LOYOLA 163</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511365 </t>
+          <t>811454048</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10364,14 +10364,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.399462</v>
+        <v>-58.432674</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.585952</v>
+        <v>-34.598923</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10393,7 +10393,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S01211534</t>
+          <t>S01248701</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUNCAL 2490</t>
+          <t>LOYOLA 189</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811454103</t>
+          <t>811454013</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10443,21 +10443,21 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.401685</v>
+        <v>-58.432825</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.591336</v>
+        <v>-34.598761</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10479,17 +10479,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S01248250</t>
+          <t>S01248264</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 564</t>
+          <t>ALVAREZ, JULIAN 516</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811454078</t>
+          <t>811454392</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10536,10 +10536,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.434547</v>
+        <v>-58.434944</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.599587</v>
+        <v>-34.599841</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S01248679</t>
+          <t>S01290507</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LOYOLA 163</t>
+          <t>CABELLO 3472</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10595,12 +10595,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811454048</t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10615,17 +10615,17 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.432674</v>
+        <v>-58.409438</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.598923</v>
+        <v>-34.58118</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10651,7 +10651,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S01248701</t>
+          <t>S01339459</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LOYOLA 189</t>
+          <t>RODRIGUEZ, MARTIN 710</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>811454013</t>
+          <t>811453958</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10708,14 +10708,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.432825</v>
+        <v>-58.361268</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.598761</v>
+        <v>-34.634378</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10737,7 +10737,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S01248264</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 516</t>
+          <t>CAMARGO 111</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>811454392</t>
+          <t>811454377</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10794,24 +10794,24 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.434944</v>
+        <v>-58.437024</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.599841</v>
+        <v>-34.603753</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10823,17 +10823,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S01290507</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CABELLO 3472</t>
+          <t>DIAZ, CNEL. AV. 2599</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10853,12 +10853,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10873,21 +10873,21 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.409438</v>
+        <v>-58.405559</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.58118</v>
+        <v>-34.582478</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10909,22 +10909,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S01339459</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RODRIGUEZ, MARTIN 710</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>811453958</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -10966,14 +10966,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.361268</v>
+        <v>-58.406807</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.634378</v>
+        <v>-34.612902</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10995,22 +10995,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CAMARGO 111</t>
+          <t>ACOYTE 908</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>811454377</t>
+          <t>811454448</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11052,24 +11052,24 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.437024</v>
+        <v>-58.440177</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.603753</v>
+        <v>-34.607612</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11081,22 +11081,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2599</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11138,14 +11138,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.405559</v>
+        <v>-58.429481</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.582478</v>
+        <v>-34.608647</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t>FRIAS, EUSTOQUIO, TTE. GENERAL 378</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811454396</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -11224,24 +11224,24 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.406807</v>
+        <v>-58.433871</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.612902</v>
+        <v>-34.601836</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11253,22 +11253,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ACOYTE 908</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>811454448</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11310,10 +11310,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.440177</v>
+        <v>-58.404243</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.607612</v>
+        <v>-34.612859</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>SAN JOSE DE CALASANZ 266</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>811497993</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11396,14 +11396,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.429481</v>
+        <v>-58.437998</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.608647</v>
+        <v>-34.62221</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>PCH-K</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11425,22 +11425,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FRIAS, EUSTOQUIO, TTE. GENERAL 378</t>
+          <t>INCLAN 2402</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>811454396</t>
+          <t>811498043</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>basee corroida</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11482,24 +11482,24 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.433871</v>
+        <v>-58.398304</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.601836</v>
+        <v>-34.629576</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11511,22 +11511,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t>SAN JOSE 807</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>811498022</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11568,14 +11568,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.404243</v>
+        <v>-58.385925</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.612859</v>
+        <v>-34.618047</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11597,22 +11597,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SAN JOSE DE CALASANZ 266</t>
+          <t xml:space="preserve">GOMEZ, JUAN CARLOS 253 </t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>811497993</t>
+          <t>811626778</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11654,14 +11654,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.437998</v>
+        <v>-58.391109</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.62221</v>
+        <v>-34.637207</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PCH-K</t>
+          <t>CON-K</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11683,17 +11683,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>INCLAN 2402</t>
+          <t>MONTES DE OCA, MANUEL AV. 499</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11713,12 +11713,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>811498043</t>
+          <t>811626787</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>basee corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11740,10 +11740,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.398304</v>
+        <v>-58.375589</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.629576</v>
+        <v>-34.634175</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>RTT-?</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11769,22 +11769,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SAN JOSE 807</t>
+          <t>AGUIRRE 640</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>811498022</t>
+          <t>811626786</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corrroida</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11826,14 +11826,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.385925</v>
+        <v>-58.436805</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.618047</v>
+        <v>-34.596512</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11855,22 +11855,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>S00005738</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ, JUAN CARLOS 253 </t>
+          <t xml:space="preserve"> JUFRE 962</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>811626778</t>
+          <t>811626974</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>incliunada</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11912,14 +11912,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.391109</v>
+        <v>-58.436718</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.637207</v>
+        <v>-34.591089</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>CON-K</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11941,22 +11941,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 499</t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>811626787</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11998,10 +11998,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.375589</v>
+        <v>-58.4048</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.634175</v>
+        <v>-34.629021</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>RTT-?</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12027,22 +12027,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AGUIRRE 640</t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>811626786</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>corrroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12084,14 +12084,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.436805</v>
+        <v>-58.399059</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.596512</v>
+        <v>-34.608499</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S00005738</t>
+          <t>S01443954</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUFRE 962</t>
+          <t xml:space="preserve"> PALOS 432</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>811626974</t>
+          <t>811626849</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>incliunada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12170,14 +12170,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.436718</v>
+        <v>-58.362579</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.591089</v>
+        <v>-34.635096</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12199,22 +12199,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t>JUFRE 77</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>811626833</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12256,14 +12256,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.4048</v>
+        <v>-58.429659</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.629021</v>
+        <v>-34.598452</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12285,7 +12285,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t>COCHABAMBA 1740</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12315,12 +12315,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>811626824</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12342,14 +12342,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.399059</v>
+        <v>-58.390308</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.608499</v>
+        <v>-34.62403</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S01443954</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PALOS 432</t>
+          <t xml:space="preserve">SAENZ PEÑA, LUIS, PRES. 895 </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>811626849</t>
+          <t>811626819</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12428,10 +12428,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.362579</v>
+        <v>-58.387479</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.635096</v>
+        <v>-34.61865</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12457,22 +12457,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>JUFRE 77</t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>811626833</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12514,14 +12514,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.429659</v>
+        <v>-58.404766</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.598452</v>
+        <v>-34.620521</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12543,22 +12543,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>COCHABAMBA 1740</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>811626824</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -12600,10 +12600,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.390308</v>
+        <v>-58.393145</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.62403</v>
+        <v>-34.621778</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12629,22 +12629,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAENZ PEÑA, LUIS, PRES. 895 </t>
+          <t>RIGLOS 553</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12659,12 +12659,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>811626819</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12686,14 +12686,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.387479</v>
+        <v>-58.436277</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.61865</v>
+        <v>-34.625202</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>PCH-B</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12715,22 +12715,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t>Costa Rica 5741</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12772,14 +12772,14 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.404766</v>
+        <v>-58.436073</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.620521</v>
+        <v>-34.581506</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12801,22 +12801,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>CALLAO AV. 2014</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12831,12 +12831,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12858,14 +12858,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.393145</v>
+        <v>-58.386954</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.621778</v>
+        <v>-34.587337</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12887,22 +12887,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>RIGLOS 553</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12917,12 +12917,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12944,14 +12944,14 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.436277</v>
+        <v>-58.400243</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.625202</v>
+        <v>-34.610864</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>PCH-B</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12973,7 +12973,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Costa Rica 5741</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13003,12 +13003,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13030,14 +13030,14 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.436073</v>
+        <v>-58.399124</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.581506</v>
+        <v>-34.610705</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13059,7 +13059,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>S00066646</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13069,12 +13069,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CALLAO AV. 2014</t>
+          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13104,26 +13104,26 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L148" t="n">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.386954</v>
+        <v>-58.408259</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.587337</v>
+        <v>-34.580266</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13145,22 +13145,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>S00072053</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>HERRERA 197</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627116</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13195,21 +13195,21 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.400243</v>
+        <v>-58.37946</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.610864</v>
+        <v>-34.632625</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t>FRANKLIN 572</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627115</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13288,10 +13288,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.399124</v>
+        <v>-58.439651</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.610705</v>
+        <v>-34.607769</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13317,22 +13317,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S00066646</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13367,21 +13367,21 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L151" t="n">
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.408259</v>
+        <v>-58.413979</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.580266</v>
+        <v>-34.607475</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13403,22 +13403,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S00072053</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HERRERA 197</t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>811627116</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13453,17 +13453,17 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.37946</v>
+        <v>-58.395668</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.632625</v>
+        <v>-34.621926</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13489,17 +13489,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>S00073317</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/11/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FRANKLIN 572</t>
+          <t xml:space="preserve"> ESPINOSA 82</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>811627115</t>
+          <t>812440077</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13546,14 +13546,14 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.439651</v>
+        <v>-58.446397</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.607769</v>
+        <v>-34.621499</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13575,22 +13575,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>S00152251</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/13/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>PALOS 560</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>812440079</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13625,21 +13625,21 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L154" t="n">
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.413979</v>
+        <v>-58.361933</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.607475</v>
+        <v>-34.636158</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13661,17 +13661,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13691,12 +13691,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13718,10 +13718,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.395668</v>
+        <v>-58.400774</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.621926</v>
+        <v>-34.621503</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13747,22 +13747,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S00073317</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2/11/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESPINOSA 82</t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13777,12 +13777,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812440077</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13804,14 +13804,14 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.446397</v>
+        <v>-58.404576</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.621499</v>
+        <v>-34.607569</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13833,22 +13833,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S00152251</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2/13/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PALOS 560</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13863,12 +13863,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812440079</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13890,14 +13890,14 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.361933</v>
+        <v>-58.395384</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.636158</v>
+        <v>-34.600962</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13907,34 +13907,34 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>SINCLAIR 3106</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13949,12 +13949,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13976,14 +13976,14 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.400774</v>
+        <v>-58.422892</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.621503</v>
+        <v>-34.573802</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14005,22 +14005,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14035,12 +14035,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14062,14 +14062,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.404576</v>
+        <v>-58.41859</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.607569</v>
+        <v>-34.624508</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14091,22 +14091,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>S01061920</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t xml:space="preserve">BROWN, ALTE. AV. 1184 </t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14121,12 +14121,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440267</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14148,14 +14148,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.395384</v>
+        <v>-58.358913</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.600962</v>
+        <v>-34.635093</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14165,19 +14165,19 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>S01064368</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SINCLAIR 3106</t>
+          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -14234,10 +14234,10 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.422892</v>
+        <v>-58.426552</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.573802</v>
+        <v>-34.592076</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14263,22 +14263,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>S01447672</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t xml:space="preserve">BRANDSEN 485 </t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14293,7 +14293,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812440635</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -14320,14 +14320,14 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.41859</v>
+        <v>-58.360611</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.624508</v>
+        <v>-34.63495</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14349,22 +14349,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S01061920</t>
+          <t>S01200005</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/25/2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">BROWN, ALTE. AV. 1184 </t>
+          <t xml:space="preserve"> ARAOZ 390</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>812440267</t>
+          <t>812503577</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14406,14 +14406,14 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.358913</v>
+        <v>-58.437124</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.635093</v>
+        <v>-34.599891</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14435,22 +14435,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S01064368</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
+          <t>SANTO DOMINGO 3930</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14465,12 +14465,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>812503584</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14492,14 +14492,14 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.426552</v>
+        <v>-58.405248</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.592076</v>
+        <v>-34.655112</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14521,22 +14521,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S01447672</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDSEN 485 </t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>812440635</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -14578,14 +14578,14 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.360611</v>
+        <v>-58.416187</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.63495</v>
+        <v>-34.600138</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14607,22 +14607,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S01200005</t>
+          <t>S00115187</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2/25/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARAOZ 390</t>
+          <t>ESTADO PLURINACIONAL DE BOLIVIA 324</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>812503577</t>
+          <t>812503658</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14664,14 +14664,14 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.437124</v>
+        <v>-58.46673</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.599891</v>
+        <v>-34.627032</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14693,22 +14693,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>S01406817</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/3/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO 3930</t>
+          <t>CAMPOS, LUIS M. AV. 155</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14723,12 +14723,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>812503584</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14743,21 +14743,21 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.405248</v>
+        <v>-58.431638</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.655112</v>
+        <v>-34.574344</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14779,17 +14779,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -14809,12 +14809,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14836,10 +14836,10 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.416187</v>
+        <v>-58.431406</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.600138</v>
+        <v>-34.605009</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14865,22 +14865,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S00115187</t>
+          <t>S00165389</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 324</t>
+          <t>HONDURAS AV. 3708</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>812503658</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14910,26 +14910,26 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L169" t="n">
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.46673</v>
+        <v>-58.414717</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.627032</v>
+        <v>-34.594123</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>VCR-B</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14951,22 +14951,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S01406817</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>3/3/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 155</t>
+          <t>GANDHI, MAHATMA 218</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -15001,31 +15001,31 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.431638</v>
+        <v>-58.440278</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.574344</v>
+        <v>-34.603336</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15037,22 +15037,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t xml:space="preserve">CAMARGO 481 </t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15094,24 +15094,24 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.431406</v>
+        <v>-58.439755</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.605009</v>
+        <v>-34.60075</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15123,22 +15123,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S00165389</t>
+          <t>900009601610</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HONDURAS AV. 3708</t>
+          <t>THAMES 1109</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15168,22 +15168,22 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L172" t="n">
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.414717</v>
+        <v>-58.436188</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.594123</v>
+        <v>-34.59138</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>VCR-B</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15209,7 +15209,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>S00194756</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 218</t>
+          <t>CALIFORNIA 2861</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15244,12 +15244,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -15259,31 +15259,31 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.440278</v>
+        <v>-58.38692</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.603336</v>
+        <v>-34.649509</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15295,22 +15295,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMARGO 481 </t>
+          <t xml:space="preserve">ESPINOSA 98 </t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15352,24 +15352,24 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.439755</v>
+        <v>-58.446457</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.60075</v>
+        <v>-34.621398</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15381,22 +15381,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>900009601610</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>THAMES 1109</t>
+          <t>RODRIGUEZ PEÑA 1650</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15438,14 +15438,14 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>-58.436188</v>
+        <v>-58.389533</v>
       </c>
       <c r="N175" t="n">
-        <v>-34.59138</v>
+        <v>-34.591306</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15467,17 +15467,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S00194756</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CALIFORNIA 2861</t>
+          <t>OLAVARRIA 861</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15524,10 +15524,10 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.38692</v>
+        <v>-58.365014</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.649509</v>
+        <v>-34.638541</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>CON-E</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15551,19 +15551,15 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>8427</t>
-        </is>
-      </c>
+      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/18/2026</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOSA 98 </t>
+          <t>GALLARDO, ANGEL AV. 1072</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -15581,14 +15577,10 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15610,14 +15602,14 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.446457</v>
+        <v>-58.444908</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.621398</v>
+        <v>-34.607205</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -15627,260 +15619,10 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>8483</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>3/5/2026</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ PEÑA 1650</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L178" t="n">
-        <v>1</v>
-      </c>
-      <c r="M178" t="n">
-        <v>-58.389533</v>
-      </c>
-      <c r="N178" t="n">
-        <v>-34.591306</v>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>RET-L</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>8556</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>OLAVARRIA 861</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="n">
-        <v>-58.365014</v>
-      </c>
-      <c r="N179" t="n">
-        <v>-34.638541</v>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>CON-E</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr"/>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>3/18/2026</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>GALLARDO, ANGEL AV. 1072</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L180" t="n">
-        <v>1</v>
-      </c>
-      <c r="M180" t="n">
-        <v>-58.444908</v>
-      </c>
-      <c r="N180" t="n">
-        <v>-34.607205</v>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>ALM-O</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R177"/>
+  <dimension ref="A1:R178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15577,7 +15577,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>812879764</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr">
         <is>
           <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
@@ -15623,6 +15627,88 @@
         </is>
       </c>
       <c r="R177" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>M881</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>4/1/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AV LA PLATA 881</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-58.42712</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-34.625871</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>ALM-A</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -15663,7 +15663,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>813046342</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr">
         <is>
           <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R178"/>
+  <dimension ref="A1:R177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15551,20 +15551,24 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>M881</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3/18/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>GALLARDO, ANGEL AV. 1072</t>
+          <t>AV LA PLATA 881</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -15579,12 +15583,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>812879764</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15606,14 +15610,14 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>-58.444908</v>
+        <v>-58.42712</v>
       </c>
       <c r="N177" t="n">
-        <v>-34.607205</v>
+        <v>-34.625871</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -15623,96 +15627,10 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>M881</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>4/1/2026</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>AV LA PLATA 881</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>813046342</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L178" t="n">
-        <v>1</v>
-      </c>
-      <c r="M178" t="n">
-        <v>-58.42712</v>
-      </c>
-      <c r="N178" t="n">
-        <v>-34.625871</v>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>ALM-A</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R177"/>
+  <dimension ref="A1:R176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4463,7 +4463,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GUARDIA NACIONAL 2616</t>
+          <t>GAONA AV. 5130</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810259140</t>
+          <t>810259143</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4520,51 +4520,51 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.476253</v>
+        <v>-58.493913</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.660961</v>
+        <v>-34.62931</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>DEV-M</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2DEV</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GAONA AV. 5130</t>
+          <t>TERRADA 1580</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810259143</t>
+          <t>810333010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4606,14 +4606,14 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.493913</v>
+        <v>-58.476778</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.62931</v>
+        <v>-34.615101</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4623,34 +4623,34 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>DEV-M</t>
+          <t>NRA-M</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TERRADA 1580</t>
+          <t>BLANCO ENCALADA 5195</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810333010</t>
+          <t>810371034</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>A relevar si es nuestro el poste</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4685,17 +4685,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.476778</v>
+        <v>-58.48745</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.615101</v>
+        <v>-34.576133</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>NRA-M</t>
+          <t>ATH-C</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4721,22 +4721,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BLANCO ENCALADA 5195</t>
+          <t>SAN JUAN AV. 4256</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810371034</t>
+          <t>810394752</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>A relevar si es nuestro el poste</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4771,31 +4771,31 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.48745</v>
+        <v>-58.424867</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.576133</v>
+        <v>-34.626806</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>ATH-C</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4807,22 +4807,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 4256</t>
+          <t>MONTES DE OCA, MANUEL AV. 1795</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810394752</t>
+          <t>810398922</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4864,14 +4864,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.424867</v>
+        <v>-58.372942</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.626806</v>
+        <v>-34.648042</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4893,7 +4893,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 1795</t>
+          <t>MONTES DE OCA, MANUEL AV. 1245</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810398922</t>
+          <t>810398924</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4950,10 +4950,10 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.372942</v>
+        <v>-58.373951</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.648042</v>
+        <v>-34.642736</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4967,19 +4967,19 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>CON-A</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 1245</t>
+          <t>MONTES DE OCA, MANUEL AV. 1079</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810398924</t>
+          <t>810398927</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5036,10 +5036,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.373951</v>
+        <v>-58.374368</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.642736</v>
+        <v>-34.640512</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 1079</t>
+          <t>CORRIENTES AV. 4515</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810398927</t>
+          <t>810398934</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5122,14 +5122,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.374368</v>
+        <v>-58.428907</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.640512</v>
+        <v>-34.602301</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5139,34 +5139,34 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CORRIENTES AV. 4515</t>
+          <t>NEWBERY, JORGE 2696</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810398934</t>
+          <t>810421921</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5201,21 +5201,21 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.428907</v>
+        <v>-58.44293</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.602301</v>
+        <v>-34.574483</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2696</t>
+          <t>ALSINA, ADOLFO 2499</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810421921</t>
+          <t>810487023</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5287,21 +5287,21 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.44293</v>
+        <v>-58.40129</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.574483</v>
+        <v>-34.612123</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,7 +5323,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2499</t>
+          <t>VALLE, ARISTOBULO DEL 1599</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810487023</t>
+          <t>810487039</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,14 +5380,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.40129</v>
+        <v>-58.373739</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.612123</v>
+        <v>-34.636037</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5397,34 +5397,34 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VALLE, ARISTOBULO DEL 1599</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 1311</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810487039</t>
+          <t>810712730</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5466,14 +5466,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.373739</v>
+        <v>-58.446763</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.636037</v>
+        <v>-34.624743</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5483,19 +5483,19 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PCH-I</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 1311</t>
+          <t>MUÑECAS 1277</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810712730</t>
+          <t>810713028</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5552,24 +5552,24 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.446763</v>
+        <v>-58.44993</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.624743</v>
+        <v>-34.596737</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PCH-I</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5581,22 +5581,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MUÑECAS 1277</t>
+          <t>Paso 280</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810713028</t>
+          <t>810787612</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5638,24 +5638,24 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.44993</v>
+        <v>-58.403566</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.596737</v>
+        <v>-34.606691</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5667,22 +5667,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/14/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paso 280</t>
+          <t>SUAREZ 951</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810787612</t>
+          <t>810787554</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,14 +5724,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.403566</v>
+        <v>-58.36561</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.606691</v>
+        <v>-34.637763</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CON-D</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SUAREZ 951</t>
+          <t>VELEZ SARSFIELD AV. 10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810787554</t>
+          <t>810787548</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,10 +5810,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.36561</v>
+        <v>-58.390341</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.637763</v>
+        <v>-34.634311</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CON-D</t>
+          <t>CON-K</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VELEZ SARSFIELD AV. 10</t>
+          <t>DIAZ VELEZ AV. 3485</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810787548</t>
+          <t>810787513</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5896,14 +5896,14 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.390341</v>
+        <v>-58.415838</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.634311</v>
+        <v>-34.608469</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>CON-K</t>
+          <t>CLI-J</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5925,7 +5925,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 3485</t>
+          <t>ARCAMENDIA 793</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810787513</t>
+          <t>810787479</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>columna inclinada chocada doblada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,14 +5982,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.415838</v>
+        <v>-58.379965</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.608469</v>
+        <v>-34.641243</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>CLI-J</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6011,22 +6011,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>S00110420</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11/14/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ARCAMENDIA 793</t>
+          <t>YATAY 760</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>810787479</t>
+          <t>810804303</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>columna inclinada chocada doblada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.379965</v>
+        <v>-58.428752</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.641243</v>
+        <v>-34.603273</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,22 +6097,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S00110420</t>
+          <t>S01145223</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YATAY 760</t>
+          <t>C. Gaspar M. de Jovellanos 302</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810804303</t>
+          <t>810804373</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6147,31 +6147,27 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L67" t="n">
         <v>1</v>
       </c>
-      <c r="M67" t="n">
-        <v>-58.428752</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-34.603273</v>
-      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>No clasificado, consultar con mantenimiento</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,7 +6179,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01145223</t>
+          <t>S00942399</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6193,12 +6189,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>C. Gaspar M. de Jovellanos 302</t>
+          <t>ESTADOS UNIDOS 4030</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6209,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>810804373</t>
+          <t xml:space="preserve">01503983 </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida Colocar PRFV 400</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6228,32 +6224,36 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>-58.422536</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-34.623094</v>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>No clasificado, consultar con mantenimiento</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6265,7 +6265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S00942399</t>
+          <t>S01123014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ESTADOS UNIDOS 4030</t>
+          <t>PADILLA 1255</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">01503983 </t>
+          <t>810804370</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>base corroida Colocar PRFV 400</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6322,24 +6322,24 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.422536</v>
+        <v>-58.447651</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.623094</v>
+        <v>-34.595324</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-?</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6351,7 +6351,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S01123014</t>
+          <t>01110546</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PADILLA 1255</t>
+          <t>ALSINA, ADOLFO 2490</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>810804370</t>
+          <t>810804369</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>columna inclinada  base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6408,24 +6408,24 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.447651</v>
+        <v>-58.401266</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.595324</v>
+        <v>-34.612194</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>01110546</t>
+          <t>S00982328</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2490</t>
+          <t>BROWN, ALTE. AV. 1201</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>810804369</t>
+          <t>810804366</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>columna inclinada  base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6494,14 +6494,14 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.401266</v>
+        <v>-58.358915</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.612194</v>
+        <v>-34.635472</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6523,7 +6523,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S00982328</t>
+          <t>S01018458</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BROWN, ALTE. AV. 1201</t>
+          <t>AGUIRRE 290</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>810804366</t>
+          <t>810804344</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6580,14 +6580,14 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.358915</v>
+        <v>-58.434002</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.635472</v>
+        <v>-34.599505</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6609,7 +6609,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S01018458</t>
+          <t>S01098187</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AGUIRRE 290</t>
+          <t>SERRANO 432</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>810804344</t>
+          <t>810804334</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6666,24 +6666,24 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.434002</v>
+        <v>-58.443352</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.599505</v>
+        <v>-34.596905</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6695,17 +6695,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S01098187</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SERRANO 432</t>
+          <t>Malabia 510</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>810804334</t>
+          <t xml:space="preserve">01565659 </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6752,24 +6752,24 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.443352</v>
+        <v>-58.43835</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.596905</v>
+        <v>-34.598031</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6781,7 +6781,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>S01145254</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malabia 510</t>
+          <t>ARAOZ DE LAMADRID, GREGORIO, GRAL. 591</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">01565659 </t>
+          <t>810820746</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6838,14 +6838,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.43835</v>
+        <v>-58.360658</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.598031</v>
+        <v>-34.638004</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CON-E</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6867,7 +6867,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S01145254</t>
+          <t>S01183783</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ARAOZ DE LAMADRID, GREGORIO, GRAL. 591</t>
+          <t xml:space="preserve"> 24 DE NOVIEMBRE 2133 </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>810820746</t>
+          <t>810820614</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6924,10 +6924,10 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.360658</v>
+        <v>-58.409282</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.638004</v>
+        <v>-34.635897</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>CON-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,7 +6953,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S01183783</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 24 DE NOVIEMBRE 2133 </t>
+          <t>UGARTECHE 3079</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>810820614</t>
+          <t xml:space="preserve">01638326 </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7010,14 +7010,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.409282</v>
+        <v>-58.411934</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.635897</v>
+        <v>-34.580653</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,7 +7039,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UGARTECHE 3079</t>
+          <t>SAN LUIS 2488</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7069,17 +7069,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638326 </t>
+          <t>810820592</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
+          <t>base muy picada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7096,14 +7096,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.411934</v>
+        <v>-58.402179</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.580653</v>
+        <v>-34.600152</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7125,22 +7125,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SAN LUIS 2488</t>
+          <t>Paraguay 4301</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>810820592</t>
+          <t>810853935</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>base muy picada</t>
+          <t>Cambio de columna propia corroida en base</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7182,14 +7182,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.402179</v>
+        <v>-58.422434</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.600152</v>
+        <v>-34.585978</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7211,22 +7211,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>S01181254</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paraguay 4301</t>
+          <t>THAMES 677</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>810853935</t>
+          <t xml:space="preserve">01638116 </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cambio de columna propia corroida en base</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7268,10 +7268,10 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.422434</v>
+        <v>-58.441083</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.585978</v>
+        <v>-34.594165</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01181254</t>
+          <t>S01199701</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>THAMES 677</t>
+          <t>LAVALLEJA 726</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638116 </t>
+          <t>01635621</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7354,10 +7354,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.441083</v>
+        <v>-58.431973</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.594165</v>
+        <v>-34.599274</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7383,7 +7383,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S01199701</t>
+          <t>S00727663</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LAVALLEJA 726</t>
+          <t>NECOCHEA 721</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01635621</t>
+          <t>810862843</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7440,14 +7440,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.431973</v>
+        <v>-58.361052</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.599274</v>
+        <v>-34.630445</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7469,22 +7469,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S00727663</t>
+          <t>S00785128</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NECOCHEA 721</t>
+          <t>Paraguay 5055</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>810862843</t>
+          <t>810877555</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7526,14 +7526,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.361052</v>
+        <v>-58.429394</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.630445</v>
+        <v>-34.580587</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S00785128</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Paraguay 5055</t>
+          <t>VILLAFAÑE, WENCESLAO 1655</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>810877555</t>
+          <t>810877541</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7612,14 +7612,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.429394</v>
+        <v>-58.374586</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.580587</v>
+        <v>-34.635118</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7629,19 +7629,19 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>S00566892</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VILLAFAÑE, WENCESLAO 1655</t>
+          <t xml:space="preserve">SANTA FE AV. 3711 </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>810877541</t>
+          <t>810877633</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7698,14 +7698,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.374586</v>
+        <v>-58.416063</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.635118</v>
+        <v>-34.584975</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7715,34 +7715,34 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S00566892</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE AV. 3711 </t>
+          <t>URUGUAY 1070</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>810877633</t>
+          <t>810984538</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7784,14 +7784,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.416063</v>
+        <v>-58.387161</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.584975</v>
+        <v>-34.596255</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7813,22 +7813,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>900008882010</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>URUGUAY 1070</t>
+          <t xml:space="preserve"> PAVON AV. 3707 </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>810984538</t>
+          <t>810984598</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7870,14 +7870,14 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.387161</v>
+        <v>-58.416724</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.596255</v>
+        <v>-34.630181</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7899,17 +7899,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>900008882010</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAVON AV. 3707 </t>
+          <t>Querandíes 4220</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>810984598</t>
+          <t>810984700</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>correr, obstaculiza acceso a garage</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7949,21 +7949,21 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.416724</v>
+        <v>-58.426168</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.630181</v>
+        <v>-34.611095</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7985,22 +7985,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Querandíes 4220</t>
+          <t>AGUERO 2038</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8015,17 +8015,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>810984700</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>correr, obstaculiza acceso a garage</t>
+          <t>Traspasar red a columna nueva y retirar la vieja</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8035,21 +8035,21 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.426168</v>
+        <v>-58.402647</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.611095</v>
+        <v>-34.588274</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>AGU-G</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8071,7 +8071,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>S01200313</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AGUERO 2038</t>
+          <t>GANDHI, MAHATMA 311</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8106,17 +8106,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Traspasar red a columna nueva y retirar la vieja</t>
+          <t>corroida colocar columna pedir traspaso</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8128,24 +8128,24 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.402647</v>
+        <v>-58.440931</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.588274</v>
+        <v>-34.603655</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>AGU-G</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8157,22 +8157,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S01200313</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 311</t>
+          <t>Riglos 957</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811198753</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>corroida colocar columna pedir traspaso</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8214,24 +8214,24 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.440931</v>
+        <v>-58.435265</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.603655</v>
+        <v>-34.630164</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Riglos 957</t>
+          <t>ABDALA, GERMAN 115</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811198753</t>
+          <t>811198752</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8293,21 +8293,21 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.435265</v>
+        <v>-58.36748</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.630164</v>
+        <v>-34.629504</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CON-D</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8329,7 +8329,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ABDALA, GERMAN 115</t>
+          <t xml:space="preserve"> GARCIA, MARTIN AV. 464 </t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811198752</t>
+          <t>811198750</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8379,17 +8379,17 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.36748</v>
+        <v>-58.3713</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.629504</v>
+        <v>-34.630267</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8403,19 +8403,19 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>CON-D</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GARCIA, MARTIN AV. 464 </t>
+          <t>French 2377</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811198750</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8472,14 +8472,14 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.3713</v>
+        <v>-58.398947</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.630267</v>
+        <v>-34.590946</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8489,19 +8489,19 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>French 2377</t>
+          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8558,14 +8558,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.398947</v>
+        <v>-58.409318</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.590946</v>
+        <v>-34.619842</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8575,19 +8575,19 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>poste inclinado base quebrada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8637,21 +8637,21 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.409318</v>
+        <v>-58.403895</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.619842</v>
+        <v>-34.575559</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
+          <t>GURRUCHAGA 2473</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>poste inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8723,21 +8723,21 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.403895</v>
+        <v>-58.420304</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.575559</v>
+        <v>-34.582607</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>VCR-L</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8759,7 +8759,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GURRUCHAGA 2473</t>
+          <t xml:space="preserve">HUMAHUACA 4298 </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t>811198696</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8816,14 +8816,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.420304</v>
+        <v>-58.425302</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.582607</v>
+        <v>-34.601502</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>VCR-L</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8845,22 +8845,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>S01217715</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAHUACA 4298 </t>
+          <t xml:space="preserve">NECOCHEA 535 </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>811198691</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8902,14 +8902,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.425302</v>
+        <v>-58.362989</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.601502</v>
+        <v>-34.629167</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8931,7 +8931,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S01217715</t>
+          <t>S01159828</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">NECOCHEA 535 </t>
+          <t xml:space="preserve"> THAMES 2041</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811198691</t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8988,14 +8988,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.362989</v>
+        <v>-58.426667</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.629167</v>
+        <v>-34.585153</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S01159828</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> THAMES 2041</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9074,14 +9074,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.426667</v>
+        <v>-58.422033</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.585153</v>
+        <v>-34.598976</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9103,7 +9103,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>S01204493</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9113,12 +9113,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t>VILLAFAÑE, WENCESLAO 1697</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>811198665</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto inclinada corroida</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9153,21 +9153,21 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.422033</v>
+        <v>-58.374994</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.598976</v>
+        <v>-34.635173</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9177,34 +9177,34 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S01204493</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VILLAFAÑE, WENCESLAO 1697</t>
+          <t>GANDHI, MAHATMA 218</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811198665</t>
+          <t>811238734</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>tensor roto inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9239,43 +9239,43 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L103" t="n">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.374994</v>
+        <v>-58.440278</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.635173</v>
+        <v>-34.603336</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 218</t>
+          <t xml:space="preserve">GAONA AV. 1360 </t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811238734</t>
+          <t>811238719</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9332,24 +9332,24 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.440278</v>
+        <v>-58.448401</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.603336</v>
+        <v>-34.608681</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>NRA-B</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAONA AV. 1360 </t>
+          <t xml:space="preserve">FERRARI 490 </t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811238719</t>
+          <t>811238711</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9411,31 +9411,31 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.448401</v>
+        <v>-58.441842</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.608681</v>
+        <v>-34.605759</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>NRA-B</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERRARI 490 </t>
+          <t>SOLER 4509</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811238711</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9492,36 +9492,36 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.441842</v>
+        <v>-58.42336</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.605759</v>
+        <v>-34.588111</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9533,7 +9533,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SOLER 4509</t>
+          <t>DIAZ, CNEL. AV. 2512</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9578,26 +9578,26 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.42336</v>
+        <v>-58.406111</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.588111</v>
+        <v>-34.58316</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9619,7 +9619,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2512</t>
+          <t>ESPINOSA 1099</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t>811238674</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9676,14 +9676,14 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.406111</v>
+        <v>-58.452139</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.58316</v>
+        <v>-34.610772</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>NRA-H</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9705,22 +9705,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ESPINOSA 1099</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>811238674</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9755,21 +9755,21 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L109" t="n">
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.452139</v>
+        <v>-58.416901</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.610772</v>
+        <v>-34.604236</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>NRA-H</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9791,22 +9791,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>ARANGUREN, JUAN F., DR. 462</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>811299459</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9848,10 +9848,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.416901</v>
+        <v>-58.437431</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.604236</v>
+        <v>-34.612405</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>ALM-I</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9877,22 +9877,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ARANGUREN, JUAN F., DR. 462</t>
+          <t>REPETTO, NICOLAS, DR. 1608</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811299459</t>
+          <t>811453857</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9934,24 +9934,24 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.437431</v>
+        <v>-58.452794</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.612405</v>
+        <v>-34.604603</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>ALM-I</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9963,7 +9963,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>REPETTO, NICOLAS, DR. 1608</t>
+          <t>LAVALLEJA 152</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811453857</t>
+          <t>811453799</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10020,10 +10020,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.452794</v>
+        <v>-58.437275</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.604603</v>
+        <v>-34.602678</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>NRA-G</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10049,22 +10049,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LAVALLEJA 152</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10079,12 +10079,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811453799</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10106,24 +10106,24 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.437275</v>
+        <v>-58.412204</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.602678</v>
+        <v>-34.628609</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10135,22 +10135,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>S01248250</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>ALVAREZ, JULIAN 564</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t>811454078</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10192,14 +10192,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.412204</v>
+        <v>-58.434547</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.628609</v>
+        <v>-34.599587</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10221,7 +10221,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S01248250</t>
+          <t>S01248679</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 564</t>
+          <t>LOYOLA 163</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811454078</t>
+          <t>811454048</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10278,10 +10278,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.434547</v>
+        <v>-58.432674</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.599587</v>
+        <v>-34.598923</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S01248679</t>
+          <t>S01248701</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LOYOLA 163</t>
+          <t>LOYOLA 189</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>811454048</t>
+          <t>811454013</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10364,10 +10364,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.432674</v>
+        <v>-58.432825</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.598923</v>
+        <v>-34.598761</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10393,17 +10393,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S01248701</t>
+          <t>S01248264</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LOYOLA 189</t>
+          <t>ALVAREZ, JULIAN 516</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811454013</t>
+          <t>811454392</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10450,10 +10450,10 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.432825</v>
+        <v>-58.434944</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.598761</v>
+        <v>-34.599841</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10479,22 +10479,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S01248264</t>
+          <t>S01290507</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 516</t>
+          <t>CABELLO 3472</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811454392</t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10529,17 +10529,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.434944</v>
+        <v>-58.409438</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.599841</v>
+        <v>-34.58118</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10565,7 +10565,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S01290507</t>
+          <t>S01339459</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CABELLO 3472</t>
+          <t>RODRIGUEZ, MARTIN 710</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10595,12 +10595,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>811453958</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10615,21 +10615,21 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.409438</v>
+        <v>-58.361268</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.58118</v>
+        <v>-34.634378</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10651,22 +10651,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S01339459</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RODRIGUEZ, MARTIN 710</t>
+          <t>CAMARGO 111</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>811453958</t>
+          <t>811454377</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10708,24 +10708,24 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.361268</v>
+        <v>-58.437024</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.634378</v>
+        <v>-34.603753</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10737,7 +10737,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10747,12 +10747,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CAMARGO 111</t>
+          <t>DIAZ, CNEL. AV. 2599</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>811454377</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10794,24 +10794,24 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.437024</v>
+        <v>-58.405559</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.603753</v>
+        <v>-34.582478</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10823,22 +10823,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2599</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10853,12 +10853,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10880,14 +10880,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.405559</v>
+        <v>-58.406807</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.582478</v>
+        <v>-34.612902</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t>ACOYTE 908</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811454448</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -10966,10 +10966,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.406807</v>
+        <v>-58.440177</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.612902</v>
+        <v>-34.607612</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10995,7 +10995,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ACOYTE 908</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>811454448</t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11052,10 +11052,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.440177</v>
+        <v>-58.429481</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.607612</v>
+        <v>-34.608647</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11081,7 +11081,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>FRIAS, EUSTOQUIO, TTE. GENERAL 378</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>811454396</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11138,24 +11138,24 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.429481</v>
+        <v>-58.433871</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.608647</v>
+        <v>-34.601836</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11167,22 +11167,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FRIAS, EUSTOQUIO, TTE. GENERAL 378</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>811454396</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11224,24 +11224,24 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.433871</v>
+        <v>-58.404243</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.601836</v>
+        <v>-34.612859</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11253,7 +11253,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t>SAN JOSE DE CALASANZ 266</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>811497993</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11310,14 +11310,14 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.404243</v>
+        <v>-58.437998</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.612859</v>
+        <v>-34.62221</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>PCH-K</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SAN JOSE DE CALASANZ 266</t>
+          <t>INCLAN 2402</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11369,12 +11369,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>811497993</t>
+          <t>811498043</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>basee corroida</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11396,14 +11396,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.437998</v>
+        <v>-58.398304</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.62221</v>
+        <v>-34.629576</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PCH-K</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11425,7 +11425,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>INCLAN 2402</t>
+          <t>SAN JOSE 807</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>811498043</t>
+          <t>811498022</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>basee corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11482,10 +11482,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.398304</v>
+        <v>-58.385925</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.629576</v>
+        <v>-34.618047</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11511,22 +11511,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SAN JOSE 807</t>
+          <t xml:space="preserve">GOMEZ, JUAN CARLOS 253 </t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>811498022</t>
+          <t>811626778</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11568,10 +11568,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.385925</v>
+        <v>-58.391109</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.618047</v>
+        <v>-34.637207</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>CON-K</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11597,17 +11597,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ, JUAN CARLOS 253 </t>
+          <t>MONTES DE OCA, MANUEL AV. 499</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>811626778</t>
+          <t>811626787</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11654,10 +11654,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.391109</v>
+        <v>-58.375589</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.637207</v>
+        <v>-34.634175</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>CON-K</t>
+          <t>RTT-?</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11683,7 +11683,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11693,12 +11693,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 499</t>
+          <t>AGUIRRE 640</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11713,12 +11713,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>811626787</t>
+          <t>811626786</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corrroida</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11740,14 +11740,14 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.375589</v>
+        <v>-58.436805</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.634175</v>
+        <v>-34.596512</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>RTT-?</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11769,17 +11769,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>S00005738</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AGUIRRE 640</t>
+          <t xml:space="preserve"> JUFRE 962</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>811626786</t>
+          <t>811626974</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>corrroida</t>
+          <t>incliunada</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11826,10 +11826,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.436805</v>
+        <v>-58.436718</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.596512</v>
+        <v>-34.591089</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11855,22 +11855,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S00005738</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUFRE 962</t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>811626974</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>incliunada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11912,14 +11912,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.436718</v>
+        <v>-58.4048</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.591089</v>
+        <v>-34.629021</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11941,17 +11941,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11998,14 +11998,14 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.4048</v>
+        <v>-58.399059</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.629021</v>
+        <v>-34.608499</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12027,7 +12027,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>S01443954</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t xml:space="preserve"> PALOS 432</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>811626849</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12084,14 +12084,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.399059</v>
+        <v>-58.362579</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.608499</v>
+        <v>-34.635096</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S01443954</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PALOS 432</t>
+          <t>JUFRE 77</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>811626849</t>
+          <t>811626833</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12170,14 +12170,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.362579</v>
+        <v>-58.429659</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.635096</v>
+        <v>-34.598452</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12199,7 +12199,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>JUFRE 77</t>
+          <t>COCHABAMBA 1740</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12229,12 +12229,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>811626833</t>
+          <t>811626824</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12256,14 +12256,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.429659</v>
+        <v>-58.390308</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.598452</v>
+        <v>-34.62403</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12285,7 +12285,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>COCHABAMBA 1740</t>
+          <t xml:space="preserve">SAENZ PEÑA, LUIS, PRES. 895 </t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>811626824</t>
+          <t>811626819</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12342,10 +12342,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.390308</v>
+        <v>-58.387479</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.62403</v>
+        <v>-34.61865</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12371,22 +12371,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAENZ PEÑA, LUIS, PRES. 895 </t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>811626819</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12428,10 +12428,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.387479</v>
+        <v>-58.404766</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.61865</v>
+        <v>-34.620521</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12457,17 +12457,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12514,10 +12514,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.404766</v>
+        <v>-58.393145</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.620521</v>
+        <v>-34.621778</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12543,7 +12543,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>RIGLOS 553</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12573,12 +12573,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -12600,14 +12600,14 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.393145</v>
+        <v>-58.436277</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.621778</v>
+        <v>-34.625202</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>PCH-B</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12629,22 +12629,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RIGLOS 553</t>
+          <t>Costa Rica 5741</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12659,12 +12659,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12686,14 +12686,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.436277</v>
+        <v>-58.436073</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.625202</v>
+        <v>-34.581506</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>PCH-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12715,7 +12715,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Costa Rica 5741</t>
+          <t>CALLAO AV. 2014</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -12772,14 +12772,14 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.436073</v>
+        <v>-58.386954</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.581506</v>
+        <v>-34.587337</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12801,7 +12801,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12811,12 +12811,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CALLAO AV. 2014</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12858,14 +12858,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.386954</v>
+        <v>-58.400243</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.587337</v>
+        <v>-34.610864</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12887,7 +12887,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12917,12 +12917,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12944,10 +12944,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.400243</v>
+        <v>-58.399124</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.610864</v>
+        <v>-34.610705</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>S00066646</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13003,12 +13003,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13023,21 +13023,21 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.399124</v>
+        <v>-58.408259</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.610705</v>
+        <v>-34.580266</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13059,22 +13059,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S00066646</t>
+          <t>S00072053</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
+          <t>HERRERA 197</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>811627116</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13109,21 +13109,21 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L148" t="n">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.408259</v>
+        <v>-58.37946</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.580266</v>
+        <v>-34.632625</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13145,7 +13145,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S00072053</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13155,12 +13155,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HERRERA 197</t>
+          <t>FRANKLIN 572</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>811627116</t>
+          <t>811627115</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13195,21 +13195,21 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.37946</v>
+        <v>-58.439651</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.632625</v>
+        <v>-34.607769</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FRANKLIN 572</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>811627115</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13281,17 +13281,17 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L150" t="n">
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.439651</v>
+        <v>-58.413979</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.607769</v>
+        <v>-34.607475</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13317,22 +13317,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13367,21 +13367,21 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L151" t="n">
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.413979</v>
+        <v>-58.395668</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.607475</v>
+        <v>-34.621926</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13403,22 +13403,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>S00073317</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/11/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t xml:space="preserve"> ESPINOSA 82</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>812440077</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13460,14 +13460,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.395668</v>
+        <v>-58.446397</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.621926</v>
+        <v>-34.621499</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13489,22 +13489,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S00073317</t>
+          <t>S00152251</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2/11/2026</t>
+          <t>2/13/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESPINOSA 82</t>
+          <t>PALOS 560</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812440077</t>
+          <t>812440079</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13546,14 +13546,14 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.446397</v>
+        <v>-58.361933</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.621499</v>
+        <v>-34.636158</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13575,22 +13575,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S00152251</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/13/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PALOS 560</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812440079</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13632,10 +13632,10 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.361933</v>
+        <v>-58.400774</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.636158</v>
+        <v>-34.621503</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13661,17 +13661,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13718,14 +13718,14 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.400774</v>
+        <v>-58.404576</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.621503</v>
+        <v>-34.607569</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13747,7 +13747,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13804,10 +13804,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.404576</v>
+        <v>-58.395384</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.607569</v>
+        <v>-34.600962</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13821,34 +13821,34 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t>SINCLAIR 3106</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13863,12 +13863,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13890,14 +13890,14 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.395384</v>
+        <v>-58.422892</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.600962</v>
+        <v>-34.573802</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13907,19 +13907,19 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SINCLAIR 3106</t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13949,12 +13949,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13976,14 +13976,14 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.422892</v>
+        <v>-58.41859</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.573802</v>
+        <v>-34.624508</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14005,7 +14005,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>S01061920</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14015,12 +14015,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t xml:space="preserve">BROWN, ALTE. AV. 1184 </t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14035,12 +14035,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812440267</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14062,14 +14062,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.41859</v>
+        <v>-58.358913</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.624508</v>
+        <v>-34.635093</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14091,7 +14091,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S01061920</t>
+          <t>S01064368</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">BROWN, ALTE. AV. 1184 </t>
+          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14121,12 +14121,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812440267</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14148,14 +14148,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.358913</v>
+        <v>-58.426552</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.635093</v>
+        <v>-34.592076</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14177,22 +14177,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S01064368</t>
+          <t>S01447672</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
+          <t xml:space="preserve">BRANDSEN 485 </t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>812440635</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14234,14 +14234,14 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.426552</v>
+        <v>-58.360611</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.592076</v>
+        <v>-34.63495</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14263,22 +14263,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S01447672</t>
+          <t>S01200005</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/25/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDSEN 485 </t>
+          <t xml:space="preserve"> ARAOZ 390</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14293,7 +14293,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812440635</t>
+          <t>812503577</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -14320,14 +14320,14 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.360611</v>
+        <v>-58.437124</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.63495</v>
+        <v>-34.599891</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14349,22 +14349,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S01200005</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2/25/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARAOZ 390</t>
+          <t>SANTO DOMINGO 3930</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>812503577</t>
+          <t>812503584</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14406,14 +14406,14 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.437124</v>
+        <v>-58.405248</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.599891</v>
+        <v>-34.655112</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14435,22 +14435,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO 3930</t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14465,12 +14465,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>812503584</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14492,14 +14492,14 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.405248</v>
+        <v>-58.416187</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.655112</v>
+        <v>-34.600138</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14521,22 +14521,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00115187</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>ESTADO PLURINACIONAL DE BOLIVIA 324</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>812503658</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14578,14 +14578,14 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.416187</v>
+        <v>-58.46673</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.600138</v>
+        <v>-34.627032</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14607,22 +14607,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S00115187</t>
+          <t>S01406817</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/3/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 324</t>
+          <t>CAMPOS, LUIS M. AV. 155</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>812503658</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -14657,21 +14657,21 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L166" t="n">
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.46673</v>
+        <v>-58.431638</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.627032</v>
+        <v>-34.574344</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14693,22 +14693,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S01406817</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3/3/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 155</t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14743,21 +14743,21 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.431638</v>
+        <v>-58.431406</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.574344</v>
+        <v>-34.605009</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14779,22 +14779,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>S00165389</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t>HONDURAS AV. 3708</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14824,26 +14824,26 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L168" t="n">
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.431406</v>
+        <v>-58.414717</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.605009</v>
+        <v>-34.594123</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>VCR-B</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14865,22 +14865,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S00165389</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HONDURAS AV. 3708</t>
+          <t>GANDHI, MAHATMA 218</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14900,46 +14900,46 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L169" t="n">
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.414717</v>
+        <v>-58.440278</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.594123</v>
+        <v>-34.603336</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>VCR-B</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14951,7 +14951,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 218</t>
+          <t xml:space="preserve">CAMARGO 481 </t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -14986,12 +14986,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.440278</v>
+        <v>-58.439755</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.603336</v>
+        <v>-34.60075</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15037,7 +15037,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>900009601610</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMARGO 481 </t>
+          <t>THAMES 1109</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15094,24 +15094,24 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.439755</v>
+        <v>-58.436188</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.60075</v>
+        <v>-34.59138</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15123,7 +15123,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>900009601610</t>
+          <t>S00194756</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>THAMES 1109</t>
+          <t>CALIFORNIA 2861</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15180,14 +15180,14 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.436188</v>
+        <v>-58.38692</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.59138</v>
+        <v>-34.649509</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15209,22 +15209,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S00194756</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CALIFORNIA 2861</t>
+          <t xml:space="preserve">ESPINOSA 98 </t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15266,14 +15266,14 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.38692</v>
+        <v>-58.446457</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.649509</v>
+        <v>-34.621398</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15295,7 +15295,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15305,12 +15305,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOSA 98 </t>
+          <t>RODRIGUEZ PEÑA 1650</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15352,14 +15352,14 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.446457</v>
+        <v>-58.389533</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.621398</v>
+        <v>-34.591306</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15381,22 +15381,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEÑA 1650</t>
+          <t>OLAVARRIA 861</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15438,14 +15438,14 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>-58.389533</v>
+        <v>-58.365014</v>
       </c>
       <c r="N175" t="n">
-        <v>-34.591306</v>
+        <v>-34.638541</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>CON-E</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15467,22 +15467,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>OLAVARRIA 861</t>
+          <t>AV LA PLATA 881</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -15497,12 +15497,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15524,14 +15524,14 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>-58.365014</v>
+        <v>-58.42712</v>
       </c>
       <c r="N176" t="n">
-        <v>-34.638541</v>
+        <v>-34.625871</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -15541,96 +15541,10 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>CON-E</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>M881</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>4/1/2026</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>AV LA PLATA 881</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>813046342</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L177" t="n">
-        <v>1</v>
-      </c>
-      <c r="M177" t="n">
-        <v>-58.42712</v>
-      </c>
-      <c r="N177" t="n">
-        <v>-34.625871</v>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>ALM-A</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R176"/>
+  <dimension ref="A1:R175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6265,7 +6265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S01123014</t>
+          <t>01110546</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PADILLA 1255</t>
+          <t>ALSINA, ADOLFO 2490</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>810804370</t>
+          <t>810804369</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>columna inclinada  base corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6322,24 +6322,24 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.447651</v>
+        <v>-58.401266</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.595324</v>
+        <v>-34.612194</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>VCR-?</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6351,7 +6351,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>01110546</t>
+          <t>S00982328</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2490</t>
+          <t>BROWN, ALTE. AV. 1201</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>810804369</t>
+          <t>810804366</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>columna inclinada  base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6408,14 +6408,14 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.401266</v>
+        <v>-58.358915</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.612194</v>
+        <v>-34.635472</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S00982328</t>
+          <t>S01018458</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BROWN, ALTE. AV. 1201</t>
+          <t>AGUIRRE 290</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>810804366</t>
+          <t>810804344</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6494,14 +6494,14 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.358915</v>
+        <v>-58.434002</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.635472</v>
+        <v>-34.599505</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6523,7 +6523,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S01018458</t>
+          <t>S01098187</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AGUIRRE 290</t>
+          <t>SERRANO 432</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>810804344</t>
+          <t>810804334</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6580,24 +6580,24 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.434002</v>
+        <v>-58.443352</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.599505</v>
+        <v>-34.596905</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6609,17 +6609,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S01098187</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SERRANO 432</t>
+          <t>Malabia 510</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>810804334</t>
+          <t xml:space="preserve">01565659 </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6666,24 +6666,24 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.443352</v>
+        <v>-58.43835</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.596905</v>
+        <v>-34.598031</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6695,7 +6695,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>S01145254</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malabia 510</t>
+          <t>ARAOZ DE LAMADRID, GREGORIO, GRAL. 591</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">01565659 </t>
+          <t>810820746</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6752,14 +6752,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.43835</v>
+        <v>-58.360658</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.598031</v>
+        <v>-34.638004</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CON-E</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6781,7 +6781,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S01145254</t>
+          <t>S01183783</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ARAOZ DE LAMADRID, GREGORIO, GRAL. 591</t>
+          <t xml:space="preserve"> 24 DE NOVIEMBRE 2133 </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>810820746</t>
+          <t>810820614</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6838,10 +6838,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.360658</v>
+        <v>-58.409282</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.638004</v>
+        <v>-34.635897</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>CON-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6867,7 +6867,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S01183783</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 24 DE NOVIEMBRE 2133 </t>
+          <t>UGARTECHE 3079</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>810820614</t>
+          <t xml:space="preserve">01638326 </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6924,14 +6924,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.409282</v>
+        <v>-58.411934</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.635897</v>
+        <v>-34.580653</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,7 +6953,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UGARTECHE 3079</t>
+          <t>SAN LUIS 2488</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638326 </t>
+          <t>810820592</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
+          <t>base muy picada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7010,14 +7010,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.411934</v>
+        <v>-58.402179</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.580653</v>
+        <v>-34.600152</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,22 +7039,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SAN LUIS 2488</t>
+          <t>Paraguay 4301</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>810820592</t>
+          <t>810853935</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>base muy picada</t>
+          <t>Cambio de columna propia corroida en base</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7096,14 +7096,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.402179</v>
+        <v>-58.422434</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.600152</v>
+        <v>-34.585978</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7125,22 +7125,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>S01181254</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Paraguay 4301</t>
+          <t>THAMES 677</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>810853935</t>
+          <t xml:space="preserve">01638116 </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cambio de columna propia corroida en base</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7182,10 +7182,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.422434</v>
+        <v>-58.441083</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.585978</v>
+        <v>-34.594165</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7211,7 +7211,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S01181254</t>
+          <t>S01199701</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>THAMES 677</t>
+          <t>LAVALLEJA 726</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638116 </t>
+          <t>01635621</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7268,10 +7268,10 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.441083</v>
+        <v>-58.431973</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.594165</v>
+        <v>-34.599274</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01199701</t>
+          <t>S00727663</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LAVALLEJA 726</t>
+          <t>NECOCHEA 721</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01635621</t>
+          <t>810862843</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7354,14 +7354,14 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.431973</v>
+        <v>-58.361052</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.599274</v>
+        <v>-34.630445</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7383,22 +7383,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S00727663</t>
+          <t>S00785128</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NECOCHEA 721</t>
+          <t>Paraguay 5055</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>810862843</t>
+          <t>810877555</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7440,14 +7440,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.361052</v>
+        <v>-58.429394</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.630445</v>
+        <v>-34.580587</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7469,7 +7469,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S00785128</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Paraguay 5055</t>
+          <t>VILLAFAÑE, WENCESLAO 1655</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>810877555</t>
+          <t>810877541</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7526,14 +7526,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.429394</v>
+        <v>-58.374586</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.580587</v>
+        <v>-34.635118</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7543,19 +7543,19 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>S00566892</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VILLAFAÑE, WENCESLAO 1655</t>
+          <t xml:space="preserve">SANTA FE AV. 3711 </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>810877541</t>
+          <t>810877633</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7612,14 +7612,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.374586</v>
+        <v>-58.416063</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.635118</v>
+        <v>-34.584975</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7629,34 +7629,34 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S00566892</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE AV. 3711 </t>
+          <t>URUGUAY 1070</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>810877633</t>
+          <t>810984538</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7698,14 +7698,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.416063</v>
+        <v>-58.387161</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.584975</v>
+        <v>-34.596255</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7727,22 +7727,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>900008882010</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>URUGUAY 1070</t>
+          <t xml:space="preserve"> PAVON AV. 3707 </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>810984538</t>
+          <t>810984598</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7784,14 +7784,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.387161</v>
+        <v>-58.416724</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.596255</v>
+        <v>-34.630181</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7813,17 +7813,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>900008882010</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAVON AV. 3707 </t>
+          <t>Querandíes 4220</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>810984598</t>
+          <t>810984700</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>correr, obstaculiza acceso a garage</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7863,21 +7863,21 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L87" t="n">
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.416724</v>
+        <v>-58.426168</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.630181</v>
+        <v>-34.611095</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7899,22 +7899,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Querandíes 4220</t>
+          <t>AGUERO 2038</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7929,17 +7929,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>810984700</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>correr, obstaculiza acceso a garage</t>
+          <t>Traspasar red a columna nueva y retirar la vieja</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7949,21 +7949,21 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.426168</v>
+        <v>-58.402647</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.611095</v>
+        <v>-34.588274</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>AGU-G</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>S01200313</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AGUERO 2038</t>
+          <t>GANDHI, MAHATMA 311</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8020,17 +8020,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Traspasar red a columna nueva y retirar la vieja</t>
+          <t>corroida colocar columna pedir traspaso</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8042,24 +8042,24 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.402647</v>
+        <v>-58.440931</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.588274</v>
+        <v>-34.603655</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>AGU-G</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8071,22 +8071,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S01200313</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 311</t>
+          <t>Riglos 957</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811198753</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>corroida colocar columna pedir traspaso</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8128,24 +8128,24 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.440931</v>
+        <v>-58.435265</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.603655</v>
+        <v>-34.630164</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8157,7 +8157,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Riglos 957</t>
+          <t>ABDALA, GERMAN 115</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811198753</t>
+          <t>811198752</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8207,21 +8207,21 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.435265</v>
+        <v>-58.36748</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.630164</v>
+        <v>-34.629504</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CON-D</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ABDALA, GERMAN 115</t>
+          <t xml:space="preserve"> GARCIA, MARTIN AV. 464 </t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811198752</t>
+          <t>811198750</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8293,17 +8293,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.36748</v>
+        <v>-58.3713</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.629504</v>
+        <v>-34.630267</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8317,19 +8317,19 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>CON-D</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GARCIA, MARTIN AV. 464 </t>
+          <t>French 2377</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8359,12 +8359,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811198750</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8386,14 +8386,14 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.3713</v>
+        <v>-58.398947</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.630267</v>
+        <v>-34.590946</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8403,19 +8403,19 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>French 2377</t>
+          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8472,14 +8472,14 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.398947</v>
+        <v>-58.409318</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.590946</v>
+        <v>-34.619842</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8489,19 +8489,19 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>poste inclinado base quebrada</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8551,21 +8551,21 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.409318</v>
+        <v>-58.403895</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.619842</v>
+        <v>-34.575559</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8587,7 +8587,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
+          <t>GURRUCHAGA 2473</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>poste inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8637,21 +8637,21 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.403895</v>
+        <v>-58.420304</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.575559</v>
+        <v>-34.582607</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>VCR-L</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GURRUCHAGA 2473</t>
+          <t xml:space="preserve">HUMAHUACA 4298 </t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t>811198696</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8730,14 +8730,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.420304</v>
+        <v>-58.425302</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.582607</v>
+        <v>-34.601502</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>VCR-L</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8759,22 +8759,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>S01217715</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAHUACA 4298 </t>
+          <t xml:space="preserve">NECOCHEA 535 </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>811198691</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8816,14 +8816,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.425302</v>
+        <v>-58.362989</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.601502</v>
+        <v>-34.629167</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8845,7 +8845,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S01217715</t>
+          <t>S01159828</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NECOCHEA 535 </t>
+          <t xml:space="preserve"> THAMES 2041</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811198691</t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8902,14 +8902,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.362989</v>
+        <v>-58.426667</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.629167</v>
+        <v>-34.585153</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8931,7 +8931,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S01159828</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> THAMES 2041</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8988,14 +8988,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.426667</v>
+        <v>-58.422033</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.585153</v>
+        <v>-34.598976</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>S01204493</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t>VILLAFAÑE, WENCESLAO 1697</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>811198665</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto inclinada corroida</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9067,21 +9067,21 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.422033</v>
+        <v>-58.374994</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.598976</v>
+        <v>-34.635173</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9091,34 +9091,34 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S01204493</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VILLAFAÑE, WENCESLAO 1697</t>
+          <t>GANDHI, MAHATMA 218</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811198665</t>
+          <t>811238734</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>tensor roto inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9153,43 +9153,43 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.374994</v>
+        <v>-58.440278</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.635173</v>
+        <v>-34.603336</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 218</t>
+          <t xml:space="preserve">GAONA AV. 1360 </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811238734</t>
+          <t>811238719</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9246,24 +9246,24 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.440278</v>
+        <v>-58.448401</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.603336</v>
+        <v>-34.608681</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>NRA-B</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9275,7 +9275,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAONA AV. 1360 </t>
+          <t xml:space="preserve">FERRARI 490 </t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811238719</t>
+          <t>811238711</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9325,31 +9325,31 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.448401</v>
+        <v>-58.441842</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.608681</v>
+        <v>-34.605759</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>NRA-B</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERRARI 490 </t>
+          <t>SOLER 4509</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811238711</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9406,36 +9406,36 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.441842</v>
+        <v>-58.42336</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.605759</v>
+        <v>-34.588111</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SOLER 4509</t>
+          <t>DIAZ, CNEL. AV. 2512</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9492,26 +9492,26 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.42336</v>
+        <v>-58.406111</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.588111</v>
+        <v>-34.58316</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9533,7 +9533,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2512</t>
+          <t>ESPINOSA 1099</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t>811238674</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9590,14 +9590,14 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.406111</v>
+        <v>-58.452139</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.58316</v>
+        <v>-34.610772</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>NRA-H</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9619,22 +9619,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ESPINOSA 1099</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>811238674</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9669,21 +9669,21 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L108" t="n">
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.452139</v>
+        <v>-58.416901</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.610772</v>
+        <v>-34.604236</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>NRA-H</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9705,22 +9705,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>ARANGUREN, JUAN F., DR. 462</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>811299459</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9762,10 +9762,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.416901</v>
+        <v>-58.437431</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.604236</v>
+        <v>-34.612405</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>ALM-I</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9791,22 +9791,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ARANGUREN, JUAN F., DR. 462</t>
+          <t>REPETTO, NICOLAS, DR. 1608</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811299459</t>
+          <t>811453857</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9848,24 +9848,24 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.437431</v>
+        <v>-58.452794</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.612405</v>
+        <v>-34.604603</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>ALM-I</t>
+          <t>NRA-G</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9877,7 +9877,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>REPETTO, NICOLAS, DR. 1608</t>
+          <t>LAVALLEJA 152</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811453857</t>
+          <t>811453799</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9934,10 +9934,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.452794</v>
+        <v>-58.437275</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.604603</v>
+        <v>-34.602678</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>NRA-G</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9963,22 +9963,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LAVALLEJA 152</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>811453799</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10020,24 +10020,24 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.437275</v>
+        <v>-58.412204</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.602678</v>
+        <v>-34.628609</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10049,22 +10049,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>S01248250</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>ALVAREZ, JULIAN 564</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10079,12 +10079,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t>811454078</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10106,14 +10106,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.412204</v>
+        <v>-58.434547</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.628609</v>
+        <v>-34.599587</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10135,7 +10135,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S01248250</t>
+          <t>S01248679</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 564</t>
+          <t>LOYOLA 163</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>811454078</t>
+          <t>811454048</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10192,10 +10192,10 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.434547</v>
+        <v>-58.432674</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.599587</v>
+        <v>-34.598923</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S01248679</t>
+          <t>S01248701</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LOYOLA 163</t>
+          <t>LOYOLA 189</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>811454048</t>
+          <t>811454013</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10278,10 +10278,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.432674</v>
+        <v>-58.432825</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.598923</v>
+        <v>-34.598761</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10307,17 +10307,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S01248701</t>
+          <t>S01248264</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LOYOLA 189</t>
+          <t>ALVAREZ, JULIAN 516</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>811454013</t>
+          <t>811454392</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10364,10 +10364,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.432825</v>
+        <v>-58.434944</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.598761</v>
+        <v>-34.599841</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10393,22 +10393,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S01248264</t>
+          <t>S01290507</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 516</t>
+          <t>CABELLO 3472</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>811454392</t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.434944</v>
+        <v>-58.409438</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.599841</v>
+        <v>-34.58118</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10479,7 +10479,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S01290507</t>
+          <t>S01339459</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CABELLO 3472</t>
+          <t>RODRIGUEZ, MARTIN 710</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>811453958</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10529,21 +10529,21 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.409438</v>
+        <v>-58.361268</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.58118</v>
+        <v>-34.634378</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10565,22 +10565,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S01339459</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>RODRIGUEZ, MARTIN 710</t>
+          <t>CAMARGO 111</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10595,12 +10595,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>811453958</t>
+          <t>811454377</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10622,24 +10622,24 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.361268</v>
+        <v>-58.437024</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.634378</v>
+        <v>-34.603753</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10651,7 +10651,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CAMARGO 111</t>
+          <t>DIAZ, CNEL. AV. 2599</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>811454377</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10708,24 +10708,24 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.437024</v>
+        <v>-58.405559</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.603753</v>
+        <v>-34.582478</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10737,22 +10737,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2599</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -10794,14 +10794,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.405559</v>
+        <v>-58.406807</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.582478</v>
+        <v>-34.612902</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10823,7 +10823,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t>ACOYTE 908</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811454448</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10880,10 +10880,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.406807</v>
+        <v>-58.440177</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.612902</v>
+        <v>-34.607612</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ACOYTE 908</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>811454448</t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10966,10 +10966,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.440177</v>
+        <v>-58.429481</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.607612</v>
+        <v>-34.608647</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10995,7 +10995,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>FRIAS, EUSTOQUIO, TTE. GENERAL 378</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>811454396</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11052,24 +11052,24 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.429481</v>
+        <v>-58.433871</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.608647</v>
+        <v>-34.601836</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11081,22 +11081,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FRIAS, EUSTOQUIO, TTE. GENERAL 378</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>811454396</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11138,24 +11138,24 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.433871</v>
+        <v>-58.404243</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.601836</v>
+        <v>-34.612859</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t>SAN JOSE DE CALASANZ 266</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>811497993</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -11224,14 +11224,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.404243</v>
+        <v>-58.437998</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.612859</v>
+        <v>-34.62221</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>PCH-K</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11253,22 +11253,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SAN JOSE DE CALASANZ 266</t>
+          <t>INCLAN 2402</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>811497993</t>
+          <t>811498043</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>basee corroida</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11310,14 +11310,14 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.437998</v>
+        <v>-58.398304</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.62221</v>
+        <v>-34.629576</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PCH-K</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11339,7 +11339,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11349,12 +11349,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>INCLAN 2402</t>
+          <t>SAN JOSE 807</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11369,12 +11369,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>811498043</t>
+          <t>811498022</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>basee corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11396,10 +11396,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.398304</v>
+        <v>-58.385925</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.629576</v>
+        <v>-34.618047</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11425,22 +11425,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SAN JOSE 807</t>
+          <t xml:space="preserve">GOMEZ, JUAN CARLOS 253 </t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>811498022</t>
+          <t>811626778</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11482,10 +11482,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.385925</v>
+        <v>-58.391109</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.618047</v>
+        <v>-34.637207</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>CON-K</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11511,17 +11511,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ, JUAN CARLOS 253 </t>
+          <t>MONTES DE OCA, MANUEL AV. 499</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>811626778</t>
+          <t>811626787</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11568,10 +11568,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.391109</v>
+        <v>-58.375589</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.637207</v>
+        <v>-34.634175</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CON-K</t>
+          <t>RTT-?</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11597,7 +11597,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 499</t>
+          <t>AGUIRRE 640</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>811626787</t>
+          <t>811626786</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corrroida</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11654,14 +11654,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.375589</v>
+        <v>-58.436805</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.634175</v>
+        <v>-34.596512</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>RTT-?</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11683,17 +11683,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>S00005738</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AGUIRRE 640</t>
+          <t xml:space="preserve"> JUFRE 962</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11713,12 +11713,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>811626786</t>
+          <t>811626974</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>corrroida</t>
+          <t>incliunada</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11740,10 +11740,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.436805</v>
+        <v>-58.436718</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.596512</v>
+        <v>-34.591089</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11769,22 +11769,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S00005738</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUFRE 962</t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>811626974</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>incliunada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11826,14 +11826,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.436718</v>
+        <v>-58.4048</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.591089</v>
+        <v>-34.629021</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11855,17 +11855,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11912,14 +11912,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.4048</v>
+        <v>-58.399059</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.629021</v>
+        <v>-34.608499</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11941,7 +11941,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>S01443954</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t xml:space="preserve"> PALOS 432</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>811626849</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11998,14 +11998,14 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.399059</v>
+        <v>-58.362579</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.608499</v>
+        <v>-34.635096</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12027,7 +12027,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S01443954</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PALOS 432</t>
+          <t>JUFRE 77</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>811626849</t>
+          <t>811626833</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12084,14 +12084,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.362579</v>
+        <v>-58.429659</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.635096</v>
+        <v>-34.598452</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JUFRE 77</t>
+          <t>COCHABAMBA 1740</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>811626833</t>
+          <t>811626824</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12170,14 +12170,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.429659</v>
+        <v>-58.390308</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.598452</v>
+        <v>-34.62403</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12199,7 +12199,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>COCHABAMBA 1740</t>
+          <t xml:space="preserve">SAENZ PEÑA, LUIS, PRES. 895 </t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>811626824</t>
+          <t>811626819</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12256,10 +12256,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.390308</v>
+        <v>-58.387479</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.62403</v>
+        <v>-34.61865</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12285,22 +12285,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAENZ PEÑA, LUIS, PRES. 895 </t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12315,12 +12315,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>811626819</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12342,10 +12342,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.387479</v>
+        <v>-58.404766</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.61865</v>
+        <v>-34.620521</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12371,17 +12371,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12428,10 +12428,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.404766</v>
+        <v>-58.393145</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.620521</v>
+        <v>-34.621778</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12457,7 +12457,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>RIGLOS 553</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -12514,14 +12514,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.393145</v>
+        <v>-58.436277</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.621778</v>
+        <v>-34.625202</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>PCH-B</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12543,22 +12543,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>RIGLOS 553</t>
+          <t>Costa Rica 5741</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12573,12 +12573,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -12600,14 +12600,14 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.436277</v>
+        <v>-58.436073</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.625202</v>
+        <v>-34.581506</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>PCH-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12629,7 +12629,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Costa Rica 5741</t>
+          <t>CALLAO AV. 2014</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12659,12 +12659,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12686,14 +12686,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.436073</v>
+        <v>-58.386954</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.581506</v>
+        <v>-34.587337</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12715,7 +12715,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CALLAO AV. 2014</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -12772,14 +12772,14 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.386954</v>
+        <v>-58.400243</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.587337</v>
+        <v>-34.610864</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12801,7 +12801,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12831,12 +12831,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12858,10 +12858,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.400243</v>
+        <v>-58.399124</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.610864</v>
+        <v>-34.610705</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>S00066646</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12897,12 +12897,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12917,12 +12917,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12937,21 +12937,21 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.399124</v>
+        <v>-58.408259</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.610705</v>
+        <v>-34.580266</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12973,22 +12973,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S00066646</t>
+          <t>S00072053</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
+          <t>HERRERA 197</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13003,12 +13003,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>811627116</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13023,21 +13023,21 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.408259</v>
+        <v>-58.37946</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.580266</v>
+        <v>-34.632625</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13059,7 +13059,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S00072053</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13069,12 +13069,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HERRERA 197</t>
+          <t>FRANKLIN 572</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>811627116</t>
+          <t>811627115</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -13109,21 +13109,21 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L148" t="n">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.37946</v>
+        <v>-58.439651</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.632625</v>
+        <v>-34.607769</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13145,22 +13145,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FRANKLIN 572</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13175,12 +13175,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>811627115</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13195,17 +13195,17 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.439651</v>
+        <v>-58.413979</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.607769</v>
+        <v>-34.607475</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13281,21 +13281,21 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L150" t="n">
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.413979</v>
+        <v>-58.395668</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.607475</v>
+        <v>-34.621926</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13317,22 +13317,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>S00073317</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/11/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t xml:space="preserve"> ESPINOSA 82</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>812440077</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13374,14 +13374,14 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.395668</v>
+        <v>-58.446397</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.621926</v>
+        <v>-34.621499</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13403,22 +13403,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S00073317</t>
+          <t>S00152251</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2/11/2026</t>
+          <t>2/13/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESPINOSA 82</t>
+          <t>PALOS 560</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>812440077</t>
+          <t>812440079</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13460,14 +13460,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.446397</v>
+        <v>-58.361933</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.621499</v>
+        <v>-34.636158</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13489,22 +13489,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S00152251</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2/13/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PALOS 560</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>812440079</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13546,10 +13546,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.361933</v>
+        <v>-58.400774</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.636158</v>
+        <v>-34.621503</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13575,17 +13575,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -13632,14 +13632,14 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.400774</v>
+        <v>-58.404576</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.621503</v>
+        <v>-34.607569</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13661,7 +13661,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13718,10 +13718,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.404576</v>
+        <v>-58.395384</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.607569</v>
+        <v>-34.600962</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13735,34 +13735,34 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t>SINCLAIR 3106</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13777,12 +13777,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13804,14 +13804,14 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.395384</v>
+        <v>-58.422892</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.600962</v>
+        <v>-34.573802</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13821,19 +13821,19 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13843,12 +13843,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SINCLAIR 3106</t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13863,12 +13863,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13890,14 +13890,14 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.422892</v>
+        <v>-58.41859</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.573802</v>
+        <v>-34.624508</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13919,7 +13919,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>S01061920</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t xml:space="preserve">BROWN, ALTE. AV. 1184 </t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13949,12 +13949,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812440267</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13976,14 +13976,14 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.41859</v>
+        <v>-58.358913</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.624508</v>
+        <v>-34.635093</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14005,7 +14005,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S01061920</t>
+          <t>S01064368</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14015,12 +14015,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">BROWN, ALTE. AV. 1184 </t>
+          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14035,12 +14035,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>812440267</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14062,14 +14062,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.358913</v>
+        <v>-58.426552</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.635093</v>
+        <v>-34.592076</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14091,22 +14091,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S01064368</t>
+          <t>S01447672</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/24/2026</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
+          <t xml:space="preserve">BRANDSEN 485 </t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14121,12 +14121,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>812440635</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14148,14 +14148,14 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.426552</v>
+        <v>-58.360611</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.592076</v>
+        <v>-34.63495</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>CON-G</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14177,22 +14177,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S01447672</t>
+          <t>S01200005</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2/24/2026</t>
+          <t>2/25/2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDSEN 485 </t>
+          <t xml:space="preserve"> ARAOZ 390</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>812440635</t>
+          <t>812503577</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -14234,14 +14234,14 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.360611</v>
+        <v>-58.437124</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.63495</v>
+        <v>-34.599891</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>CON-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14263,22 +14263,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S01200005</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2/25/2026</t>
+          <t>2/26/2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARAOZ 390</t>
+          <t>SANTO DOMINGO 3930</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>812503577</t>
+          <t>812503584</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14320,14 +14320,14 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.437124</v>
+        <v>-58.405248</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.599891</v>
+        <v>-34.655112</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14349,22 +14349,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO 3930</t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>812503584</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14406,14 +14406,14 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.405248</v>
+        <v>-58.416187</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.655112</v>
+        <v>-34.600138</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14435,22 +14435,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00115187</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>ESTADO PLURINACIONAL DE BOLIVIA 324</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14465,12 +14465,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>812503658</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14492,14 +14492,14 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.416187</v>
+        <v>-58.46673</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.600138</v>
+        <v>-34.627032</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14521,22 +14521,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S00115187</t>
+          <t>S01406817</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>3/3/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ESTADO PLURINACIONAL DE BOLIVIA 324</t>
+          <t>CAMPOS, LUIS M. AV. 155</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>812503658</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -14571,21 +14571,21 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L165" t="n">
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.46673</v>
+        <v>-58.431638</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.627032</v>
+        <v>-34.574344</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14607,22 +14607,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S01406817</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3/3/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 155</t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14657,21 +14657,21 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L166" t="n">
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.431638</v>
+        <v>-58.431406</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.574344</v>
+        <v>-34.605009</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14693,22 +14693,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>S00165389</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t>HONDURAS AV. 3708</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14738,26 +14738,26 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.431406</v>
+        <v>-58.414717</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.605009</v>
+        <v>-34.594123</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>VCR-B</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14779,22 +14779,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S00165389</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>HONDURAS AV. 3708</t>
+          <t>GANDHI, MAHATMA 218</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14814,46 +14814,46 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L168" t="n">
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.414717</v>
+        <v>-58.440278</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.594123</v>
+        <v>-34.603336</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>VCR-B</t>
+          <t>ALM-N</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14865,7 +14865,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GANDHI, MAHATMA 218</t>
+          <t xml:space="preserve">CAMARGO 481 </t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -14900,12 +14900,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -14915,17 +14915,17 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L169" t="n">
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.440278</v>
+        <v>-58.439755</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.603336</v>
+        <v>-34.60075</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>ALM-N</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14951,7 +14951,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>900009601610</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMARGO 481 </t>
+          <t>THAMES 1109</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -15008,24 +15008,24 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.439755</v>
+        <v>-58.436188</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.60075</v>
+        <v>-34.59138</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15037,7 +15037,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>900009601610</t>
+          <t>S00194756</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15047,12 +15047,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>THAMES 1109</t>
+          <t>CALIFORNIA 2861</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15094,14 +15094,14 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.436188</v>
+        <v>-58.38692</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.59138</v>
+        <v>-34.649509</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15123,22 +15123,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S00194756</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CALIFORNIA 2861</t>
+          <t xml:space="preserve">ESPINOSA 98 </t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15180,14 +15180,14 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.38692</v>
+        <v>-58.446457</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.649509</v>
+        <v>-34.621398</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15209,7 +15209,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOSA 98 </t>
+          <t>RODRIGUEZ PEÑA 1650</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15266,14 +15266,14 @@
         <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>-58.446457</v>
+        <v>-58.389533</v>
       </c>
       <c r="N173" t="n">
-        <v>-34.621398</v>
+        <v>-34.591306</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15295,22 +15295,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEÑA 1650</t>
+          <t>OLAVARRIA 861</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15352,14 +15352,14 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>-58.389533</v>
+        <v>-58.365014</v>
       </c>
       <c r="N174" t="n">
-        <v>-34.591306</v>
+        <v>-34.638541</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>CON-E</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15381,22 +15381,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>OLAVARRIA 861</t>
+          <t>AV LA PLATA 881</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15438,14 +15438,14 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>-58.365014</v>
+        <v>-58.42712</v>
       </c>
       <c r="N175" t="n">
-        <v>-34.638541</v>
+        <v>-34.625871</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -15455,96 +15455,10 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>CON-E</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>M881</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>4/1/2026</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>AV LA PLATA 881</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>813046342</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L176" t="n">
-        <v>1</v>
-      </c>
-      <c r="M176" t="n">
-        <v>-58.42712</v>
-      </c>
-      <c r="N176" t="n">
-        <v>-34.625871</v>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>ALM-A</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AV LA PLATA 881</t>
+          <t>AV LA PLATA 2288</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -15008,10 +15008,10 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.42712</v>
+        <v>-58.423203</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.625871</v>
+        <v>-34.640909</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R168"/>
+  <dimension ref="A1:R171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10841,22 +10841,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>LR00001</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>BILLINGHURST 1796</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>813350523</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10898,14 +10898,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.428528</v>
+        <v>-58.409695</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.589872</v>
+        <v>-34.589662</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-D</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10927,7 +10927,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>PJ00040</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>HONDURAS 4822</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>813350536</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10984,10 +10984,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.413378</v>
+        <v>-58.428528</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.587254</v>
+        <v>-34.589872</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11013,7 +11013,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>AF00001</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DORREGO AV.2752</t>
+          <t>SALGUERO, JERONIMO 1995</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>813304889</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11070,10 +11070,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.43266</v>
+        <v>-58.413378</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.574202</v>
+        <v>-34.587254</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11099,22 +11099,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S0000223</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ARENALES 3660</t>
+          <t>CHARCAS 3250</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>813304917</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11156,14 +11156,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.413732</v>
+        <v>-58.41175</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.585415</v>
+        <v>-34.592173</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11185,17 +11185,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4/23/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AV DORREGO 3900</t>
+          <t>DORREGO AV.2752</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>813352568</t>
+          <t>813305004</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11235,17 +11235,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L127" t="n">
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.418801</v>
+        <v>-58.43266</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.564182</v>
+        <v>-34.574202</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11271,22 +11271,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>S00419298</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 2552</t>
+          <t>AUSTRIA 2354</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>813352603</t>
+          <t>813350615</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11328,14 +11328,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.413555</v>
+        <v>-58.401523</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.585955</v>
+        <v>-34.586182</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11357,17 +11357,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>S0000223</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BULNES 2550</t>
+          <t>ARENALES 3660</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11387,17 +11387,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>813631416</t>
+          <t>813352547</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11414,10 +11414,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.407013</v>
+        <v>-58.413732</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.582645</v>
+        <v>-34.585415</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11443,17 +11443,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>4/23/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 2030</t>
+          <t>AV DORREGO 3900</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11473,17 +11473,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>813631417</t>
+          <t>813352568</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -11493,21 +11493,21 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L130" t="n">
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.401882</v>
+        <v>-58.418801</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.582006</v>
+        <v>-34.564182</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11529,17 +11529,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CASTEX 3439</t>
+          <t>ALVAREZ, JULIAN 2552</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>813631425</t>
+          <t>813352603</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11586,10 +11586,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.406414</v>
+        <v>-58.413555</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.577519</v>
+        <v>-34.585955</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11615,7 +11615,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2338</t>
+          <t>BULNES 2550</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>813631432</t>
+          <t>813631416</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -11672,24 +11672,24 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.444112</v>
+        <v>-58.407013</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.569261</v>
+        <v>-34.582645</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11701,7 +11701,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>DEL LIBERTADOR AV. 2030</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>813631446</t>
+          <t>813631417</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11758,14 +11758,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.438595</v>
+        <v>-58.401882</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.565168</v>
+        <v>-34.582006</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11787,7 +11787,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t>CASTEX 3439</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11817,17 +11817,17 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>813631449</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11844,10 +11844,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.437217</v>
+        <v>-58.406414</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.567174</v>
+        <v>-34.577519</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11873,7 +11873,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>LACROZE, FEDERICO AV. 2338</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11903,17 +11903,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>813631451</t>
+          <t>813631432</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11930,19 +11930,19 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.44018</v>
+        <v>-58.444112</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.565612</v>
+        <v>-34.569261</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -11959,7 +11959,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>813631452</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -12016,24 +12016,24 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.441718</v>
+        <v>-58.438595</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.566411</v>
+        <v>-34.565168</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12045,7 +12045,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CAPDEVILA 3245</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12075,17 +12075,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>813631453</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -12102,24 +12102,24 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.492198</v>
+        <v>-58.437217</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.567241</v>
+        <v>-34.567174</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12131,17 +12131,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12159,15 +12159,19 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>813631451</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -12184,10 +12188,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.440439</v>
+        <v>-58.44018</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.575416</v>
+        <v>-34.565612</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12201,7 +12205,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12213,17 +12217,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12241,15 +12245,19 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>813631452</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -12266,24 +12274,24 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.438274</v>
+        <v>-58.441718</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.564049</v>
+        <v>-34.566411</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12295,22 +12303,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t>9086</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>CAPDEVILA 3245</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12323,7 +12331,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>813631453</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12348,24 +12360,24 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.434721</v>
+        <v>-58.492198</v>
       </c>
       <c r="N140" t="n">
         <v>-34.567241</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12377,22 +12389,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12405,7 +12417,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>813631921</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12430,14 +12446,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.435738</v>
+        <v>-58.402534</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.564606</v>
+        <v>-34.593133</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12447,7 +12463,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12459,7 +12475,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12469,12 +12485,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12490,7 +12506,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12512,14 +12528,14 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.435011</v>
+        <v>-58.385947</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.56566</v>
+        <v>-34.588156</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12529,7 +12545,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12541,7 +12557,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12551,7 +12567,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12572,17 +12588,17 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12594,10 +12610,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.430774</v>
+        <v>-58.440439</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.568179</v>
+        <v>-34.575416</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12611,7 +12627,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12623,7 +12639,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12633,7 +12649,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12676,10 +12692,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.436255</v>
+        <v>-58.438274</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.567733</v>
+        <v>-34.564049</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12705,7 +12721,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12715,7 +12731,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12758,10 +12774,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.443403</v>
+        <v>-58.434721</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.575666</v>
+        <v>-34.567241</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12775,7 +12791,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12787,7 +12803,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12797,7 +12813,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12840,10 +12856,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.428639</v>
+        <v>-58.435738</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.59039</v>
+        <v>-34.564606</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12857,7 +12873,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12869,7 +12885,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12879,7 +12895,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12900,7 +12916,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -12910,7 +12926,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -12922,10 +12938,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.422183</v>
+        <v>-58.435011</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.576849</v>
+        <v>-34.56566</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -12939,7 +12955,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -12951,7 +12967,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12961,7 +12977,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12992,7 +13008,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -13004,10 +13020,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.425803</v>
+        <v>-58.430774</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.588513</v>
+        <v>-34.568179</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13021,7 +13037,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13033,17 +13049,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13064,17 +13080,17 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -13086,10 +13102,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.424388</v>
+        <v>-58.436255</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.59632</v>
+        <v>-34.567733</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13103,7 +13119,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13115,17 +13131,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13168,10 +13184,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.427895</v>
+        <v>-58.443403</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.583677</v>
+        <v>-34.575666</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13185,7 +13201,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13197,17 +13213,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13250,10 +13266,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.424553</v>
+        <v>-58.428639</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.59709</v>
+        <v>-34.59039</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13267,7 +13283,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13279,22 +13295,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13310,12 +13326,12 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -13332,14 +13348,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.440973</v>
+        <v>-58.404726</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.572415</v>
+        <v>-34.596069</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13349,7 +13365,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13361,17 +13377,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13402,7 +13418,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -13414,10 +13430,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.43218</v>
+        <v>-58.422183</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.578546</v>
+        <v>-34.576849</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13431,7 +13447,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13443,17 +13459,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13496,10 +13512,10 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.436737</v>
+        <v>-58.425803</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.58597</v>
+        <v>-34.588513</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13513,7 +13529,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13525,7 +13541,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13535,7 +13551,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13556,17 +13572,17 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -13578,10 +13594,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.413584</v>
+        <v>-58.424388</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.58551</v>
+        <v>-34.59632</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13595,7 +13611,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13607,7 +13623,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13617,7 +13633,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13638,17 +13654,17 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -13660,10 +13676,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.415912</v>
+        <v>-58.427895</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.588977</v>
+        <v>-34.583677</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13677,7 +13693,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13689,7 +13705,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">9924 </t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13699,7 +13715,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t>CORDOBA AV. 4089</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13720,12 +13736,12 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13742,10 +13758,10 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.413885</v>
+        <v>-58.424553</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.586628</v>
+        <v>-34.59709</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13759,7 +13775,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13771,7 +13787,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080 </t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13781,7 +13797,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>THAMES 549</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -13824,10 +13840,10 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.442534</v>
+        <v>-58.440973</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.59499</v>
+        <v>-34.572415</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13841,7 +13857,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13853,7 +13869,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13863,12 +13879,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13894,7 +13910,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -13906,10 +13922,10 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.404652</v>
+        <v>-58.40382</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.58263</v>
+        <v>-34.594385</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -13923,7 +13939,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -13935,7 +13951,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13945,7 +13961,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -13988,10 +14004,10 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.433857</v>
+        <v>-58.43218</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.57424</v>
+        <v>-34.578546</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -14005,7 +14021,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14017,7 +14033,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102 </t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14027,7 +14043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ELCANO AV. 3950</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -14048,7 +14064,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14070,24 +14086,24 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.460457</v>
+        <v>-58.436737</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.582381</v>
+        <v>-34.58597</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14099,7 +14115,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14109,7 +14125,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -14130,12 +14146,12 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -14152,10 +14168,10 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.432319</v>
+        <v>-58.413584</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.574385</v>
+        <v>-34.58551</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -14169,7 +14185,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14181,7 +14197,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14191,7 +14207,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -14212,17 +14228,17 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -14234,10 +14250,10 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.416882</v>
+        <v>-58.415912</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.562655</v>
+        <v>-34.588977</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -14251,7 +14267,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14263,7 +14279,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14273,7 +14289,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -14294,17 +14310,17 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -14316,10 +14332,10 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.419652</v>
+        <v>-58.413885</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.588271</v>
+        <v>-34.586628</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -14333,7 +14349,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14345,22 +14361,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t xml:space="preserve">10080 </t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5/26/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV. 4512</t>
+          <t>THAMES 549</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14373,19 +14389,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>813649670</t>
-        </is>
-      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>REALIZAR DESPLAZAMIENTO TRAMBUS</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -14402,14 +14414,14 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.429509</v>
+        <v>-58.442534</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.615307</v>
+        <v>-34.59499</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14419,7 +14431,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14431,22 +14443,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5/26/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV. 5012</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14462,12 +14474,12 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>DESPLAZAR COLUMNA TRAMBUS</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -14484,14 +14496,14 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.436804</v>
+        <v>-58.404652</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.618542</v>
+        <v>-34.58263</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14501,7 +14513,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>ALM-F</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14513,22 +14525,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>-4992</t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5/26/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BEYROUTH 4992</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14544,7 +14556,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>REALIZAR CAMBIO DE POSTE POR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14563,27 +14575,27 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.502223</v>
+        <v>-58.433857</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.626887</v>
+        <v>-34.57424</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>DEV-H</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14595,22 +14607,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>-4926</t>
+          <t xml:space="preserve">10102 </t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5/26/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BEYROUTH 4926</t>
+          <t>ELCANO AV. 3950</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14626,7 +14638,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CAMBIAR POSTE POR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14648,14 +14660,14 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.501459</v>
+        <v>-58.460457</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.626196</v>
+        <v>-34.582381</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -14665,10 +14677,256 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>DEV-H</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10103 </t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DORREGO AV. 2765</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>COLUMNA INCLINADA</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-58.432319</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-34.574385</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>BLO-G</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10104 </t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>-58.416882</v>
+      </c>
+      <c r="N170" t="n">
+        <v>-34.562655</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>BLO-?</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10131 </t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-58.419652</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-34.588271</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>VCR-K</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R171"/>
+  <dimension ref="A1:R159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9769,7 +9769,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PJ00009</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>4/20/2026</t>
@@ -9777,7 +9781,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AREVALO 2006</t>
+          <t>THAMES 1516</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9797,7 +9801,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813304751</t>
+          <t>813304793</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9812,7 +9816,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9824,916 +9828,960 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.444908</v>
+        <v>-58.431966</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.607205</v>
+        <v>-34.588553</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>VCR-F</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>LR00001</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>4/27/2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BILLINGHURST 1796</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>813350523</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" t="n">
+        <v>-58.409695</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-34.589662</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>AGU-D</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PJ00040</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>HONDURAS 4822</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>813350536</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-58.428528</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-34.589872</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>VCR-F</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AF00001</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SALGUERO, JERONIMO 1995</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>813304889</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-58.413378</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-34.587254</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>VCR-G</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9006</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CHARCAS 3250</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>813304917</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>-58.41175</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-34.592173</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
           <t>Almagro</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>ALM-O</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>AGU-C</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>8921</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
         <is>
           <t>4/20/2026</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AREVALO 2006</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>DORREGO AV.2752</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>813304751</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>813305004</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L111" t="n">
-        <v>1</v>
-      </c>
-      <c r="M111" t="n">
-        <v>-58.419576</v>
-      </c>
-      <c r="N111" t="n">
-        <v>-34.621289</v>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>ALM-A</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr">
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>-58.43266</v>
+      </c>
+      <c r="N115" t="n">
+        <v>-34.574202</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>BLO-G</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>S00419298</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
         <is>
           <t>4/20/2026</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AREVALO 2006</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AUSTRIA 2354</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>813350615</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-58.401523</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-34.586182</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>AGU-H</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>S0000223</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>4/21/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ARENALES 3660</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>813304751</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>813352547</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L112" t="n">
-        <v>1</v>
-      </c>
-      <c r="M112" t="n">
-        <v>-58.430568</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-34.599485</v>
-      </c>
-      <c r="O112" t="inlineStr">
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>-58.413732</v>
+      </c>
+      <c r="N117" t="n">
+        <v>-34.585415</v>
+      </c>
+      <c r="O117" t="inlineStr">
         <is>
           <t>Palermo</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>CLI-N</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AREVALO 2006</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>AGU-L</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>000025</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>4/23/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AV DORREGO 3900</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>813304751</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>813352568</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="n">
+        <v>-58.418801</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-34.564182</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>BLO-?</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>9025</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>4/24/2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ALVAREZ, JULIAN 2552</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>813352603</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L113" t="n">
-        <v>1</v>
-      </c>
-      <c r="M113" t="n">
-        <v>-58.437499</v>
-      </c>
-      <c r="N113" t="n">
-        <v>-34.578324</v>
-      </c>
-      <c r="O113" t="inlineStr">
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="n">
+        <v>-58.413555</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-34.585955</v>
+      </c>
+      <c r="O119" t="inlineStr">
         <is>
           <t>Palermo</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>ATH-B</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AREVALO 2006</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>AGU-L</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>9062</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>4/30/2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BULNES 2550</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>813304751</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>813631416</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>COLUMNA INCLINADA</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L114" t="n">
-        <v>1</v>
-      </c>
-      <c r="M114" t="n">
-        <v>-58.435547</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-34.576622</v>
-      </c>
-      <c r="O114" t="inlineStr">
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-58.407013</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-34.582645</v>
+      </c>
+      <c r="O120" t="inlineStr">
         <is>
           <t>Palermo</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>ATH-B</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AREVALO 2006</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>AGU-N</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>9063</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4/30/2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DEL LIBERTADOR AV. 2030</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>813304751</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>813631417</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>COLUMNA INCLINADA</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L115" t="n">
-        <v>1</v>
-      </c>
-      <c r="M115" t="n">
-        <v>-58.373629</v>
-      </c>
-      <c r="N115" t="n">
-        <v>-34.64417</v>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>CON-A</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>ARATO-25058.AF.1CON</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AREVALO 2260</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>813304755</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
-        <v>1</v>
-      </c>
-      <c r="M116" t="n">
-        <v>-58.444908</v>
-      </c>
-      <c r="N116" t="n">
-        <v>-34.607205</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>ALM-O</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AREVALO 2260</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>813304755</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L117" t="n">
-        <v>1</v>
-      </c>
-      <c r="M117" t="n">
-        <v>-58.419576</v>
-      </c>
-      <c r="N117" t="n">
-        <v>-34.621289</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>ALM-A</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AREVALO 2260</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>813304755</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L118" t="n">
-        <v>1</v>
-      </c>
-      <c r="M118" t="n">
-        <v>-58.430568</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-34.599485</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>CLI-N</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AREVALO 2260</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>813304755</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L119" t="n">
-        <v>1</v>
-      </c>
-      <c r="M119" t="n">
-        <v>-58.437499</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-34.578324</v>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>ATH-B</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AREVALO 2260</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>813304755</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L120" t="n">
-        <v>1</v>
-      </c>
-      <c r="M120" t="n">
-        <v>-58.435547</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-34.576622</v>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>ATH-B</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>4/20/2026</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AREVALO 2260</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>813304755</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.373629</v>
+        <v>-58.401882</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.64417</v>
+        <v>-34.582006</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10743,29 +10791,29 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>CON-A</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PJ00009</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>THAMES 1516</t>
+          <t>CASTEX 3439</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10785,7 +10833,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>813304793</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10812,10 +10860,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.431966</v>
+        <v>-58.406414</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.588553</v>
+        <v>-34.577519</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10829,7 +10877,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10841,22 +10889,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LR00001</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4/27/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BILLINGHURST 1796</t>
+          <t>LACROZE, FEDERICO AV. 2338</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10871,17 +10919,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>813350523</t>
+          <t>813631432</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10898,24 +10946,24 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.409695</v>
+        <v>-58.444112</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.589662</v>
+        <v>-34.569261</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>AGU-D</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10927,17 +10975,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10957,17 +11005,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10984,10 +11032,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.428528</v>
+        <v>-58.438595</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.589872</v>
+        <v>-34.565168</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11001,7 +11049,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11013,17 +11061,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11043,17 +11091,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -11070,10 +11118,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.413378</v>
+        <v>-58.437217</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.587254</v>
+        <v>-34.567174</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11087,7 +11135,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11099,22 +11147,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CHARCAS 3250</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11129,7 +11177,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813304917</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11156,14 +11204,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.41175</v>
+        <v>-58.44018</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.592173</v>
+        <v>-34.565612</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11173,7 +11221,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11185,17 +11233,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DORREGO AV.2752</t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11215,17 +11263,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -11242,24 +11290,24 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.43266</v>
+        <v>-58.441718</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.574202</v>
+        <v>-34.566411</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11271,22 +11319,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S00419298</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AUSTRIA 2354</t>
+          <t>CAPDEVILA 3245</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11301,7 +11349,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>813350615</t>
+          <t>813631453</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11328,24 +11376,24 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.401523</v>
+        <v>-58.492198</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.586182</v>
+        <v>-34.567241</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>PUE-F</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11357,22 +11405,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S0000223</t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ARENALES 3660</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11387,7 +11435,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11414,14 +11462,14 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.413732</v>
+        <v>-58.402534</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.585415</v>
+        <v>-34.593133</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11431,7 +11479,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11443,22 +11491,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4/23/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AV DORREGO 3900</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11471,14 +11519,10 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>813352568</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11493,21 +11537,21 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L130" t="n">
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.418801</v>
+        <v>-58.385947</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.564182</v>
+        <v>-34.588156</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11517,7 +11561,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11529,17 +11573,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 2552</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11557,19 +11601,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>813352603</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -11586,10 +11626,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.413555</v>
+        <v>-58.440439</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.585955</v>
+        <v>-34.575416</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11603,7 +11643,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11615,17 +11655,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BULNES 2550</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11643,19 +11683,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>813631416</t>
-        </is>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -11672,10 +11708,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.407013</v>
+        <v>-58.438274</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.582645</v>
+        <v>-34.564049</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11689,7 +11725,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11701,17 +11737,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 2030</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11729,19 +11765,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>813631417</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11758,14 +11790,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.401882</v>
+        <v>-58.434721</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.582006</v>
+        <v>-34.567241</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11775,7 +11807,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11787,17 +11819,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CASTEX 3439</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11815,11 +11847,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>813631425</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11844,10 +11872,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.406414</v>
+        <v>-58.435738</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.577519</v>
+        <v>-34.564606</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11861,7 +11889,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11873,17 +11901,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2338</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11901,19 +11929,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>813631432</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11930,24 +11954,24 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.444112</v>
+        <v>-58.435011</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.569261</v>
+        <v>-34.56566</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11959,17 +11983,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11987,14 +12011,10 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>813631446</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12004,7 +12024,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12016,10 +12036,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.438595</v>
+        <v>-58.430774</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.565168</v>
+        <v>-34.568179</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12033,7 +12053,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12045,17 +12065,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12073,19 +12093,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>813631449</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -12102,10 +12118,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.437217</v>
+        <v>-58.436255</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.567174</v>
+        <v>-34.567733</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12131,17 +12147,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12159,11 +12175,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>813631451</t>
-        </is>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12188,10 +12200,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.44018</v>
+        <v>-58.443403</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.565612</v>
+        <v>-34.575666</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12205,7 +12217,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12217,17 +12229,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12245,19 +12257,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>813631452</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -12274,24 +12282,24 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.441718</v>
+        <v>-58.428639</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.566411</v>
+        <v>-34.59039</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12303,22 +12311,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CAPDEVILA 3245</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12331,11 +12339,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>813631453</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12360,24 +12364,24 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.492198</v>
+        <v>-58.404726</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.567241</v>
+        <v>-34.596069</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12389,22 +12393,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S00477293</t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARENALES 2552</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12417,11 +12421,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>813631921</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -12446,14 +12446,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.402534</v>
+        <v>-58.422183</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.593133</v>
+        <v>-34.576849</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12475,7 +12475,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S01385955</t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12485,12 +12485,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>POSADAS 1391</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12528,14 +12528,14 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.385947</v>
+        <v>-58.425803</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.588156</v>
+        <v>-34.588513</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12557,17 +12557,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12610,10 +12610,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.440439</v>
+        <v>-58.424388</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.575416</v>
+        <v>-34.59632</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12639,17 +12639,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12692,10 +12692,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.438274</v>
+        <v>-58.427895</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.564049</v>
+        <v>-34.583677</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12721,17 +12721,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t xml:space="preserve">9924 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>CORDOBA AV. 4089</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12774,10 +12774,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.434721</v>
+        <v>-58.424553</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.567241</v>
+        <v>-34.59709</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12803,17 +12803,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12834,12 +12834,12 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -12856,10 +12856,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.435738</v>
+        <v>-58.440973</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.564606</v>
+        <v>-34.572415</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12885,22 +12885,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12916,17 +12916,17 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -12938,14 +12938,14 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.435011</v>
+        <v>-58.40382</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.56566</v>
+        <v>-34.594385</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -12967,17 +12967,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -13020,10 +13020,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.430774</v>
+        <v>-58.43218</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.568179</v>
+        <v>-34.578546</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13049,17 +13049,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13102,10 +13102,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.436255</v>
+        <v>-58.436737</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.567733</v>
+        <v>-34.58597</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13131,17 +13131,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13162,12 +13162,12 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -13184,10 +13184,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.443403</v>
+        <v>-58.413584</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.575666</v>
+        <v>-34.58551</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13213,17 +13213,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13244,17 +13244,17 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -13266,10 +13266,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.428639</v>
+        <v>-58.415912</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.59039</v>
+        <v>-34.588977</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13326,12 +13326,12 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -13348,14 +13348,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.404726</v>
+        <v>-58.413885</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.596069</v>
+        <v>-34.586628</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13377,17 +13377,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">10080 </t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>THAMES 549</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13408,17 +13408,17 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -13430,10 +13430,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.422183</v>
+        <v>-58.442534</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.576849</v>
+        <v>-34.59499</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13459,17 +13459,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13490,12 +13490,12 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13512,14 +13512,14 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.425803</v>
+        <v>-58.404652</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.588513</v>
+        <v>-34.58263</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13541,7 +13541,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13572,17 +13572,17 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -13594,10 +13594,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.424388</v>
+        <v>-58.433857</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.59632</v>
+        <v>-34.57424</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13623,7 +13623,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">10102 </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t>ELCANO AV. 3950</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13654,7 +13654,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13676,24 +13676,24 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.427895</v>
+        <v>-58.460457</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.583677</v>
+        <v>-34.582381</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>ATH-H</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13705,7 +13705,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13736,12 +13736,12 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13758,10 +13758,10 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.424553</v>
+        <v>-58.432319</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.59709</v>
+        <v>-34.574385</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13787,7 +13787,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -13818,12 +13818,12 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -13840,10 +13840,10 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.440973</v>
+        <v>-58.416882</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.572415</v>
+        <v>-34.562655</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13869,7 +13869,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13879,12 +13879,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13900,17 +13900,17 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -13922,14 +13922,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.40382</v>
+        <v>-58.419652</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.594385</v>
+        <v>-34.588271</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -13939,994 +13939,10 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10042 </t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>PARAGUAY 5310</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L160" t="n">
-        <v>1</v>
-      </c>
-      <c r="M160" t="n">
-        <v>-58.43218</v>
-      </c>
-      <c r="N160" t="n">
-        <v>-34.578546</v>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>ATH-B</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10062 </t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>HUMBOLDT 1556</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L161" t="n">
-        <v>1</v>
-      </c>
-      <c r="M161" t="n">
-        <v>-58.436737</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-34.58597</v>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>ATH-M</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10066 </t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>DESMONTAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Desmonte</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L162" t="n">
-        <v>1</v>
-      </c>
-      <c r="M162" t="n">
-        <v>-58.413584</v>
-      </c>
-      <c r="N162" t="n">
-        <v>-34.58551</v>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>AGU-L</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10067 </t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>CHARCAS 3601</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L163" t="n">
-        <v>1</v>
-      </c>
-      <c r="M163" t="n">
-        <v>-58.415912</v>
-      </c>
-      <c r="N163" t="n">
-        <v>-34.588977</v>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>VCR-E</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10072 </t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>SANTA FE AV. 3470</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
-      </c>
-      <c r="M164" t="n">
-        <v>-58.413885</v>
-      </c>
-      <c r="N164" t="n">
-        <v>-34.586628</v>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>VCR-G</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10080 </t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>THAMES 549</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M165" t="n">
-        <v>-58.442534</v>
-      </c>
-      <c r="N165" t="n">
-        <v>-34.59499</v>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>VCR-H</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10083 </t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L166" t="n">
-        <v>1</v>
-      </c>
-      <c r="M166" t="n">
-        <v>-58.404652</v>
-      </c>
-      <c r="N166" t="n">
-        <v>-34.58263</v>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>AGU-N</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10098 </t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>DORREGO AV. 2635</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="n">
-        <v>-58.433857</v>
-      </c>
-      <c r="N167" t="n">
-        <v>-34.57424</v>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>BLO-G</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10102 </t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>ELCANO AV. 3950</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L168" t="n">
-        <v>1</v>
-      </c>
-      <c r="M168" t="n">
-        <v>-58.460457</v>
-      </c>
-      <c r="N168" t="n">
-        <v>-34.582381</v>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>ATH-H</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10103 </t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>DORREGO AV. 2765</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L169" t="n">
-        <v>1</v>
-      </c>
-      <c r="M169" t="n">
-        <v>-58.432319</v>
-      </c>
-      <c r="N169" t="n">
-        <v>-34.574385</v>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>BLO-G</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10104 </t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
-      <c r="M170" t="n">
-        <v>-58.416882</v>
-      </c>
-      <c r="N170" t="n">
-        <v>-34.562655</v>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>BLO-?</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10131 </t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L171" t="n">
-        <v>1</v>
-      </c>
-      <c r="M171" t="n">
-        <v>-58.419652</v>
-      </c>
-      <c r="N171" t="n">
-        <v>-34.588271</v>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>VCR-K</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R159"/>
+  <dimension ref="A1:R157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3923,17 +3923,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-502</t>
+          <t>-517</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7/7/2025</t>
+          <t>7/16/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tagle 2562</t>
+          <t>Av Dorrego 2721</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>808036198</t>
+          <t>808373635</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso nodo teco</t>
+          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3980,14 +3980,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.400188</v>
+        <v>-58.432805</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.583882</v>
+        <v>-34.574345</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4009,22 +4009,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-517</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7/16/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Av Dorrego 2721</t>
+          <t>URUGUAY 1094</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>808373635</t>
+          <t>808430941</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4059,21 +4059,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.432805</v>
+        <v>-58.387175</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.574345</v>
+        <v>-34.596</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4095,22 +4095,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>-523</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>7/20/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>URUGUAY 1094</t>
+          <t>Luis Maria Campos 585</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>808430941</t>
+          <t>808460898</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4145,21 +4145,21 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.387175</v>
+        <v>-58.434668</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.596</v>
+        <v>-34.571258</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4181,17 +4181,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-523</t>
+          <t>-524</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7/20/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 585</t>
+          <t>Luis Maria Campos 509</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>808460898</t>
+          <t>808460897</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4238,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.434668</v>
+        <v>-58.434194</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.571258</v>
+        <v>-34.571754</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4267,17 +4267,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-524</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 509</t>
+          <t>GASCON 1195</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>808460897</t>
+          <t>808571975</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.434194</v>
+        <v>-58.423127</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.571754</v>
+        <v>-34.596476</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GASCON 1195</t>
+          <t>DORREGO AV. 2687</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>808571980</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4410,10 +4410,10 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.423127</v>
+        <v>-58.433295</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.596476</v>
+        <v>-34.574305</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4439,7 +4439,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>-533</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2687</t>
+          <t>Bonpland 2233</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>808571980</t>
+          <t>808571985</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t xml:space="preserve">Cambiar columna y colocar rienda a pique </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4489,17 +4489,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.433295</v>
+        <v>-58.43258</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.574305</v>
+        <v>-34.579265</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4525,22 +4525,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-533</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>8/6/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bonpland 2233</t>
+          <t>BERUTI 2496</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4555,17 +4555,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>808571985</t>
+          <t>808733917</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar columna y colocar rienda a pique </t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4575,21 +4575,21 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.43258</v>
+        <v>-58.401374</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.579265</v>
+        <v>-34.592623</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4599,29 +4599,29 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>S00946632</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8/6/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BERUTI 2496</t>
+          <t>BERUTI 2592</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>808733917</t>
+          <t>808918705</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Traspaso de redes y retiro de columna</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4668,10 +4668,10 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.401374</v>
+        <v>-58.402657</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.592623</v>
+        <v>-34.592182</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4685,34 +4685,34 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S00946632</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/20/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BERUTI 2592</t>
+          <t>ARENALES 3640</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>808918705</t>
+          <t>ICD30449342</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna</t>
+          <t>Pendiente de desmonte icd Colocacion ICD30449342</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4754,14 +4754,14 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.402657</v>
+        <v>-58.413584</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.592182</v>
+        <v>-34.58551</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4783,7 +4783,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ARENALES 3640</t>
+          <t>CHARCAS 3986</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ICD30449342</t>
+          <t>809065854</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pendiente de desmonte icd Colocacion ICD30449342</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4840,10 +4840,10 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.413584</v>
+        <v>-58.419711</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.58551</v>
+        <v>-34.586299</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4869,17 +4869,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8/20/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CHARCAS 3986</t>
+          <t>GORRITI 4417</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>809065854</t>
+          <t>809526157</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4926,10 +4926,10 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.419711</v>
+        <v>-58.425358</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.586299</v>
+        <v>-34.593308</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4955,7 +4955,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GORRITI 4417</t>
+          <t>NICARAGUA 5510</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>809526157</t>
+          <t>809526162</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5012,10 +5012,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.425358</v>
+        <v>-58.432726</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.593308</v>
+        <v>-34.582328</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5041,17 +5041,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NICARAGUA 5510</t>
+          <t>Dorrego 2265</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>809526162</t>
+          <t>809837500</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5098,10 +5098,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.432726</v>
+        <v>-58.438083</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.582328</v>
+        <v>-34.577107</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5127,17 +5127,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dorrego 2265</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>809837500</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5184,10 +5184,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.438083</v>
+        <v>-58.429159</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.577107</v>
+        <v>-34.577821</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5213,22 +5213,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>S00936008</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/30/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>Azcuenaga 1645</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>01095943</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>picada colocar R200 para pedir traspaso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5270,14 +5270,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.429159</v>
+        <v>-58.397092</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.577821</v>
+        <v>-34.590173</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5287,34 +5287,34 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S00936008</t>
+          <t>-629</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9/30/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Azcuenaga 1645</t>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01095943</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>picada colocar R200 para pedir traspaso</t>
+          <t>Colocar R400 para posterior traspaso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5356,14 +5356,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.397092</v>
+        <v>-58.422406</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.590173</v>
+        <v>-34.577085</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5373,29 +5373,29 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-629</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fray Justo Santa Maria de Oro 2730</t>
+          <t>NEWBERY, JORGE 2696</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ICD31463422</t>
+          <t>810421921</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Colocar R400 para posterior traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5430,22 +5430,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.422406</v>
+        <v>-58.44293</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.577085</v>
+        <v>-34.574483</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5471,27 +5471,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2696</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810421921</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5516,26 +5516,26 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.44293</v>
+        <v>-58.4018</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.574483</v>
+        <v>-34.590471</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5557,27 +5557,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5611,17 +5611,17 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.4018</v>
+        <v>-58.417634</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.590471</v>
+        <v>-34.587439</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5643,17 +5643,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5700,10 +5700,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.417634</v>
+        <v>-58.440031</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.587439</v>
+        <v>-34.575409</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5729,17 +5729,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>UGARTECHE 3079</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5759,22 +5759,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t xml:space="preserve">01638326 </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5786,10 +5786,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.440031</v>
+        <v>-58.411934</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.575409</v>
+        <v>-34.580653</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5815,17 +5815,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UGARTECHE 3079</t>
+          <t>Paraguay 4301</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638326 </t>
+          <t>810853935</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
+          <t>Cambio de columna propia corroida en base</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5872,10 +5872,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.411934</v>
+        <v>-58.422434</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.580653</v>
+        <v>-34.585978</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5901,17 +5901,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>S00785128</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paraguay 4301</t>
+          <t>Paraguay 5055</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810853935</t>
+          <t>810877555</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Cambio de columna propia corroida en base</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5958,10 +5958,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.422434</v>
+        <v>-58.429394</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.585978</v>
+        <v>-34.580587</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5987,7 +5987,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S00785128</t>
+          <t>S00566892</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Paraguay 5055</t>
+          <t xml:space="preserve">SANTA FE AV. 3711 </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>810877555</t>
+          <t>810877633</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6044,10 +6044,10 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.429394</v>
+        <v>-58.416063</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.580587</v>
+        <v>-34.584975</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6073,22 +6073,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S00566892</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE AV. 3711 </t>
+          <t>URUGUAY 1070</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810877633</t>
+          <t>810984538</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6130,14 +6130,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.416063</v>
+        <v>-58.387161</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.584975</v>
+        <v>-34.596255</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6159,7 +6159,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>URUGUAY 1070</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>810984538</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6216,10 +6216,10 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.387161</v>
+        <v>-58.390974</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.596255</v>
+        <v>-34.594177</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6245,17 +6245,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>-696</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>Las heras 3092</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811131649</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6290,22 +6290,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.390974</v>
+        <v>-58.405835</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.594177</v>
+        <v>-34.583573</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>-696</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Las heras 3092</t>
+          <t>AGUERO 2038</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811131649</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>Traspasar red a columna nueva y retirar la vieja</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6381,17 +6381,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.405835</v>
+        <v>-58.402647</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.583573</v>
+        <v>-34.588274</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>AGU-G</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6417,17 +6417,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AGUERO 2038</t>
+          <t>French 2377</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6447,17 +6447,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Traspasar red a columna nueva y retirar la vieja</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6474,10 +6474,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.402647</v>
+        <v>-58.398947</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.588274</v>
+        <v>-34.590946</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6491,19 +6491,19 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>AGU-G</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>French 2377</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>poste inclinado base quebrada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6553,17 +6553,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.398947</v>
+        <v>-58.403895</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.590946</v>
+        <v>-34.575559</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6577,19 +6577,19 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
+          <t>GURRUCHAGA 2473</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>poste inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6639,21 +6639,21 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.403895</v>
+        <v>-58.420304</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.575559</v>
+        <v>-34.582607</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>VCR-L</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6675,17 +6675,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>S01159828</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GURRUCHAGA 2473</t>
+          <t xml:space="preserve"> THAMES 2041</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6732,10 +6732,10 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.420304</v>
+        <v>-58.426667</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.582607</v>
+        <v>-34.585153</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>VCR-L</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6761,17 +6761,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S01159828</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> THAMES 2041</t>
+          <t>SOLER 4509</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6818,10 +6818,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.426667</v>
+        <v>-58.42336</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.585153</v>
+        <v>-34.588111</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6847,7 +6847,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SOLER 4509</t>
+          <t>DIAZ, CNEL. AV. 2512</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6892,26 +6892,26 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.42336</v>
+        <v>-58.406111</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.588111</v>
+        <v>-34.58316</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6933,22 +6933,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>01018482</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2512</t>
+          <t>AGUERO 2364</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t xml:space="preserve">02511365 </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6978,22 +6978,22 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.406111</v>
+        <v>-58.399462</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.58316</v>
+        <v>-34.585952</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7019,22 +7019,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>01018482</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AGUERO 2364</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511365 </t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7076,14 +7076,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.399462</v>
+        <v>-58.436051</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.585952</v>
+        <v>-34.583855</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7105,7 +7105,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7162,10 +7162,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.436051</v>
+        <v>-58.437628</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.583855</v>
+        <v>-34.587953</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7191,7 +7191,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7248,10 +7248,10 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.437628</v>
+        <v>-58.439513</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.587953</v>
+        <v>-34.585314</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7277,7 +7277,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>01211534</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t xml:space="preserve"> JUNCAL 2490</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811454103</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7327,21 +7327,21 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.439513</v>
+        <v>-58.401685</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.585314</v>
+        <v>-34.591336</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7363,7 +7363,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>01211534</t>
+          <t>S01290507</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUNCAL 2490</t>
+          <t>CABELLO 3472</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811454103</t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7413,21 +7413,21 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L82" t="n">
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.401685</v>
+        <v>-58.409438</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.591336</v>
+        <v>-34.58118</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7449,7 +7449,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01290507</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CABELLO 3472</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7506,24 +7506,24 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.409438</v>
+        <v>-58.444955</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.58118</v>
+        <v>-34.569791</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7535,17 +7535,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>DIAZ, CNEL. AV. 2599</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7585,31 +7585,31 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.444955</v>
+        <v>-58.405559</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.569791</v>
+        <v>-34.582478</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7621,17 +7621,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2599</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7678,14 +7678,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.405559</v>
+        <v>-58.432319</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.582478</v>
+        <v>-34.574385</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7707,22 +7707,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>-735</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>Beruti 3012</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7761,17 +7761,17 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.432319</v>
+        <v>-58.406584</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.574385</v>
+        <v>-34.589518</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-E</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7793,22 +7793,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-735</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Beruti 3012</t>
+          <t>Costa Rica 5741</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7847,17 +7847,17 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.406584</v>
+        <v>-58.436073</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.589518</v>
+        <v>-34.581506</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>AGU-E</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7879,7 +7879,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Costa Rica 5741</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7936,10 +7936,10 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.436073</v>
+        <v>-58.413945</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.581506</v>
+        <v>-34.582774</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7965,7 +7965,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>CALLAO AV. 2014</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8022,14 +8022,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.413945</v>
+        <v>-58.386954</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.582774</v>
+        <v>-34.587337</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8051,7 +8051,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>S00066646</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CALLAO AV. 2014</t>
+          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8096,26 +8096,26 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L90" t="n">
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.386954</v>
+        <v>-58.408259</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.587337</v>
+        <v>-34.580266</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8137,17 +8137,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S00066646</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8187,17 +8187,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.408259</v>
+        <v>-58.432807</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.580266</v>
+        <v>-34.574343</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8223,17 +8223,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8280,10 +8280,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.432807</v>
+        <v>-58.432102</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.574343</v>
+        <v>-34.574248</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8309,17 +8309,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>SINCLAIR 3106</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8366,10 +8366,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.432102</v>
+        <v>-58.422892</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.574248</v>
+        <v>-34.573802</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8395,7 +8395,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>S01064368</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SINCLAIR 3106</t>
+          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8452,10 +8452,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.422892</v>
+        <v>-58.426552</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.573802</v>
+        <v>-34.592076</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8481,17 +8481,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S01064368</t>
+          <t>S01406817</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/3/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
+          <t>CAMPOS, LUIS M. AV. 155</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.426552</v>
+        <v>-58.431638</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.592076</v>
+        <v>-34.574344</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8567,17 +8567,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S01406817</t>
+          <t>S00165389</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3/3/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 155</t>
+          <t>HONDURAS AV. 3708</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8624,10 +8624,10 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.431638</v>
+        <v>-58.414717</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.574344</v>
+        <v>-34.594123</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-B</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8653,17 +8653,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S00165389</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HONDURAS AV. 3708</t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8703,17 +8703,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.414717</v>
+        <v>-58.436004</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.594123</v>
+        <v>-34.58156</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>VCR-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8796,10 +8796,10 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.436004</v>
+        <v>-58.435443</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.58156</v>
+        <v>-34.56693</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8825,22 +8825,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t>RODRIGUEZ PEÑA 1650</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8882,14 +8882,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.435443</v>
+        <v>-58.389533</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.56693</v>
+        <v>-34.591306</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8911,22 +8911,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEÑA 1650</t>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812879521</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.389533</v>
+        <v>-58.408769</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.591306</v>
+        <v>-34.587342</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+          <t>SEGUI JUAN FRANCISCO 4691</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>812879521</t>
+          <t>812879559</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9054,14 +9054,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.408769</v>
+        <v>-58.422229</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.587342</v>
+        <v>-34.573148</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9083,17 +9083,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>00781500</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SEGUI JUAN FRANCISCO 4691</t>
+          <t>RAVIGNANI EMILIO DR 1498</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9113,12 +9113,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>812879559</t>
+          <t>812879925</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9140,10 +9140,10 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.422229</v>
+        <v>-58.441411</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.573148</v>
+        <v>-34.583443</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9169,22 +9169,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>00781500</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RAVIGNANI EMILIO DR 1498</t>
+          <t>JUNCAL 2249</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>812879925</t>
+          <t>812880742</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9226,14 +9226,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.441411</v>
+        <v>-58.399319</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.583443</v>
+        <v>-34.592221</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9243,34 +9243,34 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JUNCAL 2249</t>
+          <t>PARAGUAY 4237</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>812880742</t>
+          <t>813046389</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9312,14 +9312,14 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.399319</v>
+        <v>-58.421616</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.592221</v>
+        <v>-34.586608</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9329,29 +9329,29 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>S00289486</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PARAGUAY 4237</t>
+          <t>PARAGUAY 4585</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>813046389</t>
+          <t>813046715</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -9398,10 +9398,10 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.421616</v>
+        <v>-58.42498</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.586608</v>
+        <v>-34.584031</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9427,7 +9427,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S00289486</t>
+          <t>S00325208</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PARAGUAY 4585</t>
+          <t>PARAGUAY 3711</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>813046715</t>
+          <t>813046718</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9484,10 +9484,10 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.42498</v>
+        <v>-58.416117</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.584031</v>
+        <v>-34.590942</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-C</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9513,7 +9513,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S00325208</t>
+          <t>S00337251</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PARAGUAY 3711</t>
+          <t>SANCHEZ DE BUSTAMANTE 2450</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>813046718</t>
+          <t>813046724</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9570,14 +9570,14 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.416117</v>
+        <v>-58.403295</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.590942</v>
+        <v>-34.585041</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>VCR-C</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S00337251</t>
+          <t>S00364886</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 2450</t>
+          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>813046724</t>
+          <t>813046778</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9656,14 +9656,14 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.403295</v>
+        <v>-58.434778</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.585041</v>
+        <v>-34.569188</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9685,17 +9685,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S00364886</t>
+          <t>PJ00009</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
+          <t>THAMES 1516</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>813046778</t>
+          <t>813304793</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9742,10 +9742,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.434778</v>
+        <v>-58.431966</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.569188</v>
+        <v>-34.588553</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9771,22 +9771,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PJ00009</t>
+          <t>LR00001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>THAMES 1516</t>
+          <t>BILLINGHURST 1796</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813304793</t>
+          <t>813350523</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9828,14 +9828,14 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.431966</v>
+        <v>-58.409695</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.588553</v>
+        <v>-34.589662</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-D</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9857,22 +9857,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LR00001</t>
+          <t>PJ00040</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4/27/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BILLINGHURST 1796</t>
+          <t>HONDURAS 4822</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>813350523</t>
+          <t>813350536</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9914,14 +9914,14 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.409695</v>
+        <v>-58.428528</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.589662</v>
+        <v>-34.589872</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>AGU-D</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9943,7 +9943,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>AF00001</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>SALGUERO, JERONIMO 1995</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>813304889</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10000,10 +10000,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.428528</v>
+        <v>-58.413378</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.589872</v>
+        <v>-34.587254</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10029,7 +10029,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>CHARCAS 3250</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>813304917</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10086,14 +10086,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.413378</v>
+        <v>-58.41175</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.587254</v>
+        <v>-34.592173</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10115,7 +10115,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CHARCAS 3250</t>
+          <t>DORREGO AV.2752</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>813304917</t>
+          <t>813305004</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10172,14 +10172,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.41175</v>
+        <v>-58.43266</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.592173</v>
+        <v>-34.574202</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10201,7 +10201,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>S00419298</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DORREGO AV.2752</t>
+          <t>AUSTRIA 2354</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>813350615</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10258,14 +10258,14 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.43266</v>
+        <v>-58.401523</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.574202</v>
+        <v>-34.586182</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10287,22 +10287,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S00419298</t>
+          <t>S0000223</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AUSTRIA 2354</t>
+          <t>ARENALES 3660</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>813350615</t>
+          <t>813352547</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10344,14 +10344,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.401523</v>
+        <v>-58.413732</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.586182</v>
+        <v>-34.585415</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10373,17 +10373,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S0000223</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/23/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ARENALES 3660</t>
+          <t>AV DORREGO 3900</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>813352568</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10423,17 +10423,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.413732</v>
+        <v>-58.418801</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.585415</v>
+        <v>-34.564182</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10459,17 +10459,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4/23/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AV DORREGO 3900</t>
+          <t>ALVAREZ, JULIAN 2552</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>813352568</t>
+          <t>813352603</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10509,17 +10509,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.418801</v>
+        <v>-58.413555</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.564182</v>
+        <v>-34.585955</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10545,17 +10545,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 2552</t>
+          <t>BULNES 2550</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10575,17 +10575,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>813352603</t>
+          <t>813631416</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10602,10 +10602,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.413555</v>
+        <v>-58.407013</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.585955</v>
+        <v>-34.582645</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10631,7 +10631,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BULNES 2550</t>
+          <t>DEL LIBERTADOR AV. 2030</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>813631416</t>
+          <t>813631417</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10688,14 +10688,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.407013</v>
+        <v>-58.401882</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.582645</v>
+        <v>-34.582006</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10717,7 +10717,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 2030</t>
+          <t>CASTEX 3439</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10747,17 +10747,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>813631417</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10774,14 +10774,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.401882</v>
+        <v>-58.406414</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.582006</v>
+        <v>-34.577519</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10803,7 +10803,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CASTEX 3439</t>
+          <t>LACROZE, FEDERICO AV. 2338</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10833,17 +10833,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>813631425</t>
+          <t>813631432</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10860,24 +10860,24 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.406414</v>
+        <v>-58.444112</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.577519</v>
+        <v>-34.569261</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10889,7 +10889,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2338</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>813631432</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10946,24 +10946,24 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.444112</v>
+        <v>-58.438595</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.569261</v>
+        <v>-34.565168</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10975,7 +10975,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>813631446</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -11032,10 +11032,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.438595</v>
+        <v>-58.437217</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.565168</v>
+        <v>-34.567174</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813631449</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -11118,10 +11118,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.437217</v>
+        <v>-58.44018</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.567174</v>
+        <v>-34.565612</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11177,17 +11177,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813631451</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -11204,19 +11204,19 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.44018</v>
+        <v>-58.441718</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.565612</v>
+        <v>-34.566411</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -11233,22 +11233,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11263,17 +11263,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>813631452</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -11290,24 +11290,24 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.441718</v>
+        <v>-58.402534</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.566411</v>
+        <v>-34.593133</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11319,22 +11319,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CAPDEVILA 3245</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11347,11 +11347,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>813631453</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11376,24 +11372,24 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.492198</v>
+        <v>-58.385947</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.567241</v>
+        <v>-34.588156</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PUE-F</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11405,22 +11401,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S00477293</t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARENALES 2552</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11433,19 +11429,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>813631921</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11462,14 +11454,14 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.402534</v>
+        <v>-58.440439</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.593133</v>
+        <v>-34.575416</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11479,7 +11471,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11491,7 +11483,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S01385955</t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11501,12 +11493,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>POSADAS 1391</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11544,14 +11536,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.385947</v>
+        <v>-58.438274</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.588156</v>
+        <v>-34.564049</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11561,7 +11553,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11573,7 +11565,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11583,7 +11575,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11604,12 +11596,12 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -11626,10 +11618,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.440439</v>
+        <v>-58.434721</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.575416</v>
+        <v>-34.567241</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11643,7 +11635,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11655,7 +11647,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11665,7 +11657,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11708,10 +11700,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.438274</v>
+        <v>-58.435738</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.564049</v>
+        <v>-34.564606</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11737,7 +11729,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11747,7 +11739,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11768,7 +11760,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11790,10 +11782,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.434721</v>
+        <v>-58.435011</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.567241</v>
+        <v>-34.56566</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11807,7 +11799,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11819,7 +11811,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11829,7 +11821,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11860,7 +11852,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11872,10 +11864,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.435738</v>
+        <v>-58.430774</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.564606</v>
+        <v>-34.568179</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11889,7 +11881,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11901,7 +11893,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11911,7 +11903,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11932,7 +11924,7 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11954,10 +11946,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.435011</v>
+        <v>-58.436255</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.56566</v>
+        <v>-34.567733</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11983,7 +11975,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11993,7 +11985,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12024,7 +12016,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12036,10 +12028,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.430774</v>
+        <v>-58.443403</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.568179</v>
+        <v>-34.575666</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12053,7 +12045,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12065,7 +12057,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12075,7 +12067,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12118,10 +12110,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.436255</v>
+        <v>-58.428639</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.567733</v>
+        <v>-34.59039</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12135,7 +12127,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12147,7 +12139,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12157,12 +12149,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12200,14 +12192,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.443403</v>
+        <v>-58.404726</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.575666</v>
+        <v>-34.596069</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12217,7 +12209,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12229,7 +12221,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12239,7 +12231,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12270,7 +12262,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12282,10 +12274,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.428639</v>
+        <v>-58.422183</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.59039</v>
+        <v>-34.576849</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12299,7 +12291,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12311,7 +12303,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12321,12 +12313,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12364,14 +12356,14 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.404726</v>
+        <v>-58.425803</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.596069</v>
+        <v>-34.588513</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12381,7 +12373,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12393,17 +12385,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12424,17 +12416,17 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -12446,10 +12438,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.422183</v>
+        <v>-58.424388</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.576849</v>
+        <v>-34.59632</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12463,7 +12455,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12475,17 +12467,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12528,10 +12520,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.425803</v>
+        <v>-58.427895</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.588513</v>
+        <v>-34.583677</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12545,7 +12537,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12557,7 +12549,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t xml:space="preserve">9924 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12567,7 +12559,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>CORDOBA AV. 4089</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12588,17 +12580,17 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12610,10 +12602,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.424388</v>
+        <v>-58.424553</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.59632</v>
+        <v>-34.59709</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12639,7 +12631,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12649,7 +12641,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12670,12 +12662,12 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -12692,10 +12684,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.427895</v>
+        <v>-58.440973</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.583677</v>
+        <v>-34.572415</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12709,7 +12701,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12721,7 +12713,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12731,12 +12723,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12752,17 +12744,17 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12774,14 +12766,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.424553</v>
+        <v>-58.40382</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.59709</v>
+        <v>-34.594385</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12791,7 +12783,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12803,7 +12795,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12813,7 +12805,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12834,12 +12826,12 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -12856,10 +12848,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.440973</v>
+        <v>-58.43218</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.572415</v>
+        <v>-34.578546</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12873,7 +12865,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12885,7 +12877,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12895,12 +12887,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12916,17 +12908,17 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -12938,14 +12930,14 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.40382</v>
+        <v>-58.436737</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.594385</v>
+        <v>-34.58597</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -12955,7 +12947,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -12967,7 +12959,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12977,7 +12969,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12998,12 +12990,12 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -13020,10 +13012,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.43218</v>
+        <v>-58.413584</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.578546</v>
+        <v>-34.58551</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13037,7 +13029,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13049,7 +13041,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13059,7 +13051,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13080,17 +13072,17 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -13102,10 +13094,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.436737</v>
+        <v>-58.415912</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.58597</v>
+        <v>-34.588977</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13119,7 +13111,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13131,7 +13123,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13141,7 +13133,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13162,12 +13154,12 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -13184,10 +13176,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.413584</v>
+        <v>-58.413885</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.58551</v>
+        <v>-34.586628</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13201,7 +13193,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13213,7 +13205,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">10080 </t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13223,7 +13215,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t>THAMES 549</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13254,7 +13246,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -13266,10 +13258,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.415912</v>
+        <v>-58.442534</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.588977</v>
+        <v>-34.59499</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13283,7 +13275,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13295,7 +13287,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13305,7 +13297,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13326,12 +13318,12 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -13348,14 +13340,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.413885</v>
+        <v>-58.400188</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.586628</v>
+        <v>-34.583882</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13365,7 +13357,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13377,7 +13369,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13387,7 +13379,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>THAMES 549</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13430,14 +13422,14 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.442534</v>
+        <v>-58.404652</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.59499</v>
+        <v>-34.58263</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -13447,7 +13439,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13459,7 +13451,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13469,7 +13461,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13490,12 +13482,12 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13512,14 +13504,14 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.404652</v>
+        <v>-58.433857</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.58263</v>
+        <v>-34.57424</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13529,7 +13521,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13541,7 +13533,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13551,7 +13543,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13572,12 +13564,12 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -13594,10 +13586,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.433857</v>
+        <v>-58.432319</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.57424</v>
+        <v>-34.574385</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13623,7 +13615,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13633,7 +13625,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ELCANO AV. 3950</t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13654,7 +13646,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13676,24 +13668,24 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.460457</v>
+        <v>-58.416882</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.582381</v>
+        <v>-34.562655</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ATH-H</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13705,7 +13697,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13715,7 +13707,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13736,17 +13728,17 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -13758,10 +13750,10 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.432319</v>
+        <v>-58.419652</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.574385</v>
+        <v>-34.588271</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13775,174 +13767,10 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10104 </t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L158" t="n">
-        <v>1</v>
-      </c>
-      <c r="M158" t="n">
-        <v>-58.416882</v>
-      </c>
-      <c r="N158" t="n">
-        <v>-34.562655</v>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>BLO-?</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10131 </t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L159" t="n">
-        <v>1</v>
-      </c>
-      <c r="M159" t="n">
-        <v>-58.419652</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-34.588271</v>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>VCR-K</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R157"/>
+  <dimension ref="A1:R159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11483,7 +11483,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9179 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>ARAOZ 2289</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11536,10 +11536,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.438274</v>
+        <v>-58.418131</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.564049</v>
+        <v>-34.58774</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11565,7 +11565,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11618,10 +11618,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.434721</v>
+        <v>-58.438274</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.567241</v>
+        <v>-34.564049</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11647,7 +11647,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11700,10 +11700,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.435738</v>
+        <v>-58.434721</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.564606</v>
+        <v>-34.567241</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11729,7 +11729,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11760,7 +11760,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11782,10 +11782,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.435011</v>
+        <v>-58.435738</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.56566</v>
+        <v>-34.564606</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11842,7 +11842,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11864,10 +11864,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.430774</v>
+        <v>-58.435011</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.568179</v>
+        <v>-34.56566</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11893,7 +11893,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11946,10 +11946,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.436255</v>
+        <v>-58.430774</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.567733</v>
+        <v>-34.568179</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11975,7 +11975,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12028,10 +12028,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.443403</v>
+        <v>-58.436255</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.575666</v>
+        <v>-34.567733</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12057,7 +12057,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12110,10 +12110,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.428639</v>
+        <v>-58.443403</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.59039</v>
+        <v>-34.575666</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12192,14 +12192,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.404726</v>
+        <v>-58.428639</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.596069</v>
+        <v>-34.59039</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12221,7 +12221,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12274,14 +12274,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.422183</v>
+        <v>-58.404726</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.576849</v>
+        <v>-34.596069</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12303,7 +12303,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -12356,10 +12356,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.425803</v>
+        <v>-58.422183</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.588513</v>
+        <v>-34.576849</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12385,17 +12385,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12416,17 +12416,17 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -12438,10 +12438,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.424388</v>
+        <v>-58.425803</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.59632</v>
+        <v>-34.588513</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12467,7 +12467,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12498,17 +12498,17 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -12520,10 +12520,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.427895</v>
+        <v>-58.424388</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.583677</v>
+        <v>-34.59632</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12549,7 +12549,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12602,10 +12602,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.424553</v>
+        <v>-58.427895</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.59709</v>
+        <v>-34.583677</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12631,7 +12631,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t xml:space="preserve">9924 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>CORDOBA AV. 4089</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12662,12 +12662,12 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -12684,10 +12684,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.440973</v>
+        <v>-58.424553</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.572415</v>
+        <v>-34.59709</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12713,7 +12713,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12723,12 +12723,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12766,14 +12766,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.40382</v>
+        <v>-58.440973</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.594385</v>
+        <v>-34.572415</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12795,7 +12795,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12826,17 +12826,17 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12848,14 +12848,14 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.43218</v>
+        <v>-58.40382</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.578546</v>
+        <v>-34.594385</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12877,7 +12877,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12930,10 +12930,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.436737</v>
+        <v>-58.43218</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.58597</v>
+        <v>-34.578546</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -12959,7 +12959,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12990,12 +12990,12 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -13012,10 +13012,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.413584</v>
+        <v>-58.436737</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.58551</v>
+        <v>-34.58597</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13041,7 +13041,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13072,17 +13072,17 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -13094,10 +13094,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.415912</v>
+        <v>-58.413584</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.588977</v>
+        <v>-34.58551</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13123,7 +13123,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -13176,10 +13176,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.413885</v>
+        <v>-58.415912</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.586628</v>
+        <v>-34.588977</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13205,7 +13205,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>THAMES 549</t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13258,10 +13258,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.442534</v>
+        <v>-58.413885</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.59499</v>
+        <v>-34.586628</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13287,7 +13287,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">10082 </t>
+          <t xml:space="preserve">10080 </t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TAGLE 2562</t>
+          <t>THAMES 549</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13318,12 +13318,12 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -13340,14 +13340,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.400188</v>
+        <v>-58.442534</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.583882</v>
+        <v>-34.59499</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13369,7 +13369,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13400,12 +13400,12 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -13422,10 +13422,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.404652</v>
+        <v>-58.400188</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.58263</v>
+        <v>-34.583882</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13451,7 +13451,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13482,12 +13482,12 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13504,14 +13504,14 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.433857</v>
+        <v>-58.404652</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.57424</v>
+        <v>-34.58263</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13533,7 +13533,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13564,12 +13564,12 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -13586,10 +13586,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.432319</v>
+        <v>-58.433857</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.574385</v>
+        <v>-34.57424</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13646,12 +13646,12 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -13668,10 +13668,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.416882</v>
+        <v>-58.432319</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.562655</v>
+        <v>-34.574385</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13697,7 +13697,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13728,49 +13728,213 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>-58.416882</v>
+      </c>
+      <c r="N157" t="n">
+        <v>-34.562655</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>BLO-?</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10129 </t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ALVAREZ, JULIAN 1890</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>COLUMNA INCLINADA</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>-58.42056</v>
+      </c>
+      <c r="N158" t="n">
+        <v>-34.590217</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>VCR-D</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10131 </t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="J159" t="inlineStr">
         <is>
           <t>Nodo/Fuente Teco</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="K159" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L157" t="n">
-        <v>1</v>
-      </c>
-      <c r="M157" t="n">
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
         <v>-58.419652</v>
       </c>
-      <c r="N157" t="n">
+      <c r="N159" t="n">
         <v>-34.588271</v>
       </c>
-      <c r="O157" t="inlineStr">
+      <c r="O159" t="inlineStr">
         <is>
           <t>Palermo</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
         <is>
           <t>VCR-K</t>
         </is>
       </c>
-      <c r="R157" t="inlineStr">
+      <c r="R159" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R159"/>
+  <dimension ref="A1:R158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2379,22 +2379,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S00431877</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>4/11/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>URIBURU JOSE E., PRES. 1415</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>804634219</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2436,14 +2436,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.425764</v>
+        <v>-58.397031</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.604359</v>
+        <v>-34.591926</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2453,34 +2453,34 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>-338</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4/11/2025</t>
+          <t>4/21/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>URIBURU JOSE E., PRES. 1415</t>
+          <t>PARAGUAY /ALT/ 4283</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>804634219</t>
+          <t>804838861</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2522,14 +2522,14 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.397031</v>
+        <v>-58.421964</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.591926</v>
+        <v>-34.586342</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2539,29 +2539,29 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-338</t>
+          <t>805655355</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4/21/2025</t>
+          <t>5/5/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PARAGUAY /ALT/ 4283</t>
+          <t>Arce 867</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>804838861</t>
+          <t>805655355</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2608,10 +2608,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.421964</v>
+        <v>-58.436255</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.586342</v>
+        <v>-34.567733</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>805655355</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arce 867</t>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1520</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>805655355</t>
+          <t>805655369</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.436255</v>
+        <v>-58.432419</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.567733</v>
+        <v>-34.566431</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2723,17 +2723,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>805707165</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5/5/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MATIENZO, BENJAMIN, TENIENTE 1520</t>
+          <t>Baez 793</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>805655369</t>
+          <t>ICD30592749</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2780,10 +2780,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.432419</v>
+        <v>-58.436165</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.566431</v>
+        <v>-34.569081</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2809,17 +2809,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>805707165</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>5/6/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Baez 793</t>
+          <t>Soldado de la Independencia 1298</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ICD30592749</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
+          <t>Picada - Con fuente teco</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2854,36 +2854,36 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.436165</v>
+        <v>-58.440507</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.569081</v>
+        <v>-34.564016</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-K</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2895,17 +2895,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5/6/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Soldado de la Independencia 1298</t>
+          <t>Migueletes 1326</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Picada - Con fuente teco</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2952,10 +2952,10 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.440507</v>
+        <v>-58.440177</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.564016</v>
+        <v>-34.56291</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>-395</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Migueletes 1326</t>
+          <t>POSADAS 1567</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>805707278</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3038,24 +3038,24 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.440177</v>
+        <v>-58.387847</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.56291</v>
+        <v>-34.587043</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>BLO-K</t>
+          <t>RET-A</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3067,7 +3067,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-395</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>POSADAS 1567</t>
+          <t>CAMPOS, LUIS M. AV. 1336</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>805707278</t>
+          <t>805722772</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3124,24 +3124,24 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.387847</v>
+        <v>-58.44191</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.587043</v>
+        <v>-34.564245</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>RET-A</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>-416</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 1336</t>
+          <t>Paraguay 3765</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>805722772</t>
+          <t>806926557</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3210,24 +3210,24 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.44191</v>
+        <v>-58.416562</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.564245</v>
+        <v>-34.590589</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3239,7 +3239,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-416</t>
+          <t>-434</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paraguay 3765</t>
+          <t>Billinghurst 1478</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>806926557</t>
+          <t>806926806</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
+          <t xml:space="preserve">Columna base corroida con Nap y ganancias de ambas compañias, </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3296,14 +3296,14 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.416562</v>
+        <v>-58.412302</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.590589</v>
+        <v>-34.59301</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3325,7 +3325,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-434</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Billinghurst 1478</t>
+          <t>JUNCAL 4559</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>806926806</t>
+          <t>806926927</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna base corroida con Nap y ganancias de ambas compañias, </t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3382,14 +3382,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.412302</v>
+        <v>-58.423116</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.59301</v>
+        <v>-34.576984</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>VCR-N</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3411,17 +3411,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>-451</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JUNCAL 4559</t>
+          <t>Uriarte 2426</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>806926927</t>
+          <t>807044071</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3468,10 +3468,10 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.423116</v>
+        <v>-58.423551</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.576984</v>
+        <v>-34.581258</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>VCR-N</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3497,17 +3497,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-451</t>
+          <t>-482</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uriarte 2426</t>
+          <t>Av. Coronel Diaz 2596</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3527,14 +3527,10 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>807044071</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
-        </is>
-      </c>
+          <t>807605730</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -3542,7 +3538,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3554,14 +3550,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.423551</v>
+        <v>-58.405761</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.581258</v>
+        <v>-34.582476</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3571,7 +3567,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3583,7 +3579,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-482</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3593,7 +3589,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Av. Coronel Diaz 2596</t>
+          <t>CABELLO 3486</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3613,10 +3609,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>807605730</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>807658640</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Columna inclinada evaluar con inspector un corrimiento</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -3636,14 +3636,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.405761</v>
+        <v>-58.409579</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.582476</v>
+        <v>-34.581134</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3665,17 +3665,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>-486</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6/18/2025</t>
+          <t>6/23/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CABELLO 3486</t>
+          <t>Del Libertador 4596</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>807658640</t>
+          <t>807762871</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Columna inclinada evaluar con inspector un corrimiento</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3722,10 +3722,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.409579</v>
+        <v>-58.432241</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.581134</v>
+        <v>-34.56642</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3751,17 +3751,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-486</t>
+          <t>-501</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6/23/2025</t>
+          <t>7/3/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Del Libertador 4596</t>
+          <t>Cabello 3107</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>807762871</t>
+          <t>807971967</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3801,21 +3801,21 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.432241</v>
+        <v>-58.405749</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.56642</v>
+        <v>-34.58224</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3837,17 +3837,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-501</t>
+          <t>-517</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7/3/2025</t>
+          <t>7/16/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cabello 3107</t>
+          <t>Av Dorrego 2721</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3867,17 +3867,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>807971967</t>
+          <t>808373635</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3887,21 +3887,21 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.405749</v>
+        <v>-58.432805</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.58224</v>
+        <v>-34.574345</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3923,22 +3923,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-517</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7/16/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Av Dorrego 2721</t>
+          <t>URUGUAY 1094</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>808373635</t>
+          <t>808430941</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3973,21 +3973,21 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.432805</v>
+        <v>-58.387175</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.574345</v>
+        <v>-34.596</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4009,22 +4009,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>-523</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>7/20/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>URUGUAY 1094</t>
+          <t>Luis Maria Campos 585</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>808430941</t>
+          <t>808460898</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4059,21 +4059,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.387175</v>
+        <v>-58.434668</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.596</v>
+        <v>-34.571258</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4095,17 +4095,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-523</t>
+          <t>-524</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7/20/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 585</t>
+          <t>Luis Maria Campos 509</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>808460898</t>
+          <t>808460897</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4152,10 +4152,10 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.434668</v>
+        <v>-58.434194</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.571258</v>
+        <v>-34.571754</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4181,17 +4181,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-524</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 509</t>
+          <t>GASCON 1195</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>808460897</t>
+          <t>808571975</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4238,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.434194</v>
+        <v>-58.423127</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.571754</v>
+        <v>-34.596476</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GASCON 1195</t>
+          <t>DORREGO AV. 2687</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>808571980</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.423127</v>
+        <v>-58.433295</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.596476</v>
+        <v>-34.574305</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>-533</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2687</t>
+          <t>Bonpland 2233</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>808571980</t>
+          <t>808571985</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t xml:space="preserve">Cambiar columna y colocar rienda a pique </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4403,17 +4403,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.433295</v>
+        <v>-58.43258</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.574305</v>
+        <v>-34.579265</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4439,22 +4439,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-533</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>8/6/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bonpland 2233</t>
+          <t>BERUTI 2496</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4469,17 +4469,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>808571985</t>
+          <t>808733917</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar columna y colocar rienda a pique </t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4489,21 +4489,21 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.43258</v>
+        <v>-58.401374</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.579265</v>
+        <v>-34.592623</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4513,29 +4513,29 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>S00946632</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8/6/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BERUTI 2496</t>
+          <t>BERUTI 2592</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4555,17 +4555,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>808733917</t>
+          <t>808918705</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Traspaso de redes y retiro de columna</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4582,10 +4582,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.401374</v>
+        <v>-58.402657</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.592623</v>
+        <v>-34.592182</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4599,34 +4599,34 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S00946632</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/20/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BERUTI 2592</t>
+          <t>ARENALES 3640</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>808918705</t>
+          <t>ICD30449342</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna</t>
+          <t>Pendiente de desmonte icd Colocacion ICD30449342</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4668,14 +4668,14 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.402657</v>
+        <v>-58.413584</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.592182</v>
+        <v>-34.58551</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4697,7 +4697,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ARENALES 3640</t>
+          <t>CHARCAS 3986</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ICD30449342</t>
+          <t>809065854</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pendiente de desmonte icd Colocacion ICD30449342</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4754,10 +4754,10 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.413584</v>
+        <v>-58.419711</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.58551</v>
+        <v>-34.586299</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4783,17 +4783,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8/20/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CHARCAS 3986</t>
+          <t>GORRITI 4417</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>809065854</t>
+          <t>809526157</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4840,10 +4840,10 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.419711</v>
+        <v>-58.425358</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.586299</v>
+        <v>-34.593308</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GORRITI 4417</t>
+          <t>NICARAGUA 5510</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>809526157</t>
+          <t>809526162</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4926,10 +4926,10 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.425358</v>
+        <v>-58.432726</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.593308</v>
+        <v>-34.582328</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4955,17 +4955,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NICARAGUA 5510</t>
+          <t>Dorrego 2265</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>809526162</t>
+          <t>809837500</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5012,10 +5012,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.432726</v>
+        <v>-58.438083</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.582328</v>
+        <v>-34.577107</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5041,17 +5041,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dorrego 2265</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>809837500</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5098,10 +5098,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.438083</v>
+        <v>-58.429159</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.577107</v>
+        <v>-34.577821</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5127,22 +5127,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>S00936008</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/30/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>Azcuenaga 1645</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>01095943</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>picada colocar R200 para pedir traspaso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5184,14 +5184,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.429159</v>
+        <v>-58.397092</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.577821</v>
+        <v>-34.590173</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5201,34 +5201,34 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S00936008</t>
+          <t>-629</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9/30/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Azcuenaga 1645</t>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01095943</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>picada colocar R200 para pedir traspaso</t>
+          <t>Colocar R400 para posterior traspaso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5270,14 +5270,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.397092</v>
+        <v>-58.422406</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.590173</v>
+        <v>-34.577085</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5287,29 +5287,29 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-629</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fray Justo Santa Maria de Oro 2730</t>
+          <t>NEWBERY, JORGE 2696</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ICD31463422</t>
+          <t>810421921</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Colocar R400 para posterior traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5344,22 +5344,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.422406</v>
+        <v>-58.44293</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.577085</v>
+        <v>-34.574483</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5385,27 +5385,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2696</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810421921</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5430,26 +5430,26 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.44293</v>
+        <v>-58.4018</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.574483</v>
+        <v>-34.590471</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5471,27 +5471,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5525,17 +5525,17 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.4018</v>
+        <v>-58.417634</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.590471</v>
+        <v>-34.587439</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5557,17 +5557,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5614,10 +5614,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.417634</v>
+        <v>-58.440031</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.587439</v>
+        <v>-34.575409</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5643,17 +5643,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>UGARTECHE 3079</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5673,22 +5673,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t xml:space="preserve">01638326 </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5700,10 +5700,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.440031</v>
+        <v>-58.411934</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.575409</v>
+        <v>-34.580653</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5729,17 +5729,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UGARTECHE 3079</t>
+          <t>Paraguay 4301</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5759,17 +5759,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638326 </t>
+          <t>810853935</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
+          <t>Cambio de columna propia corroida en base</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5786,10 +5786,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.411934</v>
+        <v>-58.422434</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.580653</v>
+        <v>-34.585978</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5815,17 +5815,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>S00785128</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paraguay 4301</t>
+          <t>Paraguay 5055</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810853935</t>
+          <t>810877555</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cambio de columna propia corroida en base</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5872,10 +5872,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.422434</v>
+        <v>-58.429394</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.585978</v>
+        <v>-34.580587</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5901,7 +5901,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S00785128</t>
+          <t>S00566892</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paraguay 5055</t>
+          <t xml:space="preserve">SANTA FE AV. 3711 </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810877555</t>
+          <t>810877633</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5958,10 +5958,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.429394</v>
+        <v>-58.416063</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.580587</v>
+        <v>-34.584975</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5987,22 +5987,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S00566892</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE AV. 3711 </t>
+          <t>URUGUAY 1070</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>810877633</t>
+          <t>810984538</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6044,14 +6044,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.416063</v>
+        <v>-58.387161</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.584975</v>
+        <v>-34.596255</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6073,7 +6073,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>URUGUAY 1070</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810984538</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6130,10 +6130,10 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.387161</v>
+        <v>-58.390974</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.596255</v>
+        <v>-34.594177</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6159,17 +6159,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>-696</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>Las heras 3092</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811131649</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6204,22 +6204,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.390974</v>
+        <v>-58.405835</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.594177</v>
+        <v>-34.583573</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>-696</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Las heras 3092</t>
+          <t>AGUERO 2038</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6275,17 +6275,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811131649</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>Traspasar red a columna nueva y retirar la vieja</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6295,17 +6295,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.405835</v>
+        <v>-58.402647</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.583573</v>
+        <v>-34.588274</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>AGU-G</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6331,17 +6331,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AGUERO 2038</t>
+          <t>French 2377</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Traspasar red a columna nueva y retirar la vieja</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6388,10 +6388,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.402647</v>
+        <v>-58.398947</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.588274</v>
+        <v>-34.590946</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6405,19 +6405,19 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>AGU-G</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>French 2377</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>poste inclinado base quebrada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6467,17 +6467,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.398947</v>
+        <v>-58.403895</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.590946</v>
+        <v>-34.575559</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6491,19 +6491,19 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
+          <t>GURRUCHAGA 2473</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>poste inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6553,21 +6553,21 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.403895</v>
+        <v>-58.420304</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.575559</v>
+        <v>-34.582607</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>VCR-L</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6589,17 +6589,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>S01159828</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GURRUCHAGA 2473</t>
+          <t xml:space="preserve"> THAMES 2041</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6646,10 +6646,10 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.420304</v>
+        <v>-58.426667</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.582607</v>
+        <v>-34.585153</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>VCR-L</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6675,17 +6675,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S01159828</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> THAMES 2041</t>
+          <t>SOLER 4509</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6732,10 +6732,10 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.426667</v>
+        <v>-58.42336</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.585153</v>
+        <v>-34.588111</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SOLER 4509</t>
+          <t>DIAZ, CNEL. AV. 2512</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6806,26 +6806,26 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.42336</v>
+        <v>-58.406111</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.588111</v>
+        <v>-34.58316</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6847,22 +6847,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>01018482</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2512</t>
+          <t>AGUERO 2364</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t xml:space="preserve">02511365 </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.406111</v>
+        <v>-58.399462</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.58316</v>
+        <v>-34.585952</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6933,22 +6933,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01018482</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AGUERO 2364</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511365 </t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6990,14 +6990,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.399462</v>
+        <v>-58.436051</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.585952</v>
+        <v>-34.583855</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7019,7 +7019,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7076,10 +7076,10 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.436051</v>
+        <v>-58.437628</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.583855</v>
+        <v>-34.587953</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7105,7 +7105,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7162,10 +7162,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.437628</v>
+        <v>-58.439513</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.587953</v>
+        <v>-34.585314</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7191,7 +7191,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>01211534</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t xml:space="preserve"> JUNCAL 2490</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811454103</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7241,21 +7241,21 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.439513</v>
+        <v>-58.401685</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.585314</v>
+        <v>-34.591336</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7277,7 +7277,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>01211534</t>
+          <t>S01290507</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUNCAL 2490</t>
+          <t>CABELLO 3472</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811454103</t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7327,21 +7327,21 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.401685</v>
+        <v>-58.409438</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.591336</v>
+        <v>-34.58118</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7363,7 +7363,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S01290507</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CABELLO 3472</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7420,24 +7420,24 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.409438</v>
+        <v>-58.444955</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.58118</v>
+        <v>-34.569791</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7449,17 +7449,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>DIAZ, CNEL. AV. 2599</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7499,31 +7499,31 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.444955</v>
+        <v>-58.405559</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.569791</v>
+        <v>-34.582478</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7535,17 +7535,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2599</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7592,14 +7592,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.405559</v>
+        <v>-58.432319</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.582478</v>
+        <v>-34.574385</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7621,22 +7621,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>-735</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>Beruti 3012</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -7675,17 +7675,17 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.432319</v>
+        <v>-58.406584</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.574385</v>
+        <v>-34.589518</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-E</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7707,22 +7707,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-735</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Beruti 3012</t>
+          <t>Costa Rica 5741</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7761,17 +7761,17 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.406584</v>
+        <v>-58.436073</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.589518</v>
+        <v>-34.581506</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>AGU-E</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Costa Rica 5741</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7850,10 +7850,10 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.436073</v>
+        <v>-58.413945</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.581506</v>
+        <v>-34.582774</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7879,7 +7879,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>CALLAO AV. 2014</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7936,14 +7936,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.413945</v>
+        <v>-58.386954</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.582774</v>
+        <v>-34.587337</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7965,7 +7965,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>S00066646</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CALLAO AV. 2014</t>
+          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8010,26 +8010,26 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.386954</v>
+        <v>-58.408259</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.587337</v>
+        <v>-34.580266</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8051,17 +8051,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S00066646</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8101,17 +8101,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L90" t="n">
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.408259</v>
+        <v>-58.432807</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.580266</v>
+        <v>-34.574343</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8137,17 +8137,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8194,10 +8194,10 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.432807</v>
+        <v>-58.432102</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.574343</v>
+        <v>-34.574248</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8223,17 +8223,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>SINCLAIR 3106</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8280,10 +8280,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.432102</v>
+        <v>-58.422892</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.574248</v>
+        <v>-34.573802</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8309,7 +8309,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>S01064368</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SINCLAIR 3106</t>
+          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8366,10 +8366,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.422892</v>
+        <v>-58.426552</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.573802</v>
+        <v>-34.592076</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8395,17 +8395,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S01064368</t>
+          <t>S01406817</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/3/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
+          <t>CAMPOS, LUIS M. AV. 155</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8445,17 +8445,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.426552</v>
+        <v>-58.431638</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.592076</v>
+        <v>-34.574344</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8481,17 +8481,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S01406817</t>
+          <t>S00165389</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3/3/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 155</t>
+          <t>HONDURAS AV. 3708</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8538,10 +8538,10 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.431638</v>
+        <v>-58.414717</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.574344</v>
+        <v>-34.594123</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-B</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8567,17 +8567,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S00165389</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HONDURAS AV. 3708</t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8617,17 +8617,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.414717</v>
+        <v>-58.436004</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.594123</v>
+        <v>-34.58156</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>VCR-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8653,7 +8653,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8710,10 +8710,10 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.436004</v>
+        <v>-58.435443</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.58156</v>
+        <v>-34.56693</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8739,22 +8739,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t>RODRIGUEZ PEÑA 1650</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8796,14 +8796,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.435443</v>
+        <v>-58.389533</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.56693</v>
+        <v>-34.591306</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8825,22 +8825,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEÑA 1650</t>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812879521</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8882,10 +8882,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.389533</v>
+        <v>-58.408769</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.591306</v>
+        <v>-34.587342</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8911,7 +8911,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+          <t>SEGUI JUAN FRANCISCO 4691</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812879521</t>
+          <t>812879559</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8968,14 +8968,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.408769</v>
+        <v>-58.422229</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.587342</v>
+        <v>-34.573148</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8997,17 +8997,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>00781500</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SEGUI JUAN FRANCISCO 4691</t>
+          <t>RAVIGNANI EMILIO DR 1498</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>812879559</t>
+          <t>812879925</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9054,10 +9054,10 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.422229</v>
+        <v>-58.441411</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.573148</v>
+        <v>-34.583443</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9083,22 +9083,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>00781500</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RAVIGNANI EMILIO DR 1498</t>
+          <t>JUNCAL 2249</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>812879925</t>
+          <t>812880742</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9140,14 +9140,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.441411</v>
+        <v>-58.399319</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.583443</v>
+        <v>-34.592221</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9157,34 +9157,34 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JUNCAL 2249</t>
+          <t>PARAGUAY 4237</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>812880742</t>
+          <t>813046389</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -9226,14 +9226,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.399319</v>
+        <v>-58.421616</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.592221</v>
+        <v>-34.586608</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9243,29 +9243,29 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>S00289486</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PARAGUAY 4237</t>
+          <t>PARAGUAY 4585</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>813046389</t>
+          <t>813046715</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9312,10 +9312,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.421616</v>
+        <v>-58.42498</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.586608</v>
+        <v>-34.584031</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9341,7 +9341,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S00289486</t>
+          <t>S00325208</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PARAGUAY 4585</t>
+          <t>PARAGUAY 3711</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>813046715</t>
+          <t>813046718</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9398,10 +9398,10 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.42498</v>
+        <v>-58.416117</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.584031</v>
+        <v>-34.590942</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-C</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9427,7 +9427,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S00325208</t>
+          <t>S00337251</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PARAGUAY 3711</t>
+          <t>SANCHEZ DE BUSTAMANTE 2450</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>813046718</t>
+          <t>813046724</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9484,14 +9484,14 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.416117</v>
+        <v>-58.403295</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.590942</v>
+        <v>-34.585041</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>VCR-C</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9513,7 +9513,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S00337251</t>
+          <t>S00364886</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 2450</t>
+          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>813046724</t>
+          <t>813046778</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9570,14 +9570,14 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.403295</v>
+        <v>-58.434778</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.585041</v>
+        <v>-34.569188</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9599,17 +9599,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S00364886</t>
+          <t>PJ00009</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
+          <t>THAMES 1516</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>813046778</t>
+          <t>813304793</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9656,10 +9656,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.434778</v>
+        <v>-58.431966</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.569188</v>
+        <v>-34.588553</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9685,22 +9685,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PJ00009</t>
+          <t>LR00001</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>THAMES 1516</t>
+          <t>BILLINGHURST 1796</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>813304793</t>
+          <t>813350523</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9742,14 +9742,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.431966</v>
+        <v>-58.409695</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.588553</v>
+        <v>-34.589662</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-D</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9771,22 +9771,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LR00001</t>
+          <t>PJ00040</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4/27/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BILLINGHURST 1796</t>
+          <t>HONDURAS 4822</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813350523</t>
+          <t>813350536</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9828,14 +9828,14 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.409695</v>
+        <v>-58.428528</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.589662</v>
+        <v>-34.589872</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>AGU-D</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9857,7 +9857,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>AF00001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>SALGUERO, JERONIMO 1995</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>813304889</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9914,10 +9914,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.428528</v>
+        <v>-58.413378</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.589872</v>
+        <v>-34.587254</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9943,7 +9943,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>CHARCAS 3250</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>813304917</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10000,14 +10000,14 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.413378</v>
+        <v>-58.41175</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.587254</v>
+        <v>-34.592173</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10029,7 +10029,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CHARCAS 3250</t>
+          <t>DORREGO AV.2752</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>813304917</t>
+          <t>813305004</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10086,14 +10086,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.41175</v>
+        <v>-58.43266</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.592173</v>
+        <v>-34.574202</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10115,7 +10115,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>S00419298</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DORREGO AV.2752</t>
+          <t>AUSTRIA 2354</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>813350615</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10172,14 +10172,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.43266</v>
+        <v>-58.401523</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.574202</v>
+        <v>-34.586182</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10201,22 +10201,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00419298</t>
+          <t>S0000223</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AUSTRIA 2354</t>
+          <t>ARENALES 3660</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>813350615</t>
+          <t>813352547</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10258,14 +10258,14 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.401523</v>
+        <v>-58.413732</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.586182</v>
+        <v>-34.585415</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10287,17 +10287,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S0000223</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/23/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ARENALES 3660</t>
+          <t>AV DORREGO 3900</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>813352568</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10337,17 +10337,17 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.413732</v>
+        <v>-58.418801</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.585415</v>
+        <v>-34.564182</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10373,17 +10373,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4/23/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AV DORREGO 3900</t>
+          <t>ALVAREZ, JULIAN 2552</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>813352568</t>
+          <t>813352603</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10423,17 +10423,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.418801</v>
+        <v>-58.413555</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.564182</v>
+        <v>-34.585955</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10459,17 +10459,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 2552</t>
+          <t>BULNES 2550</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10489,17 +10489,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>813352603</t>
+          <t>813631416</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10516,10 +10516,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.413555</v>
+        <v>-58.407013</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.585955</v>
+        <v>-34.582645</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10545,7 +10545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BULNES 2550</t>
+          <t>DEL LIBERTADOR AV. 2030</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>813631416</t>
+          <t>813631417</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10602,14 +10602,14 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.407013</v>
+        <v>-58.401882</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.582645</v>
+        <v>-34.582006</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10631,7 +10631,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 2030</t>
+          <t>CASTEX 3439</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10661,17 +10661,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>813631417</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10688,14 +10688,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.401882</v>
+        <v>-58.406414</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.582006</v>
+        <v>-34.577519</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10717,7 +10717,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CASTEX 3439</t>
+          <t>LACROZE, FEDERICO AV. 2338</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10747,17 +10747,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>813631425</t>
+          <t>813631432</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10774,24 +10774,24 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.406414</v>
+        <v>-58.444112</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.577519</v>
+        <v>-34.569261</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10803,7 +10803,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2338</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>813631432</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10860,24 +10860,24 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.444112</v>
+        <v>-58.438595</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.569261</v>
+        <v>-34.565168</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10889,7 +10889,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>813631446</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10946,10 +10946,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.438595</v>
+        <v>-58.437217</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.565168</v>
+        <v>-34.567174</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>813631449</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -11032,10 +11032,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.437217</v>
+        <v>-58.44018</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.567174</v>
+        <v>-34.565612</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813631451</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -11118,19 +11118,19 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.44018</v>
+        <v>-58.441718</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.565612</v>
+        <v>-34.566411</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -11147,22 +11147,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11177,17 +11177,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813631452</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -11204,24 +11204,24 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.441718</v>
+        <v>-58.402534</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.566411</v>
+        <v>-34.593133</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11233,17 +11233,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S00477293</t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARENALES 2552</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11261,11 +11261,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>813631921</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11290,10 +11286,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.402534</v>
+        <v>-58.385947</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.593133</v>
+        <v>-34.588156</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11307,7 +11303,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11319,7 +11315,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S01385955</t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11329,12 +11325,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>POSADAS 1391</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11350,12 +11346,12 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -11372,14 +11368,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.385947</v>
+        <v>-58.440439</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.588156</v>
+        <v>-34.575416</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11389,7 +11385,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11401,7 +11397,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t xml:space="preserve">9179 </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11411,7 +11407,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t>ARAOZ 2289</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11432,12 +11428,12 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11454,10 +11450,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.440439</v>
+        <v>-58.418131</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.575416</v>
+        <v>-34.58774</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11471,7 +11467,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11483,7 +11479,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179 </t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11493,7 +11489,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ARAOZ 2289</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11536,10 +11532,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.418131</v>
+        <v>-58.438274</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.58774</v>
+        <v>-34.564049</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11553,7 +11549,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11565,7 +11561,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11575,7 +11571,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11618,10 +11614,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.438274</v>
+        <v>-58.434721</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.564049</v>
+        <v>-34.567241</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11635,7 +11631,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11647,7 +11643,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11657,7 +11653,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11700,10 +11696,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.434721</v>
+        <v>-58.435738</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.567241</v>
+        <v>-34.564606</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11717,7 +11713,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11729,7 +11725,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11739,7 +11735,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11760,7 +11756,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11782,10 +11778,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.435738</v>
+        <v>-58.435011</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.564606</v>
+        <v>-34.56566</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11811,7 +11807,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11821,7 +11817,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11842,7 +11838,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11852,7 +11848,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11864,10 +11860,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.435011</v>
+        <v>-58.430774</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.56566</v>
+        <v>-34.568179</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11881,7 +11877,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11893,7 +11889,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11903,7 +11899,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11934,7 +11930,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11946,10 +11942,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.430774</v>
+        <v>-58.436255</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.568179</v>
+        <v>-34.567733</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11963,7 +11959,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11975,7 +11971,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11985,7 +11981,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12028,10 +12024,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.436255</v>
+        <v>-58.443403</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.567733</v>
+        <v>-34.575666</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12045,7 +12041,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12057,7 +12053,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12067,7 +12063,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12110,10 +12106,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.443403</v>
+        <v>-58.428639</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.575666</v>
+        <v>-34.59039</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12127,7 +12123,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12139,7 +12135,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12149,12 +12145,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12192,14 +12188,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.428639</v>
+        <v>-58.404726</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.59039</v>
+        <v>-34.596069</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12209,7 +12205,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12221,7 +12217,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12231,12 +12227,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12262,7 +12258,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12274,14 +12270,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.404726</v>
+        <v>-58.422183</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.596069</v>
+        <v>-34.576849</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12291,7 +12287,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12303,7 +12299,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12313,7 +12309,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12344,7 +12340,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -12356,10 +12352,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.422183</v>
+        <v>-58.425803</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.576849</v>
+        <v>-34.588513</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12373,7 +12369,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12385,7 +12381,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t xml:space="preserve">9945 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12395,7 +12391,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>LACROZE, FEDERICO AV. 1938</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12438,10 +12434,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.425803</v>
+        <v>-58.440759</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.588513</v>
+        <v>-34.565819</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12455,7 +12451,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -13287,7 +13283,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080 </t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13297,7 +13293,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>THAMES 549</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13318,12 +13314,12 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -13340,14 +13336,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.442534</v>
+        <v>-58.400188</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.59499</v>
+        <v>-34.583882</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13357,7 +13353,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13369,7 +13365,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">10082 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13379,7 +13375,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TAGLE 2562</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13400,12 +13396,12 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -13422,10 +13418,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.400188</v>
+        <v>-58.404652</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.583882</v>
+        <v>-34.58263</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13439,7 +13435,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13451,7 +13447,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13461,7 +13457,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13482,12 +13478,12 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13504,14 +13500,14 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.404652</v>
+        <v>-58.433857</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.58263</v>
+        <v>-34.57424</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13521,7 +13517,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13533,7 +13529,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13543,7 +13539,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13564,12 +13560,12 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -13586,10 +13582,10 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.433857</v>
+        <v>-58.432319</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.57424</v>
+        <v>-34.574385</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13615,7 +13611,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13625,7 +13621,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13646,12 +13642,12 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -13668,10 +13664,10 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.432319</v>
+        <v>-58.416882</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.574385</v>
+        <v>-34.562655</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13685,7 +13681,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13697,7 +13693,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104 </t>
+          <t xml:space="preserve">10129 </t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13707,7 +13703,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
+          <t>ALVAREZ, JULIAN 1890</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13728,12 +13724,12 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13743,17 +13739,17 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L157" t="n">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.416882</v>
+        <v>-58.42056</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.562655</v>
+        <v>-34.590217</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13767,7 +13763,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13779,7 +13775,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">10129 </t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13789,7 +13785,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 1890</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -13810,32 +13806,32 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.42056</v>
+        <v>-58.419652</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.590217</v>
+        <v>-34.588271</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13849,92 +13845,10 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10131 </t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L159" t="n">
-        <v>1</v>
-      </c>
-      <c r="M159" t="n">
-        <v>-58.419652</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-34.588271</v>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>VCR-K</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R154"/>
+  <dimension ref="A1:R148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,22 +925,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-647</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10/17/2024</t>
+          <t>11/5/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vicente López 1843</t>
+          <t>GODOY CRUZ 2604</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -955,41 +955,41 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01096066</t>
+          <t>799246642</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspasar fuente</t>
+          <t>Realizar traspasos y retiro de columna vieja</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-58.391371</v>
+        <v>-58.426169</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.590472</v>
+        <v>-34.579697</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>RET-A</t>
+          <t>VCR-N</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1011,22 +1011,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>-70</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11/5/2024</t>
+          <t>5/3/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GODOY CRUZ 2604</t>
+          <t>AGUERO /ALT/ 2310</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1041,17 +1041,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>799246642</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Realizar traspasos y retiro de columna vieja</t>
-        </is>
-      </c>
+          <t>784675618</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1061,21 +1057,21 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.426169</v>
+        <v>-58.400047</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.579697</v>
+        <v>-34.586358</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1085,7 +1081,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>VCR-N</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1097,17 +1093,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-201</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1/5/2024</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FIGUEROA ALCORTA PTE ,AV. /ALT/ 5600</t>
+          <t>MIGUELETES /ALT/ 1007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1127,12 +1123,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>777580740</t>
+          <t>799540497</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Es F. ALCORTA 5600 (pasando Av de los ombues 100mts aprox.) Para cambiar es un poste con muchas rajaduras, en Figueroa Alcorta esq. Av de los Ombues</t>
+          <t>reemplazo de columnas en mal estado Migueletes 1007 reemplazar columna 114 y colocar rienda a pique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1147,17 +1143,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.425911</v>
+        <v>-58.436377</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.56033</v>
+        <v>-34.565075</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1171,7 +1167,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1183,22 +1179,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2/7/2024</t>
+          <t>5/2/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FRENCH /ALT/ 2380</t>
+          <t>ORTIZ DE OCAMPO ,AV. /ALT/ 2635</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1213,10 +1209,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>780043028</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>784655947</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cambiar</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.39894</v>
+        <v>-58.404652</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.591084</v>
+        <v>-34.58263</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1253,34 +1253,34 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-51</t>
+          <t>803607889</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4/5/2024</t>
+          <t>2/19/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHARCAS /ALT/ 4176</t>
+          <t>Arenales 2548</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>782773317</t>
+          <t>803607889</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">columna de 114mm de nuestra propiedad que esta quebrada y en mal estado, para remplazar ubicada en CHARCAS 4176 </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1319,17 +1319,17 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.421741</v>
+        <v>-58.402534</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.584789</v>
+        <v>-34.593133</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1351,22 +1351,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-70</t>
+          <t>803608480</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5/3/2024</t>
+          <t>2/24/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AGUERO /ALT/ 2310</t>
+          <t>GUATEMALA /ALT/ 4415</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1381,10 +1381,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>784675618</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>803608480</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guatemala 4415 </t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -1404,14 +1408,14 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.400047</v>
+        <v>-58.421661</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.586358</v>
+        <v>-34.588428</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1433,17 +1437,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-103</t>
+          <t>-281</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6/12/2024</t>
+          <t>2/26/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SALGUERO JERONIMO /ALT/ 2533</t>
+          <t>SOLER /ALT/ 4517</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1463,12 +1467,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>788206681</t>
+          <t>803651203</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Altura correcta 2549</t>
+          <t>columna de 114 con nodo y redes nuestra.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1478,7 +1482,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1490,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.409971</v>
+        <v>-58.423405</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.58175</v>
+        <v>-34.588075</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1519,22 +1523,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>-201</t>
+          <t>803825124</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>3/7/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIGUELETES /ALT/ 1007</t>
+          <t>José A. Cabrera 3086</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1549,12 +1553,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>799540497</t>
+          <t>803825124</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>reemplazo de columnas en mal estado Migueletes 1007 reemplazar columna 114 y colocar rienda a pique</t>
+          <t>Desmontar columna y transferir a comunitaria</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1569,21 +1573,21 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.436377</v>
+        <v>-58.41002</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.565075</v>
+        <v>-34.596998</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-A</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1605,17 +1609,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-202</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>3/27/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MIGUELETES /ALT/ 1030</t>
+          <t>3 DE FEBRERO 990</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1635,12 +1639,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>799540503</t>
+          <t>804309752</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Recambio de columna - alt correcta 1010</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1659,13 +1663,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.436601</v>
+        <v>-58.442791</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.565035</v>
+        <v>-34.569495</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1679,7 +1683,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1691,17 +1695,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5/2/2024</t>
+          <t>3/28/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO ,AV. /ALT/ 2635</t>
+          <t>PRINGLES 1470</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1721,17 +1725,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>784655947</t>
+          <t>804316147</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1745,17 +1749,17 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.404652</v>
+        <v>-58.423996</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.58263</v>
+        <v>-34.594973</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1765,7 +1769,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1777,22 +1781,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>803607889</t>
+          <t>-312</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2/19/2025</t>
+          <t>3/29/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arenales 2548</t>
+          <t>MATIENZO BENJAMIN /ALT/ 1831</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1807,12 +1811,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>803607889</t>
+          <t>804333522</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Retirar columna ya traspasaron el nodo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1822,7 +1826,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1831,17 +1835,17 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.402534</v>
+        <v>-58.434835</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.593133</v>
+        <v>-34.569129</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1863,22 +1867,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>803608480</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2/24/2025</t>
+          <t>4/11/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GUATEMALA /ALT/ 4415</t>
+          <t>URIBURU JOSE E., PRES. 1415</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1893,12 +1897,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>803608480</t>
+          <t>804634219</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala 4415 </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1917,17 +1921,17 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.421661</v>
+        <v>-58.397031</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.588428</v>
+        <v>-34.591926</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1937,29 +1941,29 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>-281</t>
+          <t>-338</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2/26/2025</t>
+          <t>4/21/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOLER /ALT/ 4517</t>
+          <t>PARAGUAY /ALT/ 4283</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1979,12 +1983,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>803651203</t>
+          <t>804838861</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>columna de 114 con nodo y redes nuestra.</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1994,7 +1998,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2003,13 +2007,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.423405</v>
+        <v>-58.421964</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.588075</v>
+        <v>-34.586342</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2023,7 +2027,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2035,22 +2039,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>803825124</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3/7/2025</t>
+          <t>5/5/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>José A. Cabrera 3086</t>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1520</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2065,12 +2069,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>803825124</t>
+          <t>805655369</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Desmontar columna y transferir a comunitaria</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2085,21 +2089,21 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.41002</v>
+        <v>-58.432419</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.596998</v>
+        <v>-34.566431</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>VCR-A</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2121,17 +2125,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>805707165</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3/27/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3 DE FEBRERO 990</t>
+          <t>Baez 793</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2151,12 +2155,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>804309752</t>
+          <t>ICD30592749</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2178,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.442791</v>
+        <v>-58.436165</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.569495</v>
+        <v>-34.569081</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2195,7 +2199,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2207,17 +2211,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3/28/2025</t>
+          <t>5/6/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PRINGLES 1470</t>
+          <t>Soldado de la Independencia 1298</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2237,22 +2241,22 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>804316147</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada - Con fuente teco</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2264,24 +2268,24 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.423996</v>
+        <v>-58.440507</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.594973</v>
+        <v>-34.564016</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-K</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2293,17 +2297,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-312</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3/29/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN /ALT/ 1831</t>
+          <t>Migueletes 1326</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2323,12 +2327,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>804333522</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Retirar columna ya traspasaron el nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2338,7 +2342,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2347,27 +2351,27 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.434835</v>
+        <v>-58.440177</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.569129</v>
+        <v>-34.56291</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-K</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2379,17 +2383,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>-395</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4/11/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>URIBURU JOSE E., PRES. 1415</t>
+          <t>POSADAS 1567</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2409,7 +2413,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>804634219</t>
+          <t>805707278</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2436,10 +2440,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.397031</v>
+        <v>-58.387847</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.591926</v>
+        <v>-34.587043</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2453,29 +2457,29 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>RET-A</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-338</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4/21/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PARAGUAY /ALT/ 4283</t>
+          <t>CAMPOS, LUIS M. AV. 1336</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2495,7 +2499,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>804838861</t>
+          <t>805722772</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2522,24 +2526,24 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.421964</v>
+        <v>-58.44191</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.586342</v>
+        <v>-34.564245</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2551,17 +2555,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>-416</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5/5/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MATIENZO, BENJAMIN, TENIENTE 1520</t>
+          <t>Paraguay 3765</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2581,12 +2585,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>805655369</t>
+          <t>806926557</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2596,22 +2600,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.432419</v>
+        <v>-58.416562</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.566431</v>
+        <v>-34.590589</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2625,7 +2629,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2637,22 +2641,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>805707165</t>
+          <t>-434</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baez 793</t>
+          <t>Billinghurst 1478</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2667,12 +2671,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ICD30592749</t>
+          <t>806926806</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
+          <t xml:space="preserve">Columna base corroida con Nap y ganancias de ambas compañias, </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2687,21 +2691,21 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.436165</v>
+        <v>-58.412302</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.569081</v>
+        <v>-34.59301</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2711,7 +2715,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2723,17 +2727,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5/6/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Soldado de la Independencia 1298</t>
+          <t>JUNCAL 4559</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2753,12 +2757,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>806926927</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada - Con fuente teco</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2768,7 +2772,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2780,24 +2784,24 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.440507</v>
+        <v>-58.423116</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.564016</v>
+        <v>-34.576984</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>BLO-K</t>
+          <t>VCR-N</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2809,17 +2813,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>-451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Migueletes 1326</t>
+          <t>Uriarte 2426</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2839,12 +2843,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>807044071</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2854,7 +2858,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2866,24 +2870,24 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.440177</v>
+        <v>-58.423551</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.56291</v>
+        <v>-34.581258</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>BLO-K</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2895,22 +2899,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-395</t>
+          <t>-482</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>POSADAS 1567</t>
+          <t>Av. Coronel Diaz 2596</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2925,14 +2929,10 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>805707278</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Picada</t>
-        </is>
-      </c>
+          <t>807605730</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2952,10 +2952,10 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.387847</v>
+        <v>-58.405761</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.587043</v>
+        <v>-34.582476</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>RET-A</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2981,17 +2981,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>-486</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>6/23/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 1336</t>
+          <t>Del Libertador 4596</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>805722772</t>
+          <t>807762871</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3038,24 +3038,24 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.44191</v>
+        <v>-58.432241</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.564245</v>
+        <v>-34.56642</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3067,17 +3067,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-416</t>
+          <t>-501</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>7/3/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paraguay 3765</t>
+          <t>Cabello 3107</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3097,41 +3097,41 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>806926557</t>
+          <t>807971967</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.416562</v>
+        <v>-58.405749</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.590589</v>
+        <v>-34.58224</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3153,22 +3153,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-434</t>
+          <t>-517</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>7/16/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Billinghurst 1478</t>
+          <t>Av Dorrego 2721</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>806926806</t>
+          <t>808373635</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna base corroida con Nap y ganancias de ambas compañias, </t>
+          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3210,14 +3210,14 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.412302</v>
+        <v>-58.432805</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.59301</v>
+        <v>-34.574345</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3239,22 +3239,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JUNCAL 4559</t>
+          <t>URUGUAY 1094</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>806926927</t>
+          <t>808430941</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3284,26 +3284,26 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.423116</v>
+        <v>-58.387175</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.576984</v>
+        <v>-34.596</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>VCR-N</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3325,17 +3325,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-451</t>
+          <t>-523</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>7/20/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Uriarte 2426</t>
+          <t>Luis Maria Campos 585</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>807044071</t>
+          <t>808460898</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3382,10 +3382,10 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.423551</v>
+        <v>-58.434668</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.581258</v>
+        <v>-34.571258</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3411,17 +3411,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-482</t>
+          <t>-524</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6/18/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Av. Coronel Diaz 2596</t>
+          <t>Luis Maria Campos 509</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3441,10 +3441,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>807605730</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>808460897</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -3464,14 +3468,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.405761</v>
+        <v>-58.434194</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.582476</v>
+        <v>-34.571754</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3481,7 +3485,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3493,17 +3497,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-486</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6/23/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Del Libertador 4596</t>
+          <t>GASCON 1195</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3523,7 +3527,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>807762871</t>
+          <t>808571975</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3550,10 +3554,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.432241</v>
+        <v>-58.423127</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.56642</v>
+        <v>-34.596476</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3567,7 +3571,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3579,17 +3583,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-501</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7/3/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cabello 3107</t>
+          <t>DORREGO AV. 2687</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3609,17 +3613,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>807971967</t>
+          <t>808571980</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3629,21 +3633,21 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.405749</v>
+        <v>-58.433295</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.58224</v>
+        <v>-34.574305</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3653,7 +3657,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3665,17 +3669,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-517</t>
+          <t>-533</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7/16/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Av Dorrego 2721</t>
+          <t>Bonpland 2233</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3695,12 +3699,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>808373635</t>
+          <t>808571985</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
+          <t xml:space="preserve">Cambiar columna y colocar rienda a pique </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3715,17 +3719,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L39" t="n">
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.432805</v>
+        <v>-58.43258</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.574345</v>
+        <v>-34.579265</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3751,17 +3755,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>8/6/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>URUGUAY 1094</t>
+          <t>BERUTI 2496</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3781,17 +3785,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>808430941</t>
+          <t>808733917</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3801,17 +3805,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.387175</v>
+        <v>-58.401374</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.596</v>
+        <v>-34.592623</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3825,34 +3829,34 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-523</t>
+          <t>S00946632</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7/20/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 585</t>
+          <t>BERUTI 2592</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3867,12 +3871,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>808460898</t>
+          <t>808918705</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de redes y retiro de columna</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3894,14 +3898,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.434668</v>
+        <v>-58.402657</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.571258</v>
+        <v>-34.592182</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3911,7 +3915,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3923,17 +3927,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-524</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>8/20/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 509</t>
+          <t>CHARCAS 3986</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3953,7 +3957,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>808460897</t>
+          <t>809065854</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3980,10 +3984,10 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.434194</v>
+        <v>-58.419711</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.571754</v>
+        <v>-34.586299</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3997,7 +4001,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4009,17 +4013,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GASCON 1195</t>
+          <t>GORRITI 4417</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>809526157</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4066,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.423127</v>
+        <v>-58.425358</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.596476</v>
+        <v>-34.593308</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4095,17 +4099,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2687</t>
+          <t>NICARAGUA 5510</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4125,7 +4129,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>808571980</t>
+          <t>809526162</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4152,10 +4156,10 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.433295</v>
+        <v>-58.432726</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.574305</v>
+        <v>-34.582328</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4169,7 +4173,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4181,17 +4185,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-533</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bonpland 2233</t>
+          <t>Dorrego 2265</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4211,12 +4215,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>808571985</t>
+          <t>809837500</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar columna y colocar rienda a pique </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4231,17 +4235,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.43258</v>
+        <v>-58.438083</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.579265</v>
+        <v>-34.577107</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4255,7 +4259,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4267,22 +4271,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8/6/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BERUTI 2496</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4297,17 +4301,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>808733917</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4324,14 +4328,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.401374</v>
+        <v>-58.429159</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.592623</v>
+        <v>-34.577821</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4341,29 +4345,29 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S00946632</t>
+          <t>S00936008</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>9/30/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BERUTI 2592</t>
+          <t>Azcuenaga 1645</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4383,12 +4387,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>808918705</t>
+          <t>01095943</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna</t>
+          <t>picada colocar R200 para pedir traspaso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4398,7 +4402,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4410,10 +4414,10 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.402657</v>
+        <v>-58.397092</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.592182</v>
+        <v>-34.590173</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4427,29 +4431,29 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>-629</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8/20/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CHARCAS 3986</t>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4469,12 +4473,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>809065854</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para posterior traspaso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4496,10 +4500,10 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.419711</v>
+        <v>-58.422406</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.586299</v>
+        <v>-34.577085</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4513,7 +4517,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4525,17 +4529,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GORRITI 4417</t>
+          <t>NEWBERY, JORGE 2696</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4555,7 +4559,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>809526157</t>
+          <t>810421921</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4575,17 +4579,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.425358</v>
+        <v>-58.44293</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.593308</v>
+        <v>-34.574483</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4599,7 +4603,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4611,27 +4615,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NICARAGUA 5510</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4641,12 +4645,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>809526162</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4656,7 +4660,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4665,17 +4669,17 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.432726</v>
+        <v>-58.4018</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.582328</v>
+        <v>-34.590471</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4685,7 +4689,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4697,17 +4701,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dorrego 2265</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4727,12 +4731,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>809837500</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4754,10 +4758,10 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.438083</v>
+        <v>-58.417634</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.577107</v>
+        <v>-34.587439</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4771,7 +4775,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4783,17 +4787,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4813,12 +4817,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4828,7 +4832,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4840,10 +4844,10 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.429159</v>
+        <v>-58.440031</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.577821</v>
+        <v>-34.575409</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4857,7 +4861,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4869,22 +4873,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00936008</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azcuenaga 1645</t>
+          <t>UGARTECHE 3079</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4899,22 +4903,22 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01095943</t>
+          <t xml:space="preserve">01638326 </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>picada colocar R200 para pedir traspaso</t>
+          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4926,14 +4930,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.397092</v>
+        <v>-58.411934</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.590173</v>
+        <v>-34.580653</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4943,29 +4947,29 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>-629</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fray Justo Santa Maria de Oro 2730</t>
+          <t>Paraguay 4301</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4985,12 +4989,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ICD31463422</t>
+          <t>810853935</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Colocar R400 para posterior traspaso</t>
+          <t>Cambio de columna propia corroida en base</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5000,7 +5004,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5012,10 +5016,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.422406</v>
+        <v>-58.422434</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.577085</v>
+        <v>-34.585978</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5029,7 +5033,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5041,17 +5045,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>S00785128</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2696</t>
+          <t>Paraguay 5055</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5071,12 +5075,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810421921</t>
+          <t>810877555</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5091,17 +5095,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.44293</v>
+        <v>-58.429394</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.574483</v>
+        <v>-34.580587</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5115,7 +5119,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5127,27 +5131,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>S00566892</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t xml:space="preserve">SANTA FE AV. 3711 </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5157,12 +5161,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810877633</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5172,7 +5176,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5181,17 +5185,17 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.4018</v>
+        <v>-58.416063</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.590471</v>
+        <v>-34.584975</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5201,7 +5205,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5213,22 +5217,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>URUGUAY 1070</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5243,12 +5247,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810984538</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5270,14 +5274,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.417634</v>
+        <v>-58.387161</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.587439</v>
+        <v>-34.596255</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5287,7 +5291,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5299,22 +5303,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5329,12 +5333,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5344,7 +5348,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5356,14 +5360,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.440031</v>
+        <v>-58.390974</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.575409</v>
+        <v>-34.594177</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5373,7 +5377,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5385,22 +5389,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>-696</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UGARTECHE 3079</t>
+          <t>Las heras 3092</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5415,17 +5419,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638326 </t>
+          <t>811131649</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5435,21 +5439,21 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.411934</v>
+        <v>-58.405835</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.580653</v>
+        <v>-34.583573</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5471,22 +5475,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paraguay 4301</t>
+          <t>AGUERO 2038</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5501,17 +5505,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810853935</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Cambio de columna propia corroida en base</t>
+          <t>Traspasar red a columna nueva y retirar la vieja</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5528,14 +5532,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.422434</v>
+        <v>-58.402647</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.585978</v>
+        <v>-34.588274</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5545,7 +5549,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>AGU-G</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5557,22 +5561,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S00785128</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paraguay 5055</t>
+          <t>French 2377</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5587,7 +5591,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810877555</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5614,14 +5618,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.429394</v>
+        <v>-58.398947</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.580587</v>
+        <v>-34.590946</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5631,29 +5635,29 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S00566892</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE AV. 3711 </t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5673,12 +5677,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810877633</t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>poste inclinado base quebrada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5693,21 +5697,21 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.416063</v>
+        <v>-58.403895</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.584975</v>
+        <v>-34.575559</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5717,7 +5721,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5729,22 +5733,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>URUGUAY 1070</t>
+          <t>GURRUCHAGA 2473</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5759,12 +5763,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810984538</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5786,14 +5790,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.387161</v>
+        <v>-58.420304</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.596255</v>
+        <v>-34.582607</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5803,7 +5807,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>VCR-L</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5815,22 +5819,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>S01159828</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t xml:space="preserve"> THAMES 2041</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5845,12 +5849,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5860,7 +5864,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5872,14 +5876,14 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.390974</v>
+        <v>-58.426667</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.594177</v>
+        <v>-34.585153</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5889,7 +5893,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5901,22 +5905,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-696</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Las heras 3092</t>
+          <t>SOLER 4509</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5931,12 +5935,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811131649</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5946,26 +5950,26 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.405835</v>
+        <v>-58.42336</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.583573</v>
+        <v>-34.588111</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5975,7 +5979,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5987,22 +5991,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AGUERO 2038</t>
+          <t>DIAZ, CNEL. AV. 2512</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6017,17 +6021,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Traspasar red a columna nueva y retirar la vieja</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6037,17 +6041,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.402647</v>
+        <v>-58.406111</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.588274</v>
+        <v>-34.58316</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6061,7 +6065,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>AGU-G</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6073,17 +6077,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>01018482</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>French 2377</t>
+          <t>AGUERO 2364</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6103,12 +6107,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t xml:space="preserve">02511365 </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6118,7 +6122,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6130,10 +6134,10 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.398947</v>
+        <v>-58.399462</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.590946</v>
+        <v>-34.585952</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6147,29 +6151,29 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6189,12 +6193,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>poste inclinado base quebrada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6209,21 +6213,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.403895</v>
+        <v>-58.436051</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.575559</v>
+        <v>-34.583855</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6233,7 +6237,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6245,17 +6249,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>S01180023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GURRUCHAGA 2473</t>
+          <t>VEGA, NICETO, CNEL. AV. 5420</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6275,12 +6279,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6302,10 +6306,10 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.420304</v>
+        <v>-58.437628</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.582607</v>
+        <v>-34.587953</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6319,7 +6323,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>VCR-L</t>
+          <t>ATH-?</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6331,17 +6335,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S01159828</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> THAMES 2041</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6361,12 +6365,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6388,10 +6392,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.426667</v>
+        <v>-58.439513</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.585153</v>
+        <v>-34.585314</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6405,7 +6409,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6417,22 +6421,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>01211534</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SOLER 4509</t>
+          <t xml:space="preserve"> JUNCAL 2490</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6447,12 +6451,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811454103</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6462,26 +6466,26 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.42336</v>
+        <v>-58.401685</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.588111</v>
+        <v>-34.591336</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6491,7 +6495,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6503,17 +6507,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>S01290507</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2512</t>
+          <t>CABELLO 3472</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6533,12 +6537,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6553,21 +6557,21 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.406111</v>
+        <v>-58.409438</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.58316</v>
+        <v>-34.58118</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6577,7 +6581,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6589,22 +6593,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>01018482</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AGUERO 2364</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6619,12 +6623,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511365 </t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6634,36 +6638,36 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.399462</v>
+        <v>-58.444955</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.585952</v>
+        <v>-34.569791</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6675,17 +6679,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>DIAZ, CNEL. AV. 2599</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6705,12 +6709,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6732,14 +6736,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.436051</v>
+        <v>-58.405559</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.583855</v>
+        <v>-34.582478</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6749,7 +6753,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6761,17 +6765,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6791,12 +6795,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6818,10 +6822,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.437628</v>
+        <v>-58.432319</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.587953</v>
+        <v>-34.574385</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6835,7 +6839,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6847,22 +6851,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>-735</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t>Beruti 3012</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6877,12 +6881,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6892,7 +6896,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6901,17 +6905,17 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.439513</v>
+        <v>-58.406584</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.585314</v>
+        <v>-34.589518</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6921,7 +6925,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-E</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6933,22 +6937,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01211534</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUNCAL 2490</t>
+          <t>Costa Rica 5741</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6963,12 +6967,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811454103</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6983,21 +6987,21 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.401685</v>
+        <v>-58.436073</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.591336</v>
+        <v>-34.581506</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7007,7 +7011,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7019,17 +7023,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S01290507</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CABELLO 3472</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7049,12 +7053,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7069,17 +7073,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.409438</v>
+        <v>-58.413945</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.58118</v>
+        <v>-34.582774</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7093,7 +7097,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7105,22 +7109,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>CALLAO AV. 2014</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7135,7 +7139,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7150,36 +7154,36 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.444955</v>
+        <v>-58.386954</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.569791</v>
+        <v>-34.587337</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7191,17 +7195,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>S00066646</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2599</t>
+          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7221,12 +7225,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7241,21 +7245,21 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.405559</v>
+        <v>-58.408259</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.582478</v>
+        <v>-34.580266</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7265,7 +7269,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7277,17 +7281,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7307,12 +7311,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7334,10 +7338,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.432319</v>
+        <v>-58.432807</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.574385</v>
+        <v>-34.574343</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7363,22 +7367,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-735</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Beruti 3012</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7393,12 +7397,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7408,7 +7412,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7417,17 +7421,17 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.406584</v>
+        <v>-58.432102</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.589518</v>
+        <v>-34.574248</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7437,7 +7441,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>AGU-E</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7449,17 +7453,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Costa Rica 5741</t>
+          <t>SINCLAIR 3106</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7479,12 +7483,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7506,10 +7510,10 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.436073</v>
+        <v>-58.422892</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.581506</v>
+        <v>-34.573802</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7523,7 +7527,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7535,17 +7539,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>S01064368</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7565,12 +7569,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7592,10 +7596,10 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.413945</v>
+        <v>-58.426552</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.582774</v>
+        <v>-34.592076</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7609,7 +7613,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7621,22 +7625,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>S01406817</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>3/3/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CALLAO AV. 2014</t>
+          <t>CAMPOS, LUIS M. AV. 155</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7666,26 +7670,26 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L85" t="n">
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.386954</v>
+        <v>-58.431638</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.587337</v>
+        <v>-34.574344</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7695,7 +7699,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7707,17 +7711,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S00066646</t>
+          <t>S00165389</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
+          <t>HONDURAS AV. 3708</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7737,12 +7741,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7752,22 +7756,22 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.408259</v>
+        <v>-58.414717</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.580266</v>
+        <v>-34.594123</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7781,7 +7785,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>VCR-B</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7793,17 +7797,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7823,12 +7827,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7838,7 +7842,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7850,10 +7854,10 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.432807</v>
+        <v>-58.436004</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.574343</v>
+        <v>-34.58156</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7867,7 +7871,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7879,17 +7883,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7909,12 +7913,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7936,10 +7940,10 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.432102</v>
+        <v>-58.435443</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.574248</v>
+        <v>-34.56693</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7953,7 +7957,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7965,22 +7969,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SINCLAIR 3106</t>
+          <t>RODRIGUEZ PEÑA 1650</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7995,12 +7999,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8022,14 +8026,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.422892</v>
+        <v>-58.389533</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.573802</v>
+        <v>-34.591306</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8039,7 +8043,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8051,17 +8055,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S01064368</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8081,12 +8085,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>812879521</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8108,14 +8112,14 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.426552</v>
+        <v>-58.408769</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.592076</v>
+        <v>-34.587342</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8125,7 +8129,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8137,17 +8141,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S01406817</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3/3/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 155</t>
+          <t>SEGUI JUAN FRANCISCO 4691</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8167,12 +8171,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812879559</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8187,17 +8191,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.431638</v>
+        <v>-58.422229</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.574344</v>
+        <v>-34.573148</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8211,7 +8215,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8223,17 +8227,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S00165389</t>
+          <t>00781500</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HONDURAS AV. 3708</t>
+          <t>RAVIGNANI EMILIO DR 1498</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8253,12 +8257,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812879925</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8268,22 +8272,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.414717</v>
+        <v>-58.441411</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.594123</v>
+        <v>-34.583443</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8297,7 +8301,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>VCR-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8309,22 +8313,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>JUNCAL 2249</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8339,12 +8343,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812880742</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8354,7 +8358,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8366,14 +8370,14 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.436004</v>
+        <v>-58.399319</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.58156</v>
+        <v>-34.592221</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8383,29 +8387,29 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t>PARAGUAY 4237</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8425,12 +8429,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>813046389</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8440,7 +8444,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8452,10 +8456,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.435443</v>
+        <v>-58.421616</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.56693</v>
+        <v>-34.586608</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8469,7 +8473,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8481,22 +8485,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>S00289486</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEÑA 1650</t>
+          <t>PARAGUAY 4585</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8511,12 +8515,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>813046715</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8538,14 +8542,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.389533</v>
+        <v>-58.42498</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.591306</v>
+        <v>-34.584031</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8555,7 +8559,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8567,17 +8571,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>S00325208</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+          <t>PARAGUAY 3711</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8597,12 +8601,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>812879521</t>
+          <t>813046718</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8624,14 +8628,14 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.408769</v>
+        <v>-58.416117</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.587342</v>
+        <v>-34.590942</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8641,7 +8645,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>VCR-C</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8653,22 +8657,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>S00337251</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SEGUI JUAN FRANCISCO 4691</t>
+          <t>SANCHEZ DE BUSTAMANTE 2450</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8683,12 +8687,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812879559</t>
+          <t>813046724</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8710,14 +8714,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.422229</v>
+        <v>-58.403295</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.573148</v>
+        <v>-34.585041</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8727,7 +8731,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8739,17 +8743,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>00781500</t>
+          <t>S00364886</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RAVIGNANI EMILIO DR 1498</t>
+          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8769,7 +8773,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>812879925</t>
+          <t>813046778</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8796,10 +8800,10 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.441411</v>
+        <v>-58.434778</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.583443</v>
+        <v>-34.569188</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8813,7 +8817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8825,22 +8829,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>PJ00009</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JUNCAL 2249</t>
+          <t>THAMES 1516</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8855,7 +8859,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812880742</t>
+          <t>813304793</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8882,14 +8886,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.399319</v>
+        <v>-58.431966</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.592221</v>
+        <v>-34.588553</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8899,34 +8903,34 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>LR00001</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PARAGUAY 4237</t>
+          <t>BILLINGHURST 1796</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8941,7 +8945,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>813046389</t>
+          <t>813350523</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8956,7 +8960,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8968,14 +8972,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.421616</v>
+        <v>-58.409695</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.586608</v>
+        <v>-34.589662</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8985,7 +8989,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>AGU-D</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8997,17 +9001,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S00289486</t>
+          <t>PJ00040</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PARAGUAY 4585</t>
+          <t>HONDURAS 4822</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9027,7 +9031,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>813046715</t>
+          <t>813350536</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9037,7 +9041,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -9054,10 +9058,10 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.42498</v>
+        <v>-58.428528</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.584031</v>
+        <v>-34.589872</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9071,7 +9075,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9083,17 +9087,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S00325208</t>
+          <t>AF00001</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PARAGUAY 3711</t>
+          <t>SALGUERO, JERONIMO 1995</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9113,7 +9117,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>813046718</t>
+          <t>813304889</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9140,10 +9144,10 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.416117</v>
+        <v>-58.413378</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.590942</v>
+        <v>-34.587254</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9157,7 +9161,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>VCR-C</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9169,17 +9173,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S00337251</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 2450</t>
+          <t>CHARCAS 3250</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9199,7 +9203,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>813046724</t>
+          <t>813304917</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9226,14 +9230,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.403295</v>
+        <v>-58.41175</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.585041</v>
+        <v>-34.592173</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9243,7 +9247,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9255,17 +9259,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S00364886</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
+          <t>DORREGO AV.2752</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9285,7 +9289,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>813046778</t>
+          <t>813305004</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9312,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.434778</v>
+        <v>-58.43266</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.569188</v>
+        <v>-34.574202</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9329,7 +9333,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9341,7 +9345,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PJ00009</t>
+          <t>S00419298</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9351,12 +9355,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>THAMES 1516</t>
+          <t>AUSTRIA 2354</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9371,7 +9375,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>813304793</t>
+          <t>813350615</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9398,14 +9402,14 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.431966</v>
+        <v>-58.401523</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.588553</v>
+        <v>-34.586182</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9415,7 +9419,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9427,22 +9431,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LR00001</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4/27/2026</t>
+          <t>4/23/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BILLINGHURST 1796</t>
+          <t>AV DORREGO 3900</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9457,12 +9461,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>813350523</t>
+          <t>813352568</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9477,21 +9481,21 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.409695</v>
+        <v>-58.418801</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.589662</v>
+        <v>-34.564182</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9501,7 +9505,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>AGU-D</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9513,17 +9517,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>ALVAREZ, JULIAN 2552</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9543,7 +9547,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>813352603</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9553,7 +9557,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9570,10 +9574,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.428528</v>
+        <v>-58.413555</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.589872</v>
+        <v>-34.585955</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9587,7 +9591,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9599,17 +9603,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>BULNES 2550</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9629,17 +9633,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>813631416</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9656,10 +9660,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.413378</v>
+        <v>-58.407013</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.587254</v>
+        <v>-34.582645</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9673,7 +9677,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9685,22 +9689,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CHARCAS 3250</t>
+          <t>DEL LIBERTADOR AV. 2030</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9715,17 +9719,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>813304917</t>
+          <t>813631417</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9742,14 +9746,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.41175</v>
+        <v>-58.401882</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.592173</v>
+        <v>-34.582006</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9759,7 +9763,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9771,17 +9775,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DORREGO AV.2752</t>
+          <t>CASTEX 3439</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9801,7 +9805,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9828,10 +9832,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.43266</v>
+        <v>-58.406414</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.574202</v>
+        <v>-34.577519</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9845,7 +9849,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9857,22 +9861,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S00419298</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AUSTRIA 2354</t>
+          <t>LACROZE, FEDERICO AV. 2338</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9887,17 +9891,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>813350615</t>
+          <t>813631432</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9914,24 +9918,24 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.401523</v>
+        <v>-58.444112</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.586182</v>
+        <v>-34.569261</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9943,17 +9947,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4/23/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AV DORREGO 3900</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9973,12 +9977,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>813352568</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -9993,17 +9997,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.418801</v>
+        <v>-58.438595</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.564182</v>
+        <v>-34.565168</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10017,7 +10021,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10029,17 +10033,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 2552</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10059,17 +10063,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>813352603</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10086,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.413555</v>
+        <v>-58.437217</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.585955</v>
+        <v>-34.567174</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10103,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10115,7 +10119,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10125,7 +10129,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BULNES 2550</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10145,17 +10149,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>813631416</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -10172,10 +10176,10 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.407013</v>
+        <v>-58.44018</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.582645</v>
+        <v>-34.565612</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10189,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10201,7 +10205,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10211,7 +10215,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 2030</t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10231,7 +10235,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>813631417</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10258,24 +10262,24 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.401882</v>
+        <v>-58.441718</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.582006</v>
+        <v>-34.566411</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10287,22 +10291,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CASTEX 3439</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10317,7 +10321,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>813631425</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10344,14 +10348,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.406414</v>
+        <v>-58.402534</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.577519</v>
+        <v>-34.593133</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10361,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10373,22 +10377,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2338</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10401,19 +10405,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>813631432</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -10430,24 +10430,24 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.444112</v>
+        <v>-58.385947</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.569261</v>
+        <v>-34.588156</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10459,17 +10459,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10487,11 +10487,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>813631446</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -10499,7 +10495,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10516,10 +10512,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.438595</v>
+        <v>-58.440439</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.565168</v>
+        <v>-34.575416</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10533,7 +10529,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10545,17 +10541,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t xml:space="preserve">9179 </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t>ARAOZ 2289</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10573,19 +10569,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>813631449</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10602,10 +10594,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.437217</v>
+        <v>-58.418131</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.567174</v>
+        <v>-34.58774</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10619,7 +10611,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10631,17 +10623,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10659,11 +10651,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>813631451</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -10688,10 +10676,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.44018</v>
+        <v>-58.438274</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.565612</v>
+        <v>-34.564049</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10705,7 +10693,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10717,17 +10705,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10745,19 +10733,15 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>813631452</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10774,24 +10758,24 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.441718</v>
+        <v>-58.434721</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.566411</v>
+        <v>-34.567241</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10803,22 +10787,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S00477293</t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARENALES 2552</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10831,11 +10815,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>813631921</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -10860,14 +10840,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.402534</v>
+        <v>-58.435738</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.593133</v>
+        <v>-34.564606</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10877,7 +10857,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10889,7 +10869,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S01385955</t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10899,12 +10879,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>POSADAS 1391</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10920,7 +10900,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10942,14 +10922,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.385947</v>
+        <v>-58.435011</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.588156</v>
+        <v>-34.56566</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10959,7 +10939,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10971,7 +10951,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10981,7 +10961,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11002,17 +10982,17 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -11024,10 +11004,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.440439</v>
+        <v>-58.430774</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.575416</v>
+        <v>-34.568179</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11041,7 +11021,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11053,7 +11033,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179 </t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11063,7 +11043,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ARAOZ 2289</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11106,10 +11086,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.418131</v>
+        <v>-58.436255</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.58774</v>
+        <v>-34.567733</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11123,7 +11103,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11135,7 +11115,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11145,7 +11125,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11188,10 +11168,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.438274</v>
+        <v>-58.443403</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.564049</v>
+        <v>-34.575666</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11205,7 +11185,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11217,7 +11197,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11227,7 +11207,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11270,10 +11250,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.434721</v>
+        <v>-58.428639</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.567241</v>
+        <v>-34.59039</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11287,7 +11267,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11299,7 +11279,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11309,12 +11289,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11352,14 +11332,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.435738</v>
+        <v>-58.404726</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.564606</v>
+        <v>-34.596069</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11369,7 +11349,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11381,7 +11361,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11391,7 +11371,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11412,7 +11392,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11422,7 +11402,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -11434,10 +11414,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.435011</v>
+        <v>-58.422183</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.56566</v>
+        <v>-34.576849</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11451,7 +11431,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11463,7 +11443,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11473,7 +11453,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11504,7 +11484,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -11516,10 +11496,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.430774</v>
+        <v>-58.425803</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.568179</v>
+        <v>-34.588513</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11533,7 +11513,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11545,7 +11525,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">9945 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11555,7 +11535,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>LACROZE, FEDERICO AV. 1938</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11598,10 +11578,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.436255</v>
+        <v>-58.440759</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.567733</v>
+        <v>-34.565819</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11615,7 +11595,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11627,17 +11607,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11658,17 +11638,17 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -11680,10 +11660,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.443403</v>
+        <v>-58.424388</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.575666</v>
+        <v>-34.59632</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11697,7 +11677,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11709,17 +11689,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11762,10 +11742,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.428639</v>
+        <v>-58.427895</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.59039</v>
+        <v>-34.583677</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11779,7 +11759,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11791,22 +11771,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t xml:space="preserve">9924 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>CORDOBA AV. 4089</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11844,14 +11824,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.404726</v>
+        <v>-58.424553</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.596069</v>
+        <v>-34.59709</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11861,7 +11841,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11873,17 +11853,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11904,17 +11884,17 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11926,10 +11906,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.422183</v>
+        <v>-58.440973</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.576849</v>
+        <v>-34.572415</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11943,7 +11923,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11955,22 +11935,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -11986,17 +11966,17 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12008,14 +11988,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.425803</v>
+        <v>-58.40382</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.588513</v>
+        <v>-34.594385</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12025,7 +12005,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12037,17 +12017,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9945 </t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 1938</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12090,10 +12070,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.440759</v>
+        <v>-58.43218</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.565819</v>
+        <v>-34.578546</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12107,7 +12087,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12119,7 +12099,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12129,7 +12109,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12150,17 +12130,17 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -12172,10 +12152,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.424388</v>
+        <v>-58.436737</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.59632</v>
+        <v>-34.58597</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12189,7 +12169,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12201,7 +12181,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12211,7 +12191,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12232,12 +12212,12 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -12254,10 +12234,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.427895</v>
+        <v>-58.413584</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.583677</v>
+        <v>-34.58551</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12271,7 +12251,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12283,7 +12263,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12293,7 +12273,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12314,17 +12294,17 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -12336,10 +12316,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.424553</v>
+        <v>-58.415912</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.59709</v>
+        <v>-34.588977</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12353,7 +12333,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12365,7 +12345,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12375,7 +12355,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12418,10 +12398,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.440973</v>
+        <v>-58.413885</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.572415</v>
+        <v>-34.586628</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12435,7 +12415,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12447,7 +12427,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12457,12 +12437,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12478,17 +12458,17 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -12500,10 +12480,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.40382</v>
+        <v>-58.400188</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.594385</v>
+        <v>-34.583882</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12517,7 +12497,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12529,7 +12509,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12539,7 +12519,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12560,12 +12540,12 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -12582,14 +12562,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.43218</v>
+        <v>-58.404652</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.578546</v>
+        <v>-34.58263</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12599,7 +12579,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12611,7 +12591,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12621,7 +12601,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12664,10 +12644,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.436737</v>
+        <v>-58.433857</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.58597</v>
+        <v>-34.57424</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12681,7 +12661,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12693,7 +12673,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12703,7 +12683,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12724,12 +12704,12 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -12746,10 +12726,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.413584</v>
+        <v>-58.432319</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.58551</v>
+        <v>-34.574385</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12763,7 +12743,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12775,7 +12755,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12785,7 +12765,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12806,17 +12786,17 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12828,10 +12808,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.415912</v>
+        <v>-58.416882</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.588977</v>
+        <v>-34.562655</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12845,7 +12825,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12857,7 +12837,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">10129 </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12867,7 +12847,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t>ALVAREZ, JULIAN 1890</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12903,17 +12883,17 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.413885</v>
+        <v>-58.42056</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.586628</v>
+        <v>-34.590217</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -12927,7 +12907,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -12939,7 +12919,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">10082 </t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12949,7 +12929,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TAGLE 2562</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12980,7 +12960,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -12992,14 +12972,14 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.400188</v>
+        <v>-58.419652</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.583882</v>
+        <v>-34.588271</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13009,502 +12989,10 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10083 </t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="n">
-        <v>-58.404652</v>
-      </c>
-      <c r="N149" t="n">
-        <v>-34.58263</v>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>AGU-N</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10098 </t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>DORREGO AV. 2635</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L150" t="n">
-        <v>1</v>
-      </c>
-      <c r="M150" t="n">
-        <v>-58.433857</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-34.57424</v>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>BLO-G</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10103 </t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>DORREGO AV. 2765</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L151" t="n">
-        <v>1</v>
-      </c>
-      <c r="M151" t="n">
-        <v>-58.432319</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-34.574385</v>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>BLO-G</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10104 </t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="n">
-        <v>-58.416882</v>
-      </c>
-      <c r="N152" t="n">
-        <v>-34.562655</v>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>BLO-?</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10129 </t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ALVAREZ, JULIAN 1890</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L153" t="n">
-        <v>1</v>
-      </c>
-      <c r="M153" t="n">
-        <v>-58.42056</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-34.590217</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>VCR-D</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10131 </t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Nodo/Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L154" t="n">
-        <v>1</v>
-      </c>
-      <c r="M154" t="n">
-        <v>-58.419652</v>
-      </c>
-      <c r="N154" t="n">
-        <v>-34.588271</v>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>VCR-K</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -7655,7 +7655,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105825</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107507</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107596</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10405,7 +10405,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>814108527</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -10569,7 +10573,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>814108607</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -10651,7 +10659,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>814108619</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -10733,7 +10745,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>814108632</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -10815,7 +10831,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>814108642</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -10897,7 +10917,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>814108650</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
@@ -11061,7 +11085,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>814108660</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11143,7 +11171,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>814109172</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11225,7 +11257,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>814109219</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11717,7 +11753,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>814108116</t>
+        </is>
+      </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11799,7 +11839,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>814108196</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12045,7 +12089,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>814108322</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12127,7 +12175,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>814108343</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12455,7 +12507,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>814108377</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12619,7 +12675,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>814108458</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12783,7 +12843,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>814108469</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMBIAR COLUMNA </t>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -11343,7 +11343,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>814109418</t>
+        </is>
+      </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11507,7 +11511,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>814109740</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11589,7 +11597,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>814109788</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R148"/>
+  <dimension ref="A1:R155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,17 +439,17 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>OT</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>ICD30334341</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ICD30334341</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -613,17 +613,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>791764767</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>791764767</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -699,17 +699,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>798897149</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>798897149</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -781,17 +781,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>798897163</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>798897163</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>798897384</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>798897384</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -945,17 +945,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>799246642</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>799246642</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>784675618</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>784675618</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1113,17 +1113,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>799540497</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>799540497</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>784655947</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>784655947</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803607889</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>803607889</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803608480</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>803608480</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803651203</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>803651203</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803825124</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>803825124</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804309752</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>804309752</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804316147</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>804316147</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1801,17 +1801,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804333522</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>804333522</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804634219</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>804634219</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804838861</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>804838861</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805655369</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>805655369</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD30592749</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ICD30592749</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2317,17 +2317,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805707278</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>805707278</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>805722772</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>805722772</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926557</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>806926557</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926806</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>806926806</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926927</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>806926927</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2833,17 +2833,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807044071</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>807044071</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807605730</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>807605730</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -3001,17 +3001,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807762871</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>807762871</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807971967</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>807971967</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808373635</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>808373635</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808430941</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>808430941</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3345,17 +3345,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808460898</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>808460898</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808460897</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>808460897</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3517,17 +3517,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808571975</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3603,17 +3603,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808571980</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>808571980</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808571985</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>808571985</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808733917</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>808733917</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808918705</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>808918705</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809065854</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>809065854</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809526157</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>809526157</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4119,17 +4119,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809526162</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>809526162</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809837500</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>809837500</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>01095943</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01095943</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ICD31463422</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4549,17 +4549,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810421921</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810421921</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>01230434</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4807,17 +4807,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4893,17 +4893,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t xml:space="preserve">01638326 </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638326 </t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4979,17 +4979,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810853935</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810853935</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5065,17 +5065,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810877555</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810877555</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5151,17 +5151,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810877633</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810877633</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5237,17 +5237,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810984538</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810984538</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5323,17 +5323,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811131649</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811131649</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5495,17 +5495,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5581,17 +5581,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5667,17 +5667,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5839,17 +5839,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6011,17 +6011,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t xml:space="preserve">02511365 </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511365 </t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6269,17 +6269,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811454198</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6355,17 +6355,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811454103</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811454103</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6527,17 +6527,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6613,17 +6613,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6699,17 +6699,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6785,17 +6785,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6957,17 +6957,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7043,17 +7043,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7129,17 +7129,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7215,17 +7215,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7301,17 +7301,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7387,17 +7387,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7473,17 +7473,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7559,17 +7559,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814105825</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>814105825</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7731,17 +7731,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7903,17 +7903,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814107507</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>814107507</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7989,17 +7989,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814107596</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>814107596</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812879521</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>812879521</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8161,17 +8161,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812879559</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>812879559</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8247,17 +8247,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812879925</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812879925</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812880742</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812880742</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8419,17 +8419,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046389</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>813046389</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8505,17 +8505,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046715</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>813046715</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046718</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>813046718</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046724</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>813046724</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8763,17 +8763,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046778</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>813046778</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8849,17 +8849,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813304793</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>813304793</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8935,17 +8935,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813350523</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>813350523</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9021,17 +9021,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813350536</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9107,17 +9107,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813304889</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9193,17 +9193,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813304917</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>813304917</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9279,17 +9279,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813305004</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813350615</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>813350615</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352568</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>813352568</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9537,17 +9537,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352603</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>813352603</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9623,17 +9623,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631416</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>813631416</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9709,17 +9709,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631417</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>813631417</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9795,17 +9795,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813631425</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9881,17 +9881,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631432</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>813631432</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9967,17 +9967,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>813631446</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10053,17 +10053,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>813631449</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10139,17 +10139,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>813631451</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10225,17 +10225,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>813631452</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>813631921</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10397,17 +10397,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108527</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>814108527</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10483,15 +10483,19 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814111029</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -10499,7 +10503,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10565,17 +10569,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108607</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>814108607</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10651,17 +10655,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108619</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>814108619</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10737,17 +10741,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108632</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>814108632</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10823,17 +10827,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108642</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>814108642</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10909,17 +10913,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108650</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>814108650</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10993,17 +10997,17 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11077,17 +11081,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108660</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>814108660</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11163,17 +11167,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109172</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>814109172</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11249,17 +11253,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109219</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>814109219</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11335,17 +11339,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109418</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>814109418</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11419,17 +11423,17 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -11503,17 +11507,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109740</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>814109740</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -11589,17 +11593,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109788</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>814109788</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11673,17 +11677,17 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -11757,17 +11761,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108116</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>814108116</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11843,17 +11847,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108196</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>814108196</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11929,15 +11933,19 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814111706</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -11945,7 +11953,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -12009,17 +12017,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -12093,17 +12101,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108322</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>814108322</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12179,17 +12187,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108343</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>814108343</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12263,17 +12271,17 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>DESMONTAR COLUMNA</t>
@@ -12345,17 +12353,17 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -12429,15 +12437,19 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814111751</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -12445,7 +12457,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -12511,17 +12523,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108377</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>814108377</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -12597,15 +12609,19 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814111784</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -12613,7 +12629,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -12679,17 +12695,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108458</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>814108458</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -12765,15 +12781,19 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814111791</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -12781,7 +12801,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -12847,17 +12867,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108469</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>814108469</t>
+          <t>PEBCOM</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -12933,15 +12953,19 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814111804</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -12949,7 +12973,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -13013,17 +13037,17 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -13069,6 +13093,608 @@
         </is>
       </c>
       <c r="R148" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>-775</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>11 DE SEPTIEMBRE DE 1888 996</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-58.442098</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-34.568762</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>BLO-G</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>-781</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ARENALES 3658</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>814125568</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>-58.413717</v>
+      </c>
+      <c r="N150" t="n">
+        <v>-34.585425</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>AGU-L</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>-782</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ARMENIA 1800</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>814125577</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>-58.426328</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-34.588734</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>VCR-F</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>-787</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-58.432822</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-34.571917</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>BLO-H</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>-796</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>CABRERA, JOSE A. 4723</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>814125624</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-58.429431</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-34.591921</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>VCR-F</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>-797</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CHARCAS 3248</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>814125633</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>columna chocada</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-58.411747</v>
+      </c>
+      <c r="N154" t="n">
+        <v>-34.592175</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>AGU-C</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>-805</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>814125656</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>-58.432345</v>
+      </c>
+      <c r="N155" t="n">
+        <v>-34.566345</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>BLO-I</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>Pendiente ADM OT GxC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Beruti 3012</t>
+          <t>BERUTI 3012</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>Pendiente ADM OT GxC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>Pendiente ADM OT GxC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R153"/>
+  <dimension ref="A1:R152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9693,7 +9693,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 2338</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>813631432</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9750,24 +9750,24 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.444112</v>
+        <v>-58.438595</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.569261</v>
+        <v>-34.565168</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9779,7 +9779,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>813631446</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9836,10 +9836,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.438595</v>
+        <v>-58.437217</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.565168</v>
+        <v>-34.567174</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>813631449</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9922,10 +9922,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.437217</v>
+        <v>-58.44018</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.567174</v>
+        <v>-34.565612</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9951,7 +9951,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>813631451</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9986,12 +9986,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10008,19 +10008,19 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.44018</v>
+        <v>-58.441718</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.565612</v>
+        <v>-34.566411</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -10037,22 +10037,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>813631452</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10072,12 +10072,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10094,24 +10094,24 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.441718</v>
+        <v>-58.402534</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.566411</v>
+        <v>-34.593133</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,17 +10123,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S00477293</t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARENALES 2552</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>813631921</t>
+          <t>814108527</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10180,10 +10180,10 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.402534</v>
+        <v>-58.385947</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.593133</v>
+        <v>-34.588156</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,7 +10209,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S01385955</t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>POSADAS 1391</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>814108527</t>
+          <t>814111029</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10266,14 +10266,14 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.385947</v>
+        <v>-58.440439</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.588156</v>
+        <v>-34.575416</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,7 +10295,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t xml:space="preserve">9179 </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t>ARAOZ 2289</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>814111029</t>
+          <t>814108607</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10352,10 +10352,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.440439</v>
+        <v>-58.418131</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.575416</v>
+        <v>-34.58774</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10381,7 +10381,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179 </t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ARAOZ 2289</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>814108607</t>
+          <t>814108619</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10438,10 +10438,10 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.418131</v>
+        <v>-58.438274</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.58774</v>
+        <v>-34.564049</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>814108619</t>
+          <t>814108632</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10524,10 +10524,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.438274</v>
+        <v>-58.434721</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.564049</v>
+        <v>-34.567241</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>814108632</t>
+          <t>814108642</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.434721</v>
+        <v>-58.435738</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.567241</v>
+        <v>-34.564606</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>814108642</t>
+          <t>814108650</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10696,10 +10696,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.435738</v>
+        <v>-58.435011</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.564606</v>
+        <v>-34.56566</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10748,11 +10748,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>814108650</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10760,7 +10756,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10770,7 +10766,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -10782,10 +10778,10 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.435011</v>
+        <v>-58.430774</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.56566</v>
+        <v>-34.568179</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10799,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10811,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10821,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10834,7 +10830,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>814108660</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10864,10 +10864,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.430774</v>
+        <v>-58.436255</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.568179</v>
+        <v>-34.567733</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>814108660</t>
+          <t>814109172</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10950,10 +10950,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.436255</v>
+        <v>-58.443403</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.567733</v>
+        <v>-34.575666</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>814109172</t>
+          <t>814109219</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11036,10 +11036,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.443403</v>
+        <v>-58.428639</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.575666</v>
+        <v>-34.59039</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>814109219</t>
+          <t>814109418</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11122,14 +11122,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.428639</v>
+        <v>-58.404726</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.59039</v>
+        <v>-34.596069</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11151,7 +11151,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11174,11 +11174,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>814109418</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11196,7 +11192,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -11208,14 +11204,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.404726</v>
+        <v>-58.422183</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.596069</v>
+        <v>-34.576849</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11225,7 +11221,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11237,7 +11233,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11247,7 +11243,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11260,7 +11256,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>814109740</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -11290,10 +11290,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.422183</v>
+        <v>-58.425803</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.576849</v>
+        <v>-34.588513</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11319,7 +11319,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t xml:space="preserve">9945 </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>LACROZE, FEDERICO AV. 1938</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>814109740</t>
+          <t>814109788</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11376,10 +11376,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.425803</v>
+        <v>-58.440759</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.588513</v>
+        <v>-34.565819</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11405,17 +11405,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9945 </t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 1938</t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11428,11 +11428,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>814109788</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11440,17 +11436,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -11462,10 +11458,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.440759</v>
+        <v>-58.424388</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.565819</v>
+        <v>-34.59632</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11479,7 +11475,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11491,7 +11487,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11501,7 +11497,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11514,7 +11510,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>814108116</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11522,17 +11522,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -11544,10 +11544,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.424388</v>
+        <v>-58.427895</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.59632</v>
+        <v>-34.583677</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11573,7 +11573,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">9924 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t>CORDOBA AV. 4089</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>814108116</t>
+          <t>814108196</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11630,10 +11630,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.427895</v>
+        <v>-58.424553</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.583677</v>
+        <v>-34.59709</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11659,7 +11659,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>814108196</t>
+          <t>814111706</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11716,10 +11716,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.424553</v>
+        <v>-58.440973</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.59709</v>
+        <v>-34.572415</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11745,7 +11745,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11768,11 +11768,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>814111706</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11785,12 +11781,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -11802,14 +11798,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.440973</v>
+        <v>-58.40382</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.572415</v>
+        <v>-34.594385</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11819,7 +11815,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11831,7 +11827,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11841,12 +11837,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11854,7 +11850,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>814108322</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11862,17 +11862,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11884,14 +11884,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.40382</v>
+        <v>-58.43218</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.594385</v>
+        <v>-34.578546</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11913,7 +11913,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>814108322</t>
+          <t>814108343</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11970,10 +11970,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.43218</v>
+        <v>-58.436737</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.578546</v>
+        <v>-34.58597</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11999,7 +11999,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12022,11 +12022,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>814108343</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12034,12 +12030,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -12056,10 +12052,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.436737</v>
+        <v>-58.413584</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.58597</v>
+        <v>-34.58551</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12073,7 +12069,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12085,7 +12081,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12095,7 +12091,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12116,17 +12112,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12138,10 +12134,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.413584</v>
+        <v>-58.415912</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.58551</v>
+        <v>-34.588977</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12155,7 +12151,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12167,7 +12163,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12177,7 +12173,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12190,7 +12186,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>814111751</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12203,12 +12203,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -12220,10 +12220,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.415912</v>
+        <v>-58.413885</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.588977</v>
+        <v>-34.586628</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12249,7 +12249,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>814111751</t>
+          <t>814108377</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12306,14 +12306,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.413885</v>
+        <v>-58.400188</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.586628</v>
+        <v>-34.583882</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12335,7 +12335,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10082 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TAGLE 2562</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>814108377</t>
+          <t>814111784</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12392,10 +12392,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.400188</v>
+        <v>-58.404652</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.583882</v>
+        <v>-34.58263</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12421,7 +12421,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>814111784</t>
+          <t>814108458</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12478,14 +12478,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.404652</v>
+        <v>-58.433857</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.58263</v>
+        <v>-34.57424</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>814108458</t>
+          <t>814111791</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12564,10 +12564,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.433857</v>
+        <v>-58.432319</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.57424</v>
+        <v>-34.574385</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>814111791</t>
+          <t>814108469</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12650,10 +12650,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.432319</v>
+        <v>-58.416882</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.574385</v>
+        <v>-34.562655</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12679,7 +12679,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104 </t>
+          <t xml:space="preserve">10129 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
+          <t>ALVAREZ, JULIAN 1890</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>814108469</t>
+          <t>814111804</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12729,17 +12729,17 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L144" t="n">
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.416882</v>
+        <v>-58.42056</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.562655</v>
+        <v>-34.590217</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12765,7 +12765,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">10129 </t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 1890</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12788,11 +12788,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>814111804</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12800,7 +12796,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12810,22 +12806,22 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L145" t="n">
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.42056</v>
+        <v>-58.419652</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.590217</v>
+        <v>-34.588271</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12839,7 +12835,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12851,17 +12847,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131 </t>
+          <t>-775</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
+          <t>11 DE SEPTIEMBRE DE 1888 996</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12874,7 +12870,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12904,10 +12904,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.419652</v>
+        <v>-58.442098</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.588271</v>
+        <v>-34.568762</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12933,7 +12933,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-775</t>
+          <t>-781</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>11 DE SEPTIEMBRE DE 1888 996</t>
+          <t>ARENALES 3658</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125568</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -12990,10 +12990,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.442098</v>
+        <v>-58.413717</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.568762</v>
+        <v>-34.585425</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13019,7 +13019,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-781</t>
+          <t>-782</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ARENALES 3658</t>
+          <t>ARMENIA 1800</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>814125568</t>
+          <t>814125577</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13076,10 +13076,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.413717</v>
+        <v>-58.426328</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.585425</v>
+        <v>-34.588734</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13105,7 +13105,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-782</t>
+          <t>-787</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ARMENIA 1800</t>
+          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>814125577</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -13162,10 +13162,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.426328</v>
+        <v>-58.432822</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.588734</v>
+        <v>-34.571917</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13191,7 +13191,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-787</t>
+          <t>-796</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
+          <t>CABRERA, JOSE A. 4723</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125624</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -13248,10 +13248,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.432822</v>
+        <v>-58.429431</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.571917</v>
+        <v>-34.591921</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13277,7 +13277,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-796</t>
+          <t>-797</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CABRERA, JOSE A. 4723</t>
+          <t>CHARCAS 3248</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>814125624</t>
+          <t>814125633</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna chocada</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13334,14 +13334,14 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.429431</v>
+        <v>-58.411747</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.591921</v>
+        <v>-34.592175</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13363,7 +13363,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-797</t>
+          <t>-805</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13373,12 +13373,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CHARCAS 3248</t>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>814125633</t>
+          <t>814125656</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>columna chocada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13420,14 +13420,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.411747</v>
+        <v>-58.432345</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.592175</v>
+        <v>-34.566345</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13437,96 +13437,10 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>-805</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>814125656</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L153" t="n">
-        <v>1</v>
-      </c>
-      <c r="M153" t="n">
-        <v>-58.432345</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-34.566345</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>BLO-I</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R152"/>
+  <dimension ref="A1:R154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13446,6 +13446,178 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>814446819</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>6/11/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ANGEL GALLARDO 946</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>814446819</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-58.443588</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-34.606863</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>814446825</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>6/11/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ANGEL GALLARDO 1084</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>814446825</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>PEBCOM</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-58.445084</v>
+      </c>
+      <c r="N154" t="n">
+        <v>-34.60725</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R154"/>
+  <dimension ref="A1:R153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7973,17 +7973,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>00781500</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SEGUI JUAN FRANCISCO 4691</t>
+          <t>RAVIGNANI EMILIO DR 1498</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>812879559</t>
+          <t>812879925</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8030,10 +8030,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.422229</v>
+        <v>-58.441411</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.573148</v>
+        <v>-34.583443</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8059,22 +8059,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>00781500</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RAVIGNANI EMILIO DR 1498</t>
+          <t>JUNCAL 2249</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>812879925</t>
+          <t>812880742</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8116,14 +8116,14 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.441411</v>
+        <v>-58.399319</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.583443</v>
+        <v>-34.592221</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8133,34 +8133,34 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JUNCAL 2249</t>
+          <t>PARAGUAY 4237</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>812880742</t>
+          <t>813046389</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8202,14 +8202,14 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.399319</v>
+        <v>-58.421616</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.592221</v>
+        <v>-34.586608</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8219,29 +8219,29 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>S00289486</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PARAGUAY 4237</t>
+          <t>PARAGUAY 4585</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>813046389</t>
+          <t>813046715</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8288,10 +8288,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.421616</v>
+        <v>-58.42498</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.586608</v>
+        <v>-34.584031</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8317,7 +8317,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S00289486</t>
+          <t>S00325208</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PARAGUAY 4585</t>
+          <t>PARAGUAY 3711</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>813046715</t>
+          <t>813046718</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8374,10 +8374,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.42498</v>
+        <v>-58.416117</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.584031</v>
+        <v>-34.590942</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-C</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S00325208</t>
+          <t>S00337251</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PARAGUAY 3711</t>
+          <t>SANCHEZ DE BUSTAMANTE 2450</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>813046718</t>
+          <t>813046724</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8460,14 +8460,14 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.416117</v>
+        <v>-58.403295</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.590942</v>
+        <v>-34.585041</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>VCR-C</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8489,7 +8489,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S00337251</t>
+          <t>S00364886</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 2450</t>
+          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>813046724</t>
+          <t>813046778</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8546,14 +8546,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.403295</v>
+        <v>-58.434778</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.585041</v>
+        <v>-34.569188</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8575,17 +8575,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S00364886</t>
+          <t>PJ00009</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
+          <t>THAMES 1516</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>813046778</t>
+          <t>813304793</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8632,10 +8632,10 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.434778</v>
+        <v>-58.431966</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.569188</v>
+        <v>-34.588553</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8661,22 +8661,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PJ00009</t>
+          <t>LR00001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>THAMES 1516</t>
+          <t>BILLINGHURST 1796</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>813304793</t>
+          <t>813350523</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8718,14 +8718,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.431966</v>
+        <v>-58.409695</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.588553</v>
+        <v>-34.589662</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-D</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LR00001</t>
+          <t>PJ00040</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4/27/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BILLINGHURST 1796</t>
+          <t>HONDURAS 4822</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>813350523</t>
+          <t>813350536</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8804,14 +8804,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.409695</v>
+        <v>-58.428528</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.589662</v>
+        <v>-34.589872</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>AGU-D</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8833,7 +8833,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>AF00001</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>SALGUERO, JERONIMO 1995</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>813304889</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8890,10 +8890,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.428528</v>
+        <v>-58.413378</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.589872</v>
+        <v>-34.587254</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8919,7 +8919,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>CHARCAS 3250</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>813304917</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8976,14 +8976,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.413378</v>
+        <v>-58.41175</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.587254</v>
+        <v>-34.592173</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CHARCAS 3250</t>
+          <t>DORREGO AV.2752</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>813304917</t>
+          <t>813305004</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9062,14 +9062,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.41175</v>
+        <v>-58.43266</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.592173</v>
+        <v>-34.574202</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9091,7 +9091,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>S00419298</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DORREGO AV.2752</t>
+          <t>AUSTRIA 2354</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>813350615</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9148,14 +9148,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.43266</v>
+        <v>-58.401523</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.574202</v>
+        <v>-34.586182</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,22 +9177,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S00419298</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/23/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AUSTRIA 2354</t>
+          <t>AV DORREGO 3900</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>813350615</t>
+          <t>813352568</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9227,21 +9227,21 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L103" t="n">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.401523</v>
+        <v>-58.418801</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.586182</v>
+        <v>-34.564182</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9263,17 +9263,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4/23/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AV DORREGO 3900</t>
+          <t>ALVAREZ, JULIAN 2552</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>813352568</t>
+          <t>813352603</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9313,17 +9313,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.418801</v>
+        <v>-58.413555</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.564182</v>
+        <v>-34.585955</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9349,17 +9349,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 2552</t>
+          <t>BULNES 2550</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>813352603</t>
+          <t>813631416</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -9406,10 +9406,10 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.413555</v>
+        <v>-58.407013</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.585955</v>
+        <v>-34.582645</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9435,7 +9435,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BULNES 2550</t>
+          <t>DEL LIBERTADOR AV. 2030</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>813631416</t>
+          <t>813631417</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9492,14 +9492,14 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.407013</v>
+        <v>-58.401882</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.582645</v>
+        <v>-34.582006</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,7 +9521,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 2030</t>
+          <t>CASTEX 3439</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>813631417</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9578,14 +9578,14 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.401882</v>
+        <v>-58.406414</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.582006</v>
+        <v>-34.577519</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,7 +9607,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CASTEX 3439</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>813631425</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9664,10 +9664,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.406414</v>
+        <v>-58.438595</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.577519</v>
+        <v>-34.565168</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9693,7 +9693,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>813631446</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9750,10 +9750,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.438595</v>
+        <v>-58.437217</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.565168</v>
+        <v>-34.567174</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>813631449</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9836,10 +9836,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.437217</v>
+        <v>-58.44018</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.567174</v>
+        <v>-34.565612</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>813631451</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9922,19 +9922,19 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.44018</v>
+        <v>-58.441718</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.565612</v>
+        <v>-34.566411</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9951,22 +9951,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>813631452</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9986,12 +9986,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10008,24 +10008,24 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.441718</v>
+        <v>-58.402534</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.566411</v>
+        <v>-34.593133</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10037,17 +10037,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S00477293</t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARENALES 2552</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>813631921</t>
+          <t>814108527</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10094,10 +10094,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.402534</v>
+        <v>-58.385947</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.593133</v>
+        <v>-34.588156</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,7 +10123,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S01385955</t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>POSADAS 1391</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>814108527</t>
+          <t>814111029</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10180,14 +10180,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.385947</v>
+        <v>-58.440439</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.588156</v>
+        <v>-34.575416</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,7 +10209,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t xml:space="preserve">9179 </t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t>ARAOZ 2289</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>814111029</t>
+          <t>814108607</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10266,10 +10266,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.440439</v>
+        <v>-58.418131</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.575416</v>
+        <v>-34.58774</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,7 +10295,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179 </t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ARAOZ 2289</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>814108607</t>
+          <t>814108619</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10352,10 +10352,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.418131</v>
+        <v>-58.438274</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.58774</v>
+        <v>-34.564049</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10381,7 +10381,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>814108619</t>
+          <t>814108632</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10438,10 +10438,10 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.438274</v>
+        <v>-58.434721</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.564049</v>
+        <v>-34.567241</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>814108632</t>
+          <t>814108642</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10524,10 +10524,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.434721</v>
+        <v>-58.435738</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.567241</v>
+        <v>-34.564606</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>814108642</t>
+          <t>814108650</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.435738</v>
+        <v>-58.435011</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.564606</v>
+        <v>-34.56566</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10662,11 +10662,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>814108650</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10674,7 +10670,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10684,7 +10680,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -10696,10 +10692,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.435011</v>
+        <v>-58.430774</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.56566</v>
+        <v>-34.568179</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10713,7 +10709,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10725,7 +10721,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10735,7 +10731,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10748,7 +10744,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>814108660</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -10778,10 +10778,10 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.430774</v>
+        <v>-58.436255</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.568179</v>
+        <v>-34.567733</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>814108660</t>
+          <t>814109172</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10864,10 +10864,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.436255</v>
+        <v>-58.443403</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.567733</v>
+        <v>-34.575666</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>814109172</t>
+          <t>814109219</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10950,10 +10950,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.443403</v>
+        <v>-58.428639</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.575666</v>
+        <v>-34.59039</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>814109219</t>
+          <t>814109418</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11036,14 +11036,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.428639</v>
+        <v>-58.404726</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.59039</v>
+        <v>-34.596069</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -11088,11 +11088,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>814109418</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11110,7 +11106,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -11122,14 +11118,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.404726</v>
+        <v>-58.422183</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.596069</v>
+        <v>-34.576849</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11139,7 +11135,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11151,7 +11147,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,7 +11157,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11174,7 +11170,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>814109740</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -11204,10 +11204,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.422183</v>
+        <v>-58.425803</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.576849</v>
+        <v>-34.588513</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11233,7 +11233,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t xml:space="preserve">9945 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>LACROZE, FEDERICO AV. 1938</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>814109740</t>
+          <t>814109788</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11290,10 +11290,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.425803</v>
+        <v>-58.440759</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.588513</v>
+        <v>-34.565819</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11319,17 +11319,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9945 </t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 1938</t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11342,11 +11342,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>814109788</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11354,17 +11350,17 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -11376,10 +11372,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.440759</v>
+        <v>-58.424388</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.565819</v>
+        <v>-34.59632</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11393,7 +11389,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11405,7 +11401,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11415,7 +11411,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11428,7 +11424,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>814108116</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11436,17 +11436,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -11458,10 +11458,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.424388</v>
+        <v>-58.427895</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.59632</v>
+        <v>-34.583677</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11487,7 +11487,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">9924 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t>CORDOBA AV. 4089</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>814108116</t>
+          <t>814108196</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11544,10 +11544,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.427895</v>
+        <v>-58.424553</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.583677</v>
+        <v>-34.59709</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11573,7 +11573,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>814108196</t>
+          <t>814111706</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11630,10 +11630,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.424553</v>
+        <v>-58.440973</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.59709</v>
+        <v>-34.572415</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11659,7 +11659,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11682,11 +11682,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>814111706</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11699,12 +11695,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -11716,14 +11712,14 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.440973</v>
+        <v>-58.40382</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.572415</v>
+        <v>-34.594385</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11733,7 +11729,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11745,7 +11741,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11755,12 +11751,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11768,7 +11764,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>814108322</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11776,17 +11776,17 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -11798,14 +11798,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.40382</v>
+        <v>-58.43218</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.594385</v>
+        <v>-34.578546</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>814108322</t>
+          <t>814108343</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11884,10 +11884,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.43218</v>
+        <v>-58.436737</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.578546</v>
+        <v>-34.58597</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11913,7 +11913,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11936,11 +11936,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>814108343</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11948,12 +11944,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11970,10 +11966,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.436737</v>
+        <v>-58.413584</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.58597</v>
+        <v>-34.58551</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11987,7 +11983,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11999,7 +11995,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12009,7 +12005,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12030,17 +12026,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12052,10 +12048,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.413584</v>
+        <v>-58.415912</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.58551</v>
+        <v>-34.588977</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12069,7 +12065,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12081,7 +12077,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12091,7 +12087,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12104,7 +12100,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>814111751</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12117,12 +12117,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12134,10 +12134,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.415912</v>
+        <v>-58.413885</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.588977</v>
+        <v>-34.586628</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12163,7 +12163,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>814111751</t>
+          <t>814108377</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12220,14 +12220,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.413885</v>
+        <v>-58.400188</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.586628</v>
+        <v>-34.583882</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12249,7 +12249,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">10082 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TAGLE 2562</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>814108377</t>
+          <t>814111784</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12306,10 +12306,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.400188</v>
+        <v>-58.404652</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.583882</v>
+        <v>-34.58263</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12335,7 +12335,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>814111784</t>
+          <t>814108458</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12392,14 +12392,14 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.404652</v>
+        <v>-58.433857</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.58263</v>
+        <v>-34.57424</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12421,7 +12421,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>814108458</t>
+          <t>814111791</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12478,10 +12478,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.433857</v>
+        <v>-58.432319</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.57424</v>
+        <v>-34.574385</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>814111791</t>
+          <t>814108469</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12564,10 +12564,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.432319</v>
+        <v>-58.416882</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.574385</v>
+        <v>-34.562655</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12593,7 +12593,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104 </t>
+          <t xml:space="preserve">10129 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
+          <t>ALVAREZ, JULIAN 1890</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>814108469</t>
+          <t>814111804</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12643,17 +12643,17 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.416882</v>
+        <v>-58.42056</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.562655</v>
+        <v>-34.590217</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12679,7 +12679,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10129 </t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 1890</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12702,11 +12702,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>814111804</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12714,7 +12710,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12724,22 +12720,22 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L144" t="n">
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.42056</v>
+        <v>-58.419652</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.590217</v>
+        <v>-34.588271</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12753,7 +12749,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12765,17 +12761,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131 </t>
+          <t>-775</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
+          <t>11 DE SEPTIEMBRE DE 1888 996</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12788,7 +12784,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12818,10 +12818,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.419652</v>
+        <v>-58.442098</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.588271</v>
+        <v>-34.568762</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12847,7 +12847,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-775</t>
+          <t>-781</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>11 DE SEPTIEMBRE DE 1888 996</t>
+          <t>ARENALES 3658</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125568</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12904,10 +12904,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.442098</v>
+        <v>-58.413717</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.568762</v>
+        <v>-34.585425</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12933,7 +12933,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-781</t>
+          <t>-782</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ARENALES 3658</t>
+          <t>ARMENIA 1800</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>814125568</t>
+          <t>814125577</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12990,10 +12990,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.413717</v>
+        <v>-58.426328</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.585425</v>
+        <v>-34.588734</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13019,7 +13019,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-782</t>
+          <t>-787</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ARMENIA 1800</t>
+          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>814125577</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -13076,10 +13076,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.426328</v>
+        <v>-58.432822</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.588734</v>
+        <v>-34.571917</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13105,7 +13105,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-787</t>
+          <t>-796</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
+          <t>CABRERA, JOSE A. 4723</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125624</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -13162,10 +13162,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.432822</v>
+        <v>-58.429431</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.571917</v>
+        <v>-34.591921</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13191,7 +13191,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-796</t>
+          <t>-797</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13201,12 +13201,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CABRERA, JOSE A. 4723</t>
+          <t>CHARCAS 3248</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>814125624</t>
+          <t>814125633</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna chocada</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13248,14 +13248,14 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.429431</v>
+        <v>-58.411747</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.591921</v>
+        <v>-34.592175</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13277,7 +13277,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-797</t>
+          <t>-805</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CHARCAS 3248</t>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>814125633</t>
+          <t>814125656</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>columna chocada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13334,14 +13334,14 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.411747</v>
+        <v>-58.432345</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.592175</v>
+        <v>-34.566345</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13363,22 +13363,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-805</t>
+          <t>814446819</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6/2/2026</t>
+          <t>6/11/2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
+          <t>ANGEL GALLARDO 946</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>814125656</t>
+          <t>814446819</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13417,17 +13417,17 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.432345</v>
+        <v>-58.443588</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.566345</v>
+        <v>-34.606863</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13449,7 +13449,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>814446819</t>
+          <t>814446825</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ANGEL GALLARDO 946</t>
+          <t>ANGEL GALLARDO 1084</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>814446819</t>
+          <t>814446825</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -13506,10 +13506,10 @@
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.443588</v>
+        <v>-58.445084</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.606863</v>
+        <v>-34.60725</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13527,92 +13527,6 @@
         </is>
       </c>
       <c r="R153" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>814446825</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>6/11/2026</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>ANGEL GALLARDO 1084</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>814446825</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L154" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" t="n">
-        <v>-58.445084</v>
-      </c>
-      <c r="N154" t="n">
-        <v>-34.60725</v>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>ALM-O</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R153"/>
+  <dimension ref="A1:R152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11487,7 +11487,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924 </t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CORDOBA AV. 4089</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>814108196</t>
+          <t>814111706</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11544,10 +11544,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.424553</v>
+        <v>-58.440973</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.59709</v>
+        <v>-34.572415</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11573,7 +11573,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11596,11 +11596,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>814111706</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11613,12 +11609,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -11630,14 +11626,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.440973</v>
+        <v>-58.40382</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.572415</v>
+        <v>-34.594385</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11647,7 +11643,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11659,7 +11655,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11669,12 +11665,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11682,7 +11678,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>814108322</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11690,17 +11690,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -11712,14 +11712,14 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.40382</v>
+        <v>-58.43218</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.594385</v>
+        <v>-34.578546</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11741,7 +11741,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>814108322</t>
+          <t>814108343</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11798,10 +11798,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.43218</v>
+        <v>-58.436737</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.578546</v>
+        <v>-34.58597</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11850,11 +11850,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>814108343</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11862,12 +11858,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11884,10 +11880,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.436737</v>
+        <v>-58.413584</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.58597</v>
+        <v>-34.58551</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11901,7 +11897,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11913,7 +11909,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11923,7 +11919,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11944,17 +11940,17 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11966,10 +11962,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.413584</v>
+        <v>-58.415912</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.58551</v>
+        <v>-34.588977</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11983,7 +11979,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11995,7 +11991,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12005,7 +12001,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12018,7 +12014,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>814111751</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12031,12 +12031,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12048,10 +12048,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.415912</v>
+        <v>-58.413885</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.588977</v>
+        <v>-34.586628</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12077,7 +12077,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>814111751</t>
+          <t>814108377</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12134,14 +12134,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.413885</v>
+        <v>-58.400188</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.586628</v>
+        <v>-34.583882</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12163,7 +12163,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10082 </t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TAGLE 2562</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>814108377</t>
+          <t>814111784</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12220,10 +12220,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.400188</v>
+        <v>-58.404652</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.583882</v>
+        <v>-34.58263</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12249,7 +12249,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>814111784</t>
+          <t>814108458</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12306,14 +12306,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.404652</v>
+        <v>-58.433857</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.58263</v>
+        <v>-34.57424</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12335,7 +12335,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>814108458</t>
+          <t>814111791</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12392,10 +12392,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.433857</v>
+        <v>-58.432319</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.57424</v>
+        <v>-34.574385</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>814111791</t>
+          <t>814108469</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12478,10 +12478,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.432319</v>
+        <v>-58.416882</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.574385</v>
+        <v>-34.562655</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104 </t>
+          <t xml:space="preserve">10129 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
+          <t>ALVAREZ, JULIAN 1890</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>814108469</t>
+          <t>814111804</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12557,17 +12557,17 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.416882</v>
+        <v>-58.42056</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.562655</v>
+        <v>-34.590217</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12593,7 +12593,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10129 </t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 1890</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12616,11 +12616,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>814111804</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12628,7 +12624,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12638,22 +12634,22 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.42056</v>
+        <v>-58.419652</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.590217</v>
+        <v>-34.588271</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12667,7 +12663,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12679,17 +12675,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131 </t>
+          <t>-775</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
+          <t>11 DE SEPTIEMBRE DE 1888 996</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12702,7 +12698,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -12732,10 +12732,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.419652</v>
+        <v>-58.442098</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.588271</v>
+        <v>-34.568762</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12761,7 +12761,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>-775</t>
+          <t>-781</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>11 DE SEPTIEMBRE DE 1888 996</t>
+          <t>ARENALES 3658</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125568</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12818,10 +12818,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.442098</v>
+        <v>-58.413717</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.568762</v>
+        <v>-34.585425</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12847,7 +12847,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-781</t>
+          <t>-782</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ARENALES 3658</t>
+          <t>ARMENIA 1800</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>814125568</t>
+          <t>814125577</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -12904,10 +12904,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.413717</v>
+        <v>-58.426328</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.585425</v>
+        <v>-34.588734</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12933,7 +12933,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-782</t>
+          <t>-787</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ARMENIA 1800</t>
+          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>814125577</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -12990,10 +12990,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.426328</v>
+        <v>-58.432822</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.588734</v>
+        <v>-34.571917</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13019,7 +13019,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-787</t>
+          <t>-796</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
+          <t>CABRERA, JOSE A. 4723</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814125624</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -13076,10 +13076,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.432822</v>
+        <v>-58.429431</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.571917</v>
+        <v>-34.591921</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13105,7 +13105,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-796</t>
+          <t>-797</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13115,12 +13115,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CABRERA, JOSE A. 4723</t>
+          <t>CHARCAS 3248</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>814125624</t>
+          <t>814125633</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna chocada</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13162,14 +13162,14 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.429431</v>
+        <v>-58.411747</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.591921</v>
+        <v>-34.592175</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13191,7 +13191,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-797</t>
+          <t>-805</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13201,12 +13201,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CHARCAS 3248</t>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>814125633</t>
+          <t>814125656</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>columna chocada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13248,14 +13248,14 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.411747</v>
+        <v>-58.432345</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.592175</v>
+        <v>-34.566345</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13277,22 +13277,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-805</t>
+          <t>814446819</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6/2/2026</t>
+          <t>6/11/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
+          <t>ANGEL GALLARDO 946</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>814125656</t>
+          <t>814446819</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13331,17 +13331,17 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.432345</v>
+        <v>-58.443588</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.566345</v>
+        <v>-34.606863</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13363,7 +13363,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>814446819</t>
+          <t>814446825</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ANGEL GALLARDO 946</t>
+          <t>ANGEL GALLARDO 1084</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>814446819</t>
+          <t>814446825</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13420,10 +13420,10 @@
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.443588</v>
+        <v>-58.445084</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.606863</v>
+        <v>-34.60725</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13441,92 +13441,6 @@
         </is>
       </c>
       <c r="R152" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>814446825</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>6/11/2026</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ANGEL GALLARDO 1084</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>814446825</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L153" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" t="n">
-        <v>-58.445084</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-34.60725</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>ALM-O</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_PEBCOM.xlsx
+++ b/mapa_interactivo_PEBCOM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R152"/>
+  <dimension ref="A1:R143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1527,17 +1527,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>-312</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3/28/2025</t>
+          <t>3/29/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PRINGLES 1470</t>
+          <t>MATIENZO BENJAMIN /ALT/ 1831</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>804316147</t>
+          <t>804333522</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Retirar columna ya traspasaron el nodo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.423996</v>
+        <v>-58.434835</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.594973</v>
+        <v>-34.569129</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1613,22 +1613,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-312</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3/29/2025</t>
+          <t>4/11/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN /ALT/ 1831</t>
+          <t>URIBURU JOSE E., PRES. 1415</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>804333522</t>
+          <t>804634219</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Retirar columna ya traspasaron el nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1667,17 +1667,17 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.434835</v>
+        <v>-58.397031</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.569129</v>
+        <v>-34.591926</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1687,34 +1687,34 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>-338</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4/11/2025</t>
+          <t>4/21/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>URIBURU JOSE E., PRES. 1415</t>
+          <t>PARAGUAY /ALT/ 4283</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>804634219</t>
+          <t>804838861</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1756,14 +1756,14 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.397031</v>
+        <v>-58.421964</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.591926</v>
+        <v>-34.586342</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1773,29 +1773,29 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>-338</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4/21/2025</t>
+          <t>5/5/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PARAGUAY /ALT/ 4283</t>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1520</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>804838861</t>
+          <t>805655369</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.421964</v>
+        <v>-58.432419</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.586342</v>
+        <v>-34.566431</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1871,17 +1871,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>805707165</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5/5/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MATIENZO, BENJAMIN, TENIENTE 1520</t>
+          <t>Baez 793</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>805655369</t>
+          <t>ICD30592749</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1928,10 +1928,10 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.432419</v>
+        <v>-58.436165</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.566431</v>
+        <v>-34.569081</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1957,17 +1957,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>805707165</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>5/6/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Baez 793</t>
+          <t>Soldado de la Independencia 1298</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ICD30592749</t>
+          <t>805707245</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA DE 7 MTS Y TRANSFERIR A COMUNITARIA</t>
+          <t>Picada - Con fuente teco</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2002,36 +2002,36 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.436165</v>
+        <v>-58.440507</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.569081</v>
+        <v>-34.564016</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-K</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2043,17 +2043,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5/6/2025</t>
+          <t>5/7/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Soldado de la Independencia 1298</t>
+          <t>Migueletes 1326</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>805707245</t>
+          <t>805707264</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Picada - Con fuente teco</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2100,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.440507</v>
+        <v>-58.440177</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.564016</v>
+        <v>-34.56291</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>-395</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Migueletes 1326</t>
+          <t>POSADAS 1567</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>805707264</t>
+          <t>805707278</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2186,24 +2186,24 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.440177</v>
+        <v>-58.387847</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.56291</v>
+        <v>-34.587043</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>BLO-K</t>
+          <t>RET-A</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2215,7 +2215,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>-395</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>POSADAS 1567</t>
+          <t>CAMPOS, LUIS M. AV. 1336</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>805707278</t>
+          <t>805722772</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2272,24 +2272,24 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.387847</v>
+        <v>-58.44191</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.587043</v>
+        <v>-34.564245</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>RET-A</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2301,17 +2301,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>-416</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5/7/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 1336</t>
+          <t>Paraguay 3765</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>805722772</t>
+          <t>806926557</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2358,24 +2358,24 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.44191</v>
+        <v>-58.416562</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.564245</v>
+        <v>-34.590589</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2387,7 +2387,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-416</t>
+          <t>-434</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paraguay 3765</t>
+          <t>Billinghurst 1478</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>806926557</t>
+          <t>806926806</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
+          <t xml:space="preserve">Columna base corroida con Nap y ganancias de ambas compañias, </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2444,14 +2444,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.416562</v>
+        <v>-58.412302</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.590589</v>
+        <v>-34.59301</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2473,7 +2473,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-434</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Billinghurst 1478</t>
+          <t>JUNCAL 4559</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>806926806</t>
+          <t>806926927</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Columna base corroida con Nap y ganancias de ambas compañias, </t>
+          <t>Colocar columna para pedir traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2530,14 +2530,14 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.412302</v>
+        <v>-58.423116</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.59301</v>
+        <v>-34.576984</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>VCR-N</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2559,17 +2559,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>-451</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>5/29/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JUNCAL 4559</t>
+          <t>Uriarte 2426</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>806926927</t>
+          <t>807044071</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2616,10 +2616,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.423116</v>
+        <v>-58.423551</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.576984</v>
+        <v>-34.581258</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>VCR-N</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2645,17 +2645,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-451</t>
+          <t>-482</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Uriarte 2426</t>
+          <t>Av. Coronel Diaz 2596</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>807044071</t>
+          <t>807605730</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2678,11 +2678,7 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Colocar columna para pedir traspaso de nodo teco</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2690,7 +2686,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2702,14 +2698,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.423551</v>
+        <v>-58.405761</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.581258</v>
+        <v>-34.582476</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2719,7 +2715,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2731,17 +2727,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-482</t>
+          <t>-486</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/18/2025</t>
+          <t>6/23/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Av. Coronel Diaz 2596</t>
+          <t>Del Libertador 4596</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2756,7 +2752,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>807605730</t>
+          <t>807762871</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2764,7 +2760,11 @@
           <t>PEBCOM</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2784,14 +2784,14 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.405761</v>
+        <v>-58.432241</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.582476</v>
+        <v>-34.56642</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2813,17 +2813,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-486</t>
+          <t>-501</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6/23/2025</t>
+          <t>7/3/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Del Libertador 4596</t>
+          <t>Cabello 3107</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>807762871</t>
+          <t>807971967</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2863,21 +2863,21 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.432241</v>
+        <v>-58.405749</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.56642</v>
+        <v>-34.58224</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2899,17 +2899,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-501</t>
+          <t>-517</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7/3/2025</t>
+          <t>7/16/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cabello 3107</t>
+          <t>Av Dorrego 2721</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>807971967</t>
+          <t>808373635</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2949,21 +2949,21 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.405749</v>
+        <v>-58.432805</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.58224</v>
+        <v>-34.574345</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2985,22 +2985,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>-517</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7/16/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Av Dorrego 2721</t>
+          <t>URUGUAY 1094</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>808373635</t>
+          <t>808430941</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cambiar columna 114 base corroida y cable de fo cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3035,21 +3035,21 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.432805</v>
+        <v>-58.387175</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.574345</v>
+        <v>-34.596</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3071,22 +3071,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>-523</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>7/20/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>URUGUAY 1094</t>
+          <t>Luis Maria Campos 585</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>808430941</t>
+          <t>808460898</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3121,21 +3121,21 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.387175</v>
+        <v>-58.434668</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.596</v>
+        <v>-34.571258</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3157,17 +3157,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-523</t>
+          <t>-524</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7/20/2025</t>
+          <t>7/21/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 585</t>
+          <t>Luis Maria Campos 509</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>808460898</t>
+          <t>808460897</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3214,10 +3214,10 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.434668</v>
+        <v>-58.434194</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.571258</v>
+        <v>-34.571754</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3243,17 +3243,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-524</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7/21/2025</t>
+          <t>7/28/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luis Maria Campos 509</t>
+          <t>DORREGO AV. 2687</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>808460897</t>
+          <t>808571980</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3300,10 +3300,10 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.434194</v>
+        <v>-58.433295</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.571754</v>
+        <v>-34.574305</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3329,22 +3329,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>8/6/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GASCON 1195</t>
+          <t>BERUTI 2496</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>808571975</t>
+          <t>808733917</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3386,14 +3386,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.423127</v>
+        <v>-58.401374</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.596476</v>
+        <v>-34.592623</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3403,34 +3403,34 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>S00946632</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2687</t>
+          <t>BERUTI 2592</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>808571980</t>
+          <t>808918705</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de redes y retiro de columna</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3472,14 +3472,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.433295</v>
+        <v>-58.402657</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.574305</v>
+        <v>-34.592182</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3501,17 +3501,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-533</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7/28/2025</t>
+          <t>8/20/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bonpland 2233</t>
+          <t>CHARCAS 3986</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>808571985</t>
+          <t>809065854</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cambiar columna y colocar rienda a pique </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.43258</v>
+        <v>-58.419711</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.579265</v>
+        <v>-34.586299</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3587,22 +3587,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8/6/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BERUTI 2496</t>
+          <t>NICARAGUA 5510</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>808733917</t>
+          <t>809526162</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3644,14 +3644,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.401374</v>
+        <v>-58.432726</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.592623</v>
+        <v>-34.582328</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3661,34 +3661,34 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S00946632</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BERUTI 2592</t>
+          <t>Dorrego 2265</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>808918705</t>
+          <t>809837500</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3730,14 +3730,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.402657</v>
+        <v>-58.438083</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.592182</v>
+        <v>-34.577107</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3759,17 +3759,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8/20/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CHARCAS 3986</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>809065854</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3816,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.419711</v>
+        <v>-58.429159</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.586299</v>
+        <v>-34.577821</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3845,22 +3845,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>S00936008</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>9/30/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GORRITI 4417</t>
+          <t>Azcuenaga 1645</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>809526157</t>
+          <t>01095943</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>picada colocar R200 para pedir traspaso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3902,14 +3902,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.425358</v>
+        <v>-58.397092</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.593308</v>
+        <v>-34.590173</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3919,29 +3919,29 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>RET-D</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>-629</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NICARAGUA 5510</t>
+          <t>Fray Justo Santa Maria de Oro 2730</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>809526162</t>
+          <t>ICD31463422</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para posterior traspaso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3988,10 +3988,10 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.432726</v>
+        <v>-58.422406</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.582328</v>
+        <v>-34.577085</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4017,17 +4017,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dorrego 2265</t>
+          <t>NEWBERY, JORGE 2696</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>809837500</t>
+          <t>810421921</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.438083</v>
+        <v>-58.44293</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.577107</v>
+        <v>-34.574483</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4103,32 +4103,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4157,17 +4157,17 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.429159</v>
+        <v>-58.4018</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.577821</v>
+        <v>-34.590471</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4189,22 +4189,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S00936008</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9/30/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azcuenaga 1645</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01095943</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>picada colocar R200 para pedir traspaso</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4246,14 +4246,14 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.397092</v>
+        <v>-58.417634</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.590173</v>
+        <v>-34.587439</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4263,29 +4263,29 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>RET-D</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-629</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fray Justo Santa Maria de Oro 2730</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ICD31463422</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Colocar R400 para posterior traspaso</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4332,10 +4332,10 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.422406</v>
+        <v>-58.440031</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.577085</v>
+        <v>-34.575409</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4361,17 +4361,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2696</t>
+          <t>UGARTECHE 3079</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>810421921</t>
+          <t xml:space="preserve">01638326 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.44293</v>
+        <v>-58.411934</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.574483</v>
+        <v>-34.580653</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4447,32 +4447,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>Paraguay 4301</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810853935</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Cambio de columna propia corroida en base</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4501,17 +4501,17 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.4018</v>
+        <v>-58.422434</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.590471</v>
+        <v>-34.585978</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4533,17 +4533,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>S00785128</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>Paraguay 5055</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810877555</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4590,10 +4590,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.417634</v>
+        <v>-58.429394</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.587439</v>
+        <v>-34.580587</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4619,17 +4619,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>S00566892</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t xml:space="preserve">SANTA FE AV. 3711 </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810877633</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4676,10 +4676,10 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.440031</v>
+        <v>-58.416063</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.575409</v>
+        <v>-34.584975</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4705,22 +4705,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UGARTECHE 3079</t>
+          <t>URUGUAY 1070</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">01638326 </t>
+          <t>810984538</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Columna de telecom corroida en base para retira A pocos metros ya hay columna nueva de telecentro</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4762,14 +4762,14 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.411934</v>
+        <v>-58.387161</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.580653</v>
+        <v>-34.596255</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>RET-R</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4791,22 +4791,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Paraguay 4301</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>810853935</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Cambio de columna propia corroida en base</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4848,14 +4848,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.422434</v>
+        <v>-58.390974</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.585978</v>
+        <v>-34.594177</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4877,22 +4877,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00785128</t>
+          <t>-696</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Paraguay 5055</t>
+          <t>Las heras 3092</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>810877555</t>
+          <t>811131649</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4927,21 +4927,21 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.429394</v>
+        <v>-58.405835</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.580587</v>
+        <v>-34.583573</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4963,22 +4963,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S00566892</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE AV. 3711 </t>
+          <t>AGUERO 2038</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>810877633</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Traspasar red a columna nueva y retirar la vieja</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5020,14 +5020,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.416063</v>
+        <v>-58.402647</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.584975</v>
+        <v>-34.588274</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>AGU-G</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5049,17 +5049,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>URUGUAY 1070</t>
+          <t>French 2377</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>810984538</t>
+          <t>811198746</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5106,10 +5106,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.387161</v>
+        <v>-58.398947</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.596255</v>
+        <v>-34.590946</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5123,34 +5123,34 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>RET-R</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811198700</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>poste inclinado base quebrada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5180,22 +5180,22 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.390974</v>
+        <v>-58.403895</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.594177</v>
+        <v>-34.575559</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5221,22 +5221,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-696</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las heras 3092</t>
+          <t>GURRUCHAGA 2473</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>811131649</t>
+          <t>811198697</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5271,21 +5271,21 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.405835</v>
+        <v>-58.420304</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.583573</v>
+        <v>-34.582607</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>VCR-L</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5307,22 +5307,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>S01159828</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AGUERO 2038</t>
+          <t xml:space="preserve"> THAMES 2041</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811238652</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Traspasar red a columna nueva y retirar la vieja</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5364,14 +5364,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.402647</v>
+        <v>-58.426667</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.588274</v>
+        <v>-34.585153</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>AGU-G</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5393,22 +5393,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>French 2377</t>
+          <t>SOLER 4509</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>811198746</t>
+          <t>Pendiente ADM OT GxC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5450,14 +5450,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.398947</v>
+        <v>-58.42336</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.590946</v>
+        <v>-34.588111</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5467,29 +5467,29 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 3149 </t>
+          <t>DIAZ, CNEL. AV. 2512</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>811198700</t>
+          <t>811238686</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>poste inclinado base quebrada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5529,17 +5529,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.403895</v>
+        <v>-58.406111</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.575559</v>
+        <v>-34.58316</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5565,22 +5565,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>01018482</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GURRUCHAGA 2473</t>
+          <t>AGUERO 2364</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>811198697</t>
+          <t xml:space="preserve">02511365 </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5622,14 +5622,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.420304</v>
+        <v>-58.399462</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.582607</v>
+        <v>-34.585952</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>VCR-L</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5651,17 +5651,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01159828</t>
+          <t>S01180016</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> THAMES 2041</t>
+          <t>FITZ ROY 1730</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>811238652</t>
+          <t>811454223</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5708,10 +5708,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.426667</v>
+        <v>-58.436051</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.585153</v>
+        <v>-34.583855</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5737,17 +5737,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>S01180086</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SOLER 4509</t>
+          <t>BONPLAND 1471</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pendiente ADM OT GxC</t>
+          <t>811454194</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5794,10 +5794,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.42336</v>
+        <v>-58.439513</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.588111</v>
+        <v>-34.585314</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5823,22 +5823,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>01211534</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2512</t>
+          <t xml:space="preserve"> JUNCAL 2490</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>811238686</t>
+          <t>811454103</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5880,10 +5880,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.406111</v>
+        <v>-58.401685</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.58316</v>
+        <v>-34.591336</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5909,22 +5909,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01018482</t>
+          <t>S01290507</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AGUERO 2364</t>
+          <t>CABELLO 3472</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511365 </t>
+          <t>811453983</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5954,26 +5954,26 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.399462</v>
+        <v>-58.409438</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.585952</v>
+        <v>-34.58118</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5995,7 +5995,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S01180016</t>
+          <t>S01313361</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FITZ ROY 1730</t>
+          <t>CABILDO AV. 805</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>811454223</t>
+          <t>811453963</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6045,31 +6045,31 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.436051</v>
+        <v>-58.444955</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.583855</v>
+        <v>-34.569791</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6081,17 +6081,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S01180023</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VEGA, NICETO, CNEL. AV. 5420</t>
+          <t>DIAZ, CNEL. AV. 2599</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>811454198</t>
+          <t>811454281</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6138,14 +6138,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.437628</v>
+        <v>-58.405559</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.587953</v>
+        <v>-34.582478</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ATH-?</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6167,17 +6167,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01180086</t>
+          <t>-733</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/19/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BONPLAND 1471</t>
+          <t xml:space="preserve"> Dorrego 2755</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>811454194</t>
+          <t>811498056</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6224,10 +6224,10 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.439513</v>
+        <v>-58.432319</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.585314</v>
+        <v>-34.574385</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6253,17 +6253,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>01211534</t>
+          <t>-735</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUNCAL 2490</t>
+          <t>BERUTI 3012</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>811454103</t>
+          <t>Pendiente ADM OT GxC</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6298,22 +6298,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.401685</v>
+        <v>-58.406584</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.591336</v>
+        <v>-34.589518</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>AGU-E</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6339,17 +6339,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S01290507</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CABELLO 3472</t>
+          <t>Costa Rica 5741</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>811453983</t>
+          <t>811627110</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.409438</v>
+        <v>-58.436073</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.58118</v>
+        <v>-34.581506</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6425,17 +6425,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S01313361</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CABILDO AV. 805</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>811453963</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6475,31 +6475,31 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.444955</v>
+        <v>-58.413945</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.569791</v>
+        <v>-34.582774</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6511,22 +6511,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DIAZ, CNEL. AV. 2599</t>
+          <t>CALLAO AV. 2014</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>811454281</t>
+          <t>Pendiente ADM OT GxC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6568,10 +6568,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.405559</v>
+        <v>-58.386954</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.582478</v>
+        <v>-34.587337</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6597,17 +6597,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>-733</t>
+          <t>S00066646</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/19/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dorrego 2755</t>
+          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>811498056</t>
+          <t>811627063</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.432319</v>
+        <v>-58.408259</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.574385</v>
+        <v>-34.580266</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>AGU-O</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6683,22 +6683,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>-735</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BERUTI 3012</t>
+          <t>DORREGO AV. 2699</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pendiente ADM OT GxC</t>
+          <t>812440089</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corrodia</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6737,17 +6737,17 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.406584</v>
+        <v>-58.432807</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.589518</v>
+        <v>-34.574343</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>AGU-E</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6769,17 +6769,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>S00117686</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Costa Rica 5741</t>
+          <t>DORREGO AV. 2778</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>811627110</t>
+          <t>812440183</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inlinada</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6826,10 +6826,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.436073</v>
+        <v>-58.432102</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.581506</v>
+        <v>-34.574248</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6855,17 +6855,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>SINCLAIR 3106</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>812440495</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6912,10 +6912,10 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.413945</v>
+        <v>-58.422892</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.582774</v>
+        <v>-34.573802</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6941,22 +6941,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>S01064368</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CALLAO AV. 2014</t>
+          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pendiente ADM OT GxC</t>
+          <t>812440260</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6998,14 +6998,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.386954</v>
+        <v>-58.426552</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.587337</v>
+        <v>-34.592076</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7027,17 +7027,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S00066646</t>
+          <t>S01406817</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>3/3/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SALGUERO, JERONIMO 2715</t>
+          <t>CAMPOS, LUIS M. AV. 155</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>811627063</t>
+          <t>814105825</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.408259</v>
+        <v>-58.431638</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.580266</v>
+        <v>-34.574344</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>AGU-O</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7113,17 +7113,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>S00165389</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2699</t>
+          <t>HONDURAS AV. 3708</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>812440089</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>base corrodia</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7158,22 +7158,22 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.432807</v>
+        <v>-58.414717</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.574343</v>
+        <v>-34.594123</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>VCR-B</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7199,17 +7199,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S00117686</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2778</t>
+          <t>COSTA RICA 5733</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>812440183</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inlinada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7256,10 +7256,10 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.432102</v>
+        <v>-58.436004</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.574248</v>
+        <v>-34.58156</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7285,17 +7285,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SINCLAIR 3106</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>812440495</t>
+          <t>814107507</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7342,10 +7342,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.422892</v>
+        <v>-58.435443</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.573802</v>
+        <v>-34.56693</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7371,22 +7371,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S01064368</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SCALABRINI ORTIZ, RAUL AV. 1413</t>
+          <t>RODRIGUEZ PEÑA 1650</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>812440260</t>
+          <t>814107596</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7428,14 +7428,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.426552</v>
+        <v>-58.389533</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.592076</v>
+        <v>-34.591306</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7457,17 +7457,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01406817</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3/3/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CAMPOS, LUIS M. AV. 155</t>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>814105825</t>
+          <t>812879521</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7507,21 +7507,21 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.431638</v>
+        <v>-58.408769</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.574344</v>
+        <v>-34.587342</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>AGU-J</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7543,17 +7543,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S00165389</t>
+          <t>00781500</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HONDURAS AV. 3708</t>
+          <t>RAVIGNANI EMILIO DR 1498</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812879925</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.414717</v>
+        <v>-58.441411</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.594123</v>
+        <v>-34.583443</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>VCR-B</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7629,22 +7629,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>COSTA RICA 5733</t>
+          <t>JUNCAL 2249</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812880742</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -7686,14 +7686,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.436004</v>
+        <v>-58.399319</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.58156</v>
+        <v>-34.592221</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7703,29 +7703,29 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 851</t>
+          <t>PARAGUAY 4237</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>814107507</t>
+          <t>813046389</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7772,10 +7772,10 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.435443</v>
+        <v>-58.421616</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.56693</v>
+        <v>-34.586608</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>VCR-O</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7801,22 +7801,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>S00289486</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3/5/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PEÑA 1650</t>
+          <t>PARAGUAY 4585</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>814107596</t>
+          <t>813046715</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7858,14 +7858,14 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.389533</v>
+        <v>-58.42498</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.591306</v>
+        <v>-34.584031</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7887,17 +7887,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>S00325208</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+          <t>PARAGUAY 3711</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>812879521</t>
+          <t>813046718</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7944,14 +7944,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.408769</v>
+        <v>-58.416117</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.587342</v>
+        <v>-34.590942</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>AGU-J</t>
+          <t>VCR-C</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7973,22 +7973,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>00781500</t>
+          <t>S00337251</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RAVIGNANI EMILIO DR 1498</t>
+          <t>SANCHEZ DE BUSTAMANTE 2450</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>812879925</t>
+          <t>813046724</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8030,14 +8030,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.441411</v>
+        <v>-58.403295</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.583443</v>
+        <v>-34.585041</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8059,22 +8059,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>S00364886</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JUNCAL 2249</t>
+          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>812880742</t>
+          <t>813046778</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8116,14 +8116,14 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.399319</v>
+        <v>-58.434778</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.592221</v>
+        <v>-34.569188</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8133,34 +8133,34 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>LR00001</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PARAGUAY 4237</t>
+          <t>BILLINGHURST 1796</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>813046389</t>
+          <t>813350523</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8202,14 +8202,14 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.421616</v>
+        <v>-58.409695</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.586608</v>
+        <v>-34.589662</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>VCR-O</t>
+          <t>AGU-D</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8231,17 +8231,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S00289486</t>
+          <t>AF00001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PARAGUAY 4585</t>
+          <t>SALGUERO, JERONIMO 1995</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>813046715</t>
+          <t>813304889</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8288,10 +8288,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.42498</v>
+        <v>-58.413378</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.584031</v>
+        <v>-34.587254</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8317,22 +8317,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S00325208</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PARAGUAY 3711</t>
+          <t>CHARCAS 3250</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>813046718</t>
+          <t>813304917</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8374,14 +8374,14 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.416117</v>
+        <v>-58.41175</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.590942</v>
+        <v>-34.592173</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>VCR-C</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8403,22 +8403,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S00337251</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 2450</t>
+          <t>DORREGO AV.2752</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>813046724</t>
+          <t>813305004</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8460,14 +8460,14 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.403295</v>
+        <v>-58.43266</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.585041</v>
+        <v>-34.574202</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8489,22 +8489,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S00364886</t>
+          <t>S00419298</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
+          <t>AUSTRIA 2354</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>813046778</t>
+          <t>813350615</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8546,14 +8546,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.434778</v>
+        <v>-58.401523</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.569188</v>
+        <v>-34.586182</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8575,17 +8575,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PJ00009</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/23/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>THAMES 1516</t>
+          <t>AV DORREGO 3900</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>813304793</t>
+          <t>813352568</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8625,17 +8625,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.431966</v>
+        <v>-58.418801</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.588553</v>
+        <v>-34.564182</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8661,22 +8661,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LR00001</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4/27/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BILLINGHURST 1796</t>
+          <t>ALVAREZ, JULIAN 2552</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>813350523</t>
+          <t>813352603</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8718,14 +8718,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.409695</v>
+        <v>-58.413555</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.589662</v>
+        <v>-34.585955</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>AGU-D</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8747,17 +8747,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PJ00040</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HONDURAS 4822</t>
+          <t>BULNES 2550</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>813350536</t>
+          <t>813631416</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8804,10 +8804,10 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.428528</v>
+        <v>-58.407013</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.589872</v>
+        <v>-34.582645</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AF00001</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SALGUERO, JERONIMO 1995</t>
+          <t>DEL LIBERTADOR AV. 2030</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>813304889</t>
+          <t>813631417</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8890,14 +8890,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.413378</v>
+        <v>-58.401882</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.587254</v>
+        <v>-34.582006</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8919,22 +8919,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CHARCAS 3250</t>
+          <t>CASTEX 3439</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>813304917</t>
+          <t>813631425</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8976,14 +8976,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.41175</v>
+        <v>-58.406414</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.592173</v>
+        <v>-34.577519</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>AGU-C</t>
+          <t>AGU-R</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9005,17 +9005,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DORREGO AV.2752</t>
+          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>813305004</t>
+          <t>813631446</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9062,10 +9062,10 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.43266</v>
+        <v>-58.438595</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.574202</v>
+        <v>-34.565168</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9091,22 +9091,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S00419298</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AUSTRIA 2354</t>
+          <t>ARCE 949</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>813350615</t>
+          <t>813631449</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9148,14 +9148,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.401523</v>
+        <v>-58.437217</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.586182</v>
+        <v>-34.567174</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9177,17 +9177,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4/23/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AV DORREGO 3900</t>
+          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>813352568</t>
+          <t>813631451</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>POSTE CAIDO, VER POSIBILIDAD DE DESMONTE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9227,17 +9227,17 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L103" t="n">
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.418801</v>
+        <v>-58.44018</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.564182</v>
+        <v>-34.565612</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9263,17 +9263,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 2552</t>
+          <t>VILLANUEVA 1212</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>813352603</t>
+          <t>813631452</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -9320,24 +9320,24 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.413555</v>
+        <v>-58.441718</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.585955</v>
+        <v>-34.566411</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9349,22 +9349,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>S00477293</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BULNES 2550</t>
+          <t xml:space="preserve"> ARENALES 2552</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>813631416</t>
+          <t>813631921</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -9406,14 +9406,14 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.407013</v>
+        <v>-58.402534</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.582645</v>
+        <v>-34.593133</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9435,22 +9435,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>S01385955</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DEL LIBERTADOR AV. 2030</t>
+          <t>POSADAS 1391</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>813631417</t>
+          <t>814108527</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9470,12 +9470,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -9492,10 +9492,10 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.401882</v>
+        <v>-58.385947</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.582006</v>
+        <v>-34.588156</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>RET-L</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9521,17 +9521,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>S00432540</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CASTEX 3439</t>
+          <t>DUMONT, SANTOS 2618</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>813631425</t>
+          <t>814111029</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9578,10 +9578,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.406414</v>
+        <v>-58.440439</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.577519</v>
+        <v>-34.575416</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>AGU-R</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9607,17 +9607,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t xml:space="preserve">9179 </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SOLDADO DE LA INDEPENDENCIA 1102</t>
+          <t>ARAOZ 2289</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>813631446</t>
+          <t>814108607</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9664,10 +9664,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.438595</v>
+        <v>-58.418131</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.565168</v>
+        <v>-34.58774</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9693,17 +9693,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t xml:space="preserve">9180 </t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ARCE 949</t>
+          <t>MIGUELETES 1156</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>813631449</t>
+          <t>814108619</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9750,10 +9750,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.437217</v>
+        <v>-58.438274</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.567174</v>
+        <v>-34.564049</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9779,17 +9779,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t xml:space="preserve">9115 </t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS, LUIS M. AV. 1188 </t>
+          <t>NEWBERY, JORGE 1694</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>813631451</t>
+          <t>814108632</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9836,10 +9836,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.44018</v>
+        <v>-58.434721</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.565612</v>
+        <v>-34.567241</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9865,17 +9865,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t xml:space="preserve">9116 </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VILLANUEVA 1212</t>
+          <t>GOROSTIAGA 1514</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>813631452</t>
+          <t>814108642</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9922,24 +9922,24 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.441718</v>
+        <v>-58.435738</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.566411</v>
+        <v>-34.564606</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9951,22 +9951,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S00477293</t>
+          <t xml:space="preserve">9117 </t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARENALES 2552</t>
+          <t>MAURE 1590</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>813631921</t>
+          <t>814108650</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10008,14 +10008,14 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.402534</v>
+        <v>-58.435011</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.593133</v>
+        <v>-34.56566</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10037,7 +10037,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S01385955</t>
+          <t xml:space="preserve">9118 </t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>POSADAS 1391</t>
+          <t>ORTEGA Y GASSET 1590</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10060,11 +10060,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>814108527</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10082,7 +10078,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10094,14 +10090,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.385947</v>
+        <v>-58.430774</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.588156</v>
+        <v>-34.568179</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10111,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>RET-L</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10123,7 +10119,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S00432540</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10133,7 +10129,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DUMONT, SANTOS 2618</t>
+          <t>ARCE 867</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10148,7 +10144,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>814111029</t>
+          <t>814108660</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10158,7 +10154,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10180,10 +10176,10 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.440439</v>
+        <v>-58.436255</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.575416</v>
+        <v>-34.567733</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10197,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>BLO-J</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10209,7 +10205,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179 </t>
+          <t xml:space="preserve">9193 </t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10219,7 +10215,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ARAOZ 2289</t>
+          <t>CRAMER 315</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10234,7 +10230,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>814108607</t>
+          <t>814109172</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10266,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.418131</v>
+        <v>-58.443403</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.58774</v>
+        <v>-34.575666</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10283,7 +10279,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10295,7 +10291,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9180 </t>
+          <t xml:space="preserve">9199 </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10305,7 +10301,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MIGUELETES 1156</t>
+          <t>ARMENIA 1553</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10320,7 +10316,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>814108619</t>
+          <t>814109219</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10352,10 +10348,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.438274</v>
+        <v>-58.428639</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.564049</v>
+        <v>-34.59039</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10369,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10381,7 +10377,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9115 </t>
+          <t>S00497843</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10391,12 +10387,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 1694</t>
+          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10406,7 +10402,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>814108632</t>
+          <t>814109418</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10438,14 +10434,14 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.434721</v>
+        <v>-58.404726</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.567241</v>
+        <v>-34.596069</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10455,7 +10451,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>BLO-H</t>
+          <t>AGU-A</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10467,7 +10463,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9116 </t>
+          <t>S00522384</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10477,7 +10473,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GOROSTIAGA 1514</t>
+          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10490,11 +10486,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>814108642</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10512,7 +10504,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -10524,10 +10516,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.435738</v>
+        <v>-58.422183</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.564606</v>
+        <v>-34.576849</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10541,7 +10533,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-M</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10553,7 +10545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117 </t>
+          <t xml:space="preserve">9220 </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10563,7 +10555,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MAURE 1590</t>
+          <t>ARMENIA 1829</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10578,7 +10570,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>814108650</t>
+          <t>814109740</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10588,7 +10580,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA, POSIBLE NUEVA ALEDAÑA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10610,10 +10602,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.435011</v>
+        <v>-58.425803</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.56566</v>
+        <v>-34.588513</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10627,7 +10619,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10639,7 +10631,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118 </t>
+          <t xml:space="preserve">9945 </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,7 +10641,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ORTEGA Y GASSET 1590</t>
+          <t>LACROZE, FEDERICO AV. 1938</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10662,7 +10654,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>814109788</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10680,7 +10676,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -10692,10 +10688,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.430774</v>
+        <v>-58.440759</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.568179</v>
+        <v>-34.565819</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10709,7 +10705,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>BLO-L</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10721,17 +10717,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t xml:space="preserve">10033 </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ARCE 867</t>
+          <t>ESTADO DE PALESTINA 1192</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10744,11 +10740,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>814108660</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -10756,17 +10748,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -10778,10 +10770,10 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.436255</v>
+        <v>-58.424388</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.567733</v>
+        <v>-34.59632</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10795,7 +10787,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>BLO-J</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,17 +10799,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9193 </t>
+          <t xml:space="preserve">9157 </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CRAMER 315</t>
+          <t>GUATEMALA 5078</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10832,7 +10824,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>814109172</t>
+          <t>814108116</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10864,10 +10856,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.443403</v>
+        <v>-58.427895</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.575666</v>
+        <v>-34.583677</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10881,7 +10873,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,17 +10885,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9199 </t>
+          <t xml:space="preserve">10047 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ARMENIA 1553</t>
+          <t>NEWBERY, JORGE 2410</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10918,7 +10910,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>814109219</t>
+          <t>814111706</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10928,7 +10920,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10950,10 +10942,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.428639</v>
+        <v>-58.440973</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.59039</v>
+        <v>-34.572415</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10967,7 +10959,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>VCR-F</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,17 +10971,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S00497843</t>
+          <t>S01035299</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MANSILLA, LUCIO NORBERTO, GENERAL 2610</t>
+          <t>ECUADOR 1390</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11002,11 +10994,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>814109418</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11014,17 +11002,17 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -11036,14 +11024,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.404726</v>
+        <v>-58.40382</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.596069</v>
+        <v>-34.594385</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11065,17 +11053,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S00522384</t>
+          <t xml:space="preserve">10042 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FRAY JUSTO SANTAMARIA DE ORO 2734</t>
+          <t>PARAGUAY 5310</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11088,7 +11076,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>814108322</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11106,7 +11098,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -11118,10 +11110,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.422183</v>
+        <v>-58.43218</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.576849</v>
+        <v>-34.578546</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11135,7 +11127,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>VCR-M</t>
+          <t>ATH-B</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11147,17 +11139,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220 </t>
+          <t xml:space="preserve">10062 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ARMENIA 1829</t>
+          <t>HUMBOLDT 1556</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11172,7 +11164,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>814109740</t>
+          <t>814108343</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11204,10 +11196,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.425803</v>
+        <v>-58.436737</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.588513</v>
+        <v>-34.58597</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11221,7 +11213,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11233,17 +11225,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9945 </t>
+          <t xml:space="preserve">10066 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LACROZE, FEDERICO AV. 1938</t>
+          <t xml:space="preserve">ARENALES 3640 </t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11256,11 +11248,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>814109788</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11268,12 +11256,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -11290,10 +11278,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.440759</v>
+        <v>-58.413584</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.565819</v>
+        <v>-34.58551</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11307,7 +11295,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>BLO-L</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11319,7 +11307,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033 </t>
+          <t xml:space="preserve">10067 </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11329,7 +11317,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 1192</t>
+          <t>CHARCAS 3601</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11372,10 +11360,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.424388</v>
+        <v>-58.415912</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.59632</v>
+        <v>-34.588977</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11389,7 +11377,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>VCR-E</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11401,7 +11389,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9157 </t>
+          <t xml:space="preserve">10072 </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11411,7 +11399,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GUATEMALA 5078</t>
+          <t>SANTA FE AV. 3470</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11426,7 +11414,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>814108116</t>
+          <t>814111751</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11436,7 +11424,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11458,10 +11446,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.427895</v>
+        <v>-58.413885</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.583677</v>
+        <v>-34.586628</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11475,7 +11463,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11487,7 +11475,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">10047 </t>
+          <t xml:space="preserve">10082 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11497,7 +11485,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NEWBERY, JORGE 2410</t>
+          <t>TAGLE 2562</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11512,7 +11500,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>814111706</t>
+          <t>814108377</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11522,7 +11510,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11544,14 +11532,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.440973</v>
+        <v>-58.400188</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.572415</v>
+        <v>-34.583882</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11561,7 +11549,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>AGU-I</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11573,7 +11561,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S01035299</t>
+          <t xml:space="preserve">10083 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11583,12 +11571,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ECUADOR 1390</t>
+          <t>ORTIZ DE OCAMPO 2639</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11596,7 +11584,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>814111784</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11609,12 +11601,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -11626,10 +11618,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.40382</v>
+        <v>-58.404652</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.594385</v>
+        <v>-34.58263</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11643,7 +11635,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>AGU-A</t>
+          <t>AGU-N</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11655,7 +11647,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">10042 </t>
+          <t xml:space="preserve">10098 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11665,7 +11657,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PARAGUAY 5310</t>
+          <t>DORREGO AV. 2635</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11680,7 +11672,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>814108322</t>
+          <t>814108458</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11712,10 +11704,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.43218</v>
+        <v>-58.433857</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.578546</v>
+        <v>-34.57424</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11729,7 +11721,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ATH-B</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11741,7 +11733,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">10062 </t>
+          <t xml:space="preserve">10103 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11751,7 +11743,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HUMBOLDT 1556</t>
+          <t>DORREGO AV. 2765</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11766,7 +11758,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>814108343</t>
+          <t>814111791</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11776,7 +11768,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11798,10 +11790,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.436737</v>
+        <v>-58.432319</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.58597</v>
+        <v>-34.574385</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11815,7 +11807,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11827,7 +11819,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">10066 </t>
+          <t xml:space="preserve">10104 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11837,7 +11829,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARENALES 3640 </t>
+          <t xml:space="preserve">DORREGO AV. 4050 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11850,7 +11842,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>814108469</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11858,12 +11854,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA</t>
+          <t xml:space="preserve">CAMBIAR COLUMNA </t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11880,10 +11876,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.413584</v>
+        <v>-58.416882</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.58551</v>
+        <v>-34.562655</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11897,7 +11893,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>BLO-?</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11909,7 +11905,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067 </t>
+          <t xml:space="preserve">10129 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11919,7 +11915,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CHARCAS 3601</t>
+          <t>ALVAREZ, JULIAN 1890</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11932,7 +11928,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>814111804</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -11945,27 +11945,27 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.415912</v>
+        <v>-58.42056</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.588977</v>
+        <v>-34.590217</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>VCR-E</t>
+          <t>VCR-D</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">10072 </t>
+          <t xml:space="preserve">10131 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SANTA FE AV. 3470</t>
+          <t xml:space="preserve">PARAGUAY 4022 </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12014,11 +12014,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>814111751</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12026,7 +12022,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12036,7 +12032,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12048,10 +12044,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.413885</v>
+        <v>-58.419652</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.586628</v>
+        <v>-34.588271</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12065,7 +12061,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-K</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12077,17 +12073,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">10082 </t>
+          <t>-775</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TAGLE 2562</t>
+          <t>11 DE SEPTIEMBRE DE 1888 996</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12102,7 +12098,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>814108377</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12112,7 +12108,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12122,7 +12118,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12134,14 +12130,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.400188</v>
+        <v>-58.442098</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.583882</v>
+        <v>-34.568762</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12151,7 +12147,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>AGU-I</t>
+          <t>BLO-G</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12163,17 +12159,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10083 </t>
+          <t>-781</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ORTIZ DE OCAMPO 2639</t>
+          <t>ARENALES 3658</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12188,7 +12184,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>814111784</t>
+          <t>814125568</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12198,7 +12194,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12220,14 +12216,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.404652</v>
+        <v>-58.413717</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.58263</v>
+        <v>-34.585425</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12237,7 +12233,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>AGU-N</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12249,17 +12245,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098 </t>
+          <t>-782</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2635</t>
+          <t>ARMENIA 1800</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12274,7 +12270,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>814108458</t>
+          <t>814125577</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12284,7 +12280,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12306,10 +12302,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.433857</v>
+        <v>-58.426328</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.57424</v>
+        <v>-34.588734</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12323,7 +12319,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>VCR-F</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12335,17 +12331,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10103 </t>
+          <t>-787</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DORREGO AV. 2765</t>
+          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12360,7 +12356,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>814111791</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12370,7 +12366,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12380,7 +12376,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -12392,10 +12388,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.432319</v>
+        <v>-58.432822</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.574385</v>
+        <v>-34.571917</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12409,7 +12405,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>BLO-G</t>
+          <t>BLO-H</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12421,22 +12417,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104 </t>
+          <t>-797</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">DORREGO AV. 4050 </t>
+          <t>CHARCAS 3248</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12446,7 +12442,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>814108469</t>
+          <t>814125633</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12456,7 +12452,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBIAR COLUMNA </t>
+          <t>columna chocada</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12478,14 +12474,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.416882</v>
+        <v>-58.411747</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.562655</v>
+        <v>-34.592175</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12495,7 +12491,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>BLO-?</t>
+          <t>AGU-C</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12507,17 +12503,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10129 </t>
+          <t>-805</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ALVAREZ, JULIAN 1890</t>
+          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12532,7 +12528,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>814111804</t>
+          <t>814125656</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12542,7 +12538,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12557,17 +12553,17 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.42056</v>
+        <v>-58.432345</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.590217</v>
+        <v>-34.566345</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12581,7 +12577,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>VCR-D</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12593,22 +12589,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131 </t>
+          <t>814446825</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/11/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARAGUAY 4022 </t>
+          <t>ANGEL GALLARDO 1084</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12616,7 +12612,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>814446825</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>PEBCOM</t>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12643,17 +12643,17 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.419652</v>
+        <v>-58.445084</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.588271</v>
+        <v>-34.60725</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12663,784 +12663,10 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>VCR-K</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>-775</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>11 DE SEPTIEMBRE DE 1888 996</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>1</v>
-      </c>
-      <c r="M144" t="n">
-        <v>-58.442098</v>
-      </c>
-      <c r="N144" t="n">
-        <v>-34.568762</v>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>BLO-G</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>-781</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>ARENALES 3658</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>814125568</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L145" t="n">
-        <v>1</v>
-      </c>
-      <c r="M145" t="n">
-        <v>-58.413717</v>
-      </c>
-      <c r="N145" t="n">
-        <v>-34.585425</v>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>AGU-L</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>-782</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>ARMENIA 1800</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>814125577</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="n">
-        <v>-58.426328</v>
-      </c>
-      <c r="N146" t="n">
-        <v>-34.588734</v>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>VCR-F</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>-787</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>CHENAUT, INDALESIO, GRAL. AV. 1945</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
-        <v>1</v>
-      </c>
-      <c r="M147" t="n">
-        <v>-58.432822</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-34.571917</v>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>BLO-H</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>-796</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>CABRERA, JOSE A. 4723</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>814125624</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L148" t="n">
-        <v>1</v>
-      </c>
-      <c r="M148" t="n">
-        <v>-58.429431</v>
-      </c>
-      <c r="N148" t="n">
-        <v>-34.591921</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>VCR-F</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>-797</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>CHARCAS 3248</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>814125633</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>columna chocada</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="n">
-        <v>-58.411747</v>
-      </c>
-      <c r="N149" t="n">
-        <v>-34.592175</v>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>AGU-C</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>-805</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>MATIENZO, BENJAMIN, TENIENTE 1510</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>814125656</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L150" t="n">
-        <v>1</v>
-      </c>
-      <c r="M150" t="n">
-        <v>-58.432345</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-34.566345</v>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>BLO-I</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>814446819</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>6/11/2026</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>ANGEL GALLARDO 946</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>814446819</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="n">
-        <v>-58.443588</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-34.606863</v>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>ALM-O</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>814446825</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>6/11/2026</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>ANGEL GALLARDO 1084</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>814446825</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>PEBCOM</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="n">
-        <v>-58.445084</v>
-      </c>
-      <c r="N152" t="n">
-        <v>-34.60725</v>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>ALM-O</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>
